--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.85</v>
+        <v>3.89</v>
       </c>
       <c r="F14" t="n">
-        <v>12.26</v>
+        <v>12.2</v>
       </c>
       <c r="G14" t="n">
-        <v>187.5</v>
+        <v>204.1</v>
       </c>
       <c r="H14" t="n">
-        <v>86.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>47.4</v>
+        <v>84.27</v>
       </c>
       <c r="K14" t="n">
-        <v>-14.63</v>
+        <v>-101.78</v>
       </c>
       <c r="L14" t="n">
-        <v>49.6</v>
+        <v>132.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:31:02</t>
+          <t>04:30:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="F15" t="n">
-        <v>13.41</v>
+        <v>11.76</v>
       </c>
       <c r="G15" t="n">
-        <v>175.7</v>
+        <v>184.3</v>
       </c>
       <c r="H15" t="n">
-        <v>74.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>8.44</v>
+        <v>-56.83</v>
       </c>
       <c r="K15" t="n">
-        <v>-93.73</v>
+        <v>-325.96</v>
       </c>
       <c r="L15" t="n">
-        <v>94.11</v>
+        <v>330.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:33:03</t>
+          <t>04:32:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="F16" t="n">
-        <v>11.81</v>
+        <v>12.37</v>
       </c>
       <c r="G16" t="n">
-        <v>194.8</v>
+        <v>194.4</v>
       </c>
       <c r="H16" t="n">
-        <v>85.5</v>
+        <v>82.8</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>12.68</v>
+        <v>-67.5</v>
       </c>
       <c r="K16" t="n">
-        <v>40.42</v>
+        <v>-37.61</v>
       </c>
       <c r="L16" t="n">
-        <v>42.36</v>
+        <v>77.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:36:21</t>
+          <t>04:37:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.66</v>
+        <v>4.09</v>
       </c>
       <c r="F17" t="n">
-        <v>11.58</v>
+        <v>12.32</v>
       </c>
       <c r="G17" t="n">
-        <v>179</v>
+        <v>176.2</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>75.7</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>48.78</v>
+        <v>213.27</v>
       </c>
       <c r="K17" t="n">
-        <v>110.86</v>
+        <v>164.37</v>
       </c>
       <c r="L17" t="n">
-        <v>121.12</v>
+        <v>269.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:37:33</t>
+          <t>04:38:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="F18" t="n">
-        <v>11.45</v>
+        <v>12.48</v>
       </c>
       <c r="G18" t="n">
-        <v>192.5</v>
+        <v>177.7</v>
       </c>
       <c r="H18" t="n">
-        <v>86.8</v>
+        <v>79.2</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-89.79000000000001</v>
+        <v>125.68</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.55</v>
+        <v>-229.61</v>
       </c>
       <c r="L18" t="n">
-        <v>89.83</v>
+        <v>261.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:39:52</t>
+          <t>04:39:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4</v>
+        <v>13.02</v>
       </c>
       <c r="G19" t="n">
-        <v>178.7</v>
+        <v>197.6</v>
       </c>
       <c r="H19" t="n">
-        <v>79.3</v>
+        <v>77.5</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-36.89</v>
+        <v>105.84</v>
       </c>
       <c r="K19" t="n">
-        <v>30.01</v>
+        <v>-437.32</v>
       </c>
       <c r="L19" t="n">
-        <v>47.56</v>
+        <v>449.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:45:36</t>
+          <t>04:43:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="F20" t="n">
-        <v>12.61</v>
+        <v>12.11</v>
       </c>
       <c r="G20" t="n">
-        <v>185.8</v>
+        <v>177.6</v>
       </c>
       <c r="H20" t="n">
-        <v>84.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>314.09</v>
+        <v>-404.86</v>
       </c>
       <c r="K20" t="n">
-        <v>183.25</v>
+        <v>-98.89</v>
       </c>
       <c r="L20" t="n">
-        <v>363.64</v>
+        <v>416.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:46:49</t>
+          <t>04:44:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="F21" t="n">
-        <v>11.35</v>
+        <v>12.82</v>
       </c>
       <c r="G21" t="n">
-        <v>179.7</v>
+        <v>184.3</v>
       </c>
       <c r="H21" t="n">
-        <v>77.2</v>
+        <v>75.5</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>480.27</v>
+        <v>-214.66</v>
       </c>
       <c r="K21" t="n">
-        <v>88.13</v>
+        <v>-81</v>
       </c>
       <c r="L21" t="n">
-        <v>488.29</v>
+        <v>229.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:48:43</t>
+          <t>04:45:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="F22" t="n">
-        <v>12.82</v>
+        <v>12.76</v>
       </c>
       <c r="G22" t="n">
-        <v>203.2</v>
+        <v>182.7</v>
       </c>
       <c r="H22" t="n">
-        <v>80.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-215.81</v>
+        <v>-48.6</v>
       </c>
       <c r="K22" t="n">
-        <v>290.74</v>
+        <v>25.35</v>
       </c>
       <c r="L22" t="n">
-        <v>362.08</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:52:16</t>
+          <t>04:50:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="F23" t="n">
-        <v>12.22</v>
+        <v>12.21</v>
       </c>
       <c r="G23" t="n">
-        <v>180.3</v>
+        <v>186</v>
       </c>
       <c r="H23" t="n">
-        <v>86.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-256.12</v>
+        <v>-84.19</v>
       </c>
       <c r="K23" t="n">
-        <v>467.38</v>
+        <v>276.74</v>
       </c>
       <c r="L23" t="n">
-        <v>532.95</v>
+        <v>289.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:53:07</t>
+          <t>04:52:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="F24" t="n">
-        <v>11.98</v>
+        <v>12.64</v>
       </c>
       <c r="G24" t="n">
-        <v>188.1</v>
+        <v>181.5</v>
       </c>
       <c r="H24" t="n">
-        <v>77.8</v>
+        <v>83</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-59.77</v>
+        <v>-60.34</v>
       </c>
       <c r="K24" t="n">
-        <v>-74.01000000000001</v>
+        <v>-763.1</v>
       </c>
       <c r="L24" t="n">
-        <v>95.13</v>
+        <v>765.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:53:46</t>
+          <t>04:54:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="F25" t="n">
-        <v>12.25</v>
+        <v>11.72</v>
       </c>
       <c r="G25" t="n">
-        <v>200.7</v>
+        <v>197.1</v>
       </c>
       <c r="H25" t="n">
-        <v>73.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-291.89</v>
+        <v>355.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-355.43</v>
+        <v>-302.48</v>
       </c>
       <c r="L25" t="n">
-        <v>459.93</v>
+        <v>466.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>04:58:57</t>
+          <t>05:00:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.49</v>
+        <v>3.96</v>
       </c>
       <c r="F26" t="n">
-        <v>11.25</v>
+        <v>11.81</v>
       </c>
       <c r="G26" t="n">
-        <v>193</v>
+        <v>185.5</v>
       </c>
       <c r="H26" t="n">
-        <v>77.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-300.6</v>
+        <v>300.51</v>
       </c>
       <c r="K26" t="n">
-        <v>-260.59</v>
+        <v>71.83</v>
       </c>
       <c r="L26" t="n">
-        <v>397.83</v>
+        <v>308.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:00:39</t>
+          <t>05:02:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.41</v>
+        <v>3.43</v>
       </c>
       <c r="F27" t="n">
-        <v>11.27</v>
+        <v>12.49</v>
       </c>
       <c r="G27" t="n">
-        <v>184.4</v>
+        <v>191.3</v>
       </c>
       <c r="H27" t="n">
-        <v>77.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-434.3</v>
+        <v>-605.28</v>
       </c>
       <c r="K27" t="n">
-        <v>-211.32</v>
+        <v>-32.82</v>
       </c>
       <c r="L27" t="n">
-        <v>482.98</v>
+        <v>606.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:02:54</t>
+          <t>05:03:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="F28" t="n">
-        <v>12.43</v>
+        <v>11.42</v>
       </c>
       <c r="G28" t="n">
-        <v>186.8</v>
+        <v>204</v>
       </c>
       <c r="H28" t="n">
-        <v>72.2</v>
+        <v>82.2</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>40.11</v>
+        <v>-167.13</v>
       </c>
       <c r="K28" t="n">
-        <v>-138.57</v>
+        <v>108.8</v>
       </c>
       <c r="L28" t="n">
-        <v>144.26</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:13:51</t>
+          <t>05:13:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.28</v>
+        <v>3.08</v>
       </c>
       <c r="F29" t="n">
-        <v>11.61</v>
+        <v>12.23</v>
       </c>
       <c r="G29" t="n">
-        <v>190.7</v>
+        <v>172.6</v>
       </c>
       <c r="H29" t="n">
-        <v>84.8</v>
+        <v>80</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-106.74</v>
+        <v>-30.98</v>
       </c>
       <c r="K29" t="n">
-        <v>69.37</v>
+        <v>152.92</v>
       </c>
       <c r="L29" t="n">
-        <v>127.3</v>
+        <v>156.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:15:52</t>
+          <t>05:14:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.33</v>
+        <v>4.08</v>
       </c>
       <c r="F30" t="n">
-        <v>12.14</v>
+        <v>12.22</v>
       </c>
       <c r="G30" t="n">
-        <v>186.7</v>
+        <v>188.5</v>
       </c>
       <c r="H30" t="n">
-        <v>84.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>31.54</v>
+        <v>9.59</v>
       </c>
       <c r="K30" t="n">
-        <v>-181.57</v>
+        <v>-393.17</v>
       </c>
       <c r="L30" t="n">
-        <v>184.29</v>
+        <v>393.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:17:54</t>
+          <t>05:17:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.73</v>
+        <v>3.57</v>
       </c>
       <c r="F31" t="n">
-        <v>11.56</v>
+        <v>12.1</v>
       </c>
       <c r="G31" t="n">
-        <v>191.4</v>
+        <v>194.9</v>
       </c>
       <c r="H31" t="n">
-        <v>82.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>1.35</v>
+        <v>-84.67</v>
       </c>
       <c r="K31" t="n">
-        <v>-294.85</v>
+        <v>244.34</v>
       </c>
       <c r="L31" t="n">
-        <v>294.86</v>
+        <v>258.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:22:16</t>
+          <t>05:21:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.06</v>
+        <v>3.39</v>
       </c>
       <c r="F32" t="n">
-        <v>11.84</v>
+        <v>12.86</v>
       </c>
       <c r="G32" t="n">
-        <v>185.3</v>
+        <v>200.1</v>
       </c>
       <c r="H32" t="n">
-        <v>81.7</v>
+        <v>84.3</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>218.45</v>
+        <v>183.73</v>
       </c>
       <c r="K32" t="n">
-        <v>-28.65</v>
+        <v>2.13</v>
       </c>
       <c r="L32" t="n">
-        <v>220.32</v>
+        <v>183.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:57</t>
+          <t>05:23:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.69</v>
+        <v>2.85</v>
       </c>
       <c r="F33" t="n">
-        <v>12.01</v>
+        <v>11.81</v>
       </c>
       <c r="G33" t="n">
-        <v>185.1</v>
+        <v>186.7</v>
       </c>
       <c r="H33" t="n">
-        <v>80.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>202.77</v>
+        <v>248.44</v>
       </c>
       <c r="K33" t="n">
-        <v>104.17</v>
+        <v>249.18</v>
       </c>
       <c r="L33" t="n">
-        <v>227.97</v>
+        <v>351.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:26:15</t>
+          <t>05:24:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42</v>
+        <v>12.9</v>
       </c>
       <c r="G34" t="n">
-        <v>186.5</v>
+        <v>193.2</v>
       </c>
       <c r="H34" t="n">
-        <v>79.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-100.03</v>
+        <v>78.98</v>
       </c>
       <c r="K34" t="n">
-        <v>166.37</v>
+        <v>86.2</v>
       </c>
       <c r="L34" t="n">
-        <v>194.13</v>
+        <v>116.92</v>
       </c>
     </row>
     <row r="35">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.08</v>
+        <v>3.89</v>
       </c>
       <c r="F35" t="n">
-        <v>12.28</v>
+        <v>12.23</v>
       </c>
       <c r="G35" t="n">
-        <v>180.9</v>
+        <v>193.5</v>
       </c>
       <c r="H35" t="n">
-        <v>83.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-330.8</v>
+        <v>74.33</v>
       </c>
       <c r="K35" t="n">
-        <v>-102.47</v>
+        <v>173.03</v>
       </c>
       <c r="L35" t="n">
-        <v>346.31</v>
+        <v>188.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:32:06</t>
+          <t>05:32:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="F36" t="n">
-        <v>11.87</v>
+        <v>11.86</v>
       </c>
       <c r="G36" t="n">
-        <v>188.6</v>
+        <v>184.5</v>
       </c>
       <c r="H36" t="n">
-        <v>80.5</v>
+        <v>78.3</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-34.52</v>
+        <v>103.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-246.97</v>
+        <v>224.32</v>
       </c>
       <c r="L36" t="n">
-        <v>249.37</v>
+        <v>247.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:33:26</t>
+          <t>05:34:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="F37" t="n">
-        <v>12.03</v>
+        <v>12.13</v>
       </c>
       <c r="G37" t="n">
-        <v>194.9</v>
+        <v>188.3</v>
       </c>
       <c r="H37" t="n">
-        <v>74.7</v>
+        <v>79.5</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>581.0599999999999</v>
+        <v>238.34</v>
       </c>
       <c r="K37" t="n">
-        <v>-407.77</v>
+        <v>211.89</v>
       </c>
       <c r="L37" t="n">
-        <v>709.86</v>
+        <v>318.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:39:26</t>
+          <t>05:40:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="F38" t="n">
-        <v>12.72</v>
+        <v>12.02</v>
       </c>
       <c r="G38" t="n">
-        <v>202.5</v>
+        <v>195</v>
       </c>
       <c r="H38" t="n">
-        <v>89.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-270.69</v>
+        <v>-185.68</v>
       </c>
       <c r="K38" t="n">
-        <v>479.02</v>
+        <v>415.28</v>
       </c>
       <c r="L38" t="n">
-        <v>550.22</v>
+        <v>454.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:41:37</t>
+          <t>05:42:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.22</v>
+        <v>4.31</v>
       </c>
       <c r="F39" t="n">
-        <v>12.08</v>
+        <v>11.9</v>
       </c>
       <c r="G39" t="n">
-        <v>179.3</v>
+        <v>209</v>
       </c>
       <c r="H39" t="n">
-        <v>80.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>64.72</v>
+        <v>-20.45</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.55</v>
+        <v>-471.97</v>
       </c>
       <c r="L39" t="n">
-        <v>97.22</v>
+        <v>472.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:43:35</t>
+          <t>05:44:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.88</v>
+        <v>3.69</v>
       </c>
       <c r="F40" t="n">
-        <v>12.01</v>
+        <v>12.58</v>
       </c>
       <c r="G40" t="n">
-        <v>186.5</v>
+        <v>190.6</v>
       </c>
       <c r="H40" t="n">
-        <v>82.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-24.54</v>
+        <v>-211.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-341.39</v>
+        <v>-105.34</v>
       </c>
       <c r="L40" t="n">
-        <v>342.27</v>
+        <v>236.27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:48:39</t>
+          <t>05:49:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.03</v>
+        <v>4.27</v>
       </c>
       <c r="F41" t="n">
-        <v>12.76</v>
+        <v>12.27</v>
       </c>
       <c r="G41" t="n">
-        <v>183.4</v>
+        <v>183.6</v>
       </c>
       <c r="H41" t="n">
-        <v>85.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>62.24</v>
+        <v>535.47</v>
       </c>
       <c r="K41" t="n">
-        <v>949.09</v>
+        <v>652.28</v>
       </c>
       <c r="L41" t="n">
-        <v>951.13</v>
+        <v>843.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:49:40</t>
+          <t>05:51:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="F42" t="n">
-        <v>11.54</v>
+        <v>11.77</v>
       </c>
       <c r="G42" t="n">
-        <v>176</v>
+        <v>191.5</v>
       </c>
       <c r="H42" t="n">
-        <v>87.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>253.08</v>
+        <v>1247.81</v>
       </c>
       <c r="K42" t="n">
-        <v>175.55</v>
+        <v>49.93</v>
       </c>
       <c r="L42" t="n">
-        <v>308.01</v>
+        <v>1248.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:50:37</t>
+          <t>05:54:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.54</v>
+        <v>3.43</v>
       </c>
       <c r="F43" t="n">
-        <v>12.02</v>
+        <v>12.63</v>
       </c>
       <c r="G43" t="n">
-        <v>192.4</v>
+        <v>204.9</v>
       </c>
       <c r="H43" t="n">
-        <v>85.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>58.08</v>
+        <v>-211.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-854.4400000000001</v>
+        <v>-211.76</v>
       </c>
       <c r="L43" t="n">
-        <v>856.41</v>
+        <v>299.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:59:51</t>
+          <t>06:06:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.7</v>
+        <v>4.94</v>
       </c>
       <c r="F44" t="n">
-        <v>12.27</v>
+        <v>12.34</v>
       </c>
       <c r="G44" t="n">
-        <v>201.1</v>
+        <v>189.6</v>
       </c>
       <c r="H44" t="n">
-        <v>82.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-107.91</v>
+        <v>90.03</v>
       </c>
       <c r="K44" t="n">
-        <v>101.02</v>
+        <v>139.35</v>
       </c>
       <c r="L44" t="n">
-        <v>147.81</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:02:01</t>
+          <t>06:08:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.34</v>
+        <v>3.65</v>
       </c>
       <c r="F45" t="n">
-        <v>11.36</v>
+        <v>11.91</v>
       </c>
       <c r="G45" t="n">
-        <v>196.3</v>
+        <v>182.9</v>
       </c>
       <c r="H45" t="n">
-        <v>85.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>43.3</v>
+        <v>-64.39</v>
       </c>
       <c r="K45" t="n">
-        <v>-331.97</v>
+        <v>-61.42</v>
       </c>
       <c r="L45" t="n">
-        <v>334.78</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:03:15</t>
+          <t>06:09:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="F46" t="n">
-        <v>12.05</v>
+        <v>12.29</v>
       </c>
       <c r="G46" t="n">
-        <v>189.3</v>
+        <v>183.8</v>
       </c>
       <c r="H46" t="n">
-        <v>80.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>74.03</v>
+        <v>145.61</v>
       </c>
       <c r="K46" t="n">
-        <v>84.05</v>
+        <v>228.24</v>
       </c>
       <c r="L46" t="n">
-        <v>112</v>
+        <v>270.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:06:34</t>
+          <t>06:14:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.84</v>
+        <v>4.42</v>
       </c>
       <c r="F47" t="n">
-        <v>12.25</v>
+        <v>12.43</v>
       </c>
       <c r="G47" t="n">
-        <v>191.9</v>
+        <v>188.2</v>
       </c>
       <c r="H47" t="n">
-        <v>74.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>108.74</v>
+        <v>122.02</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.74</v>
+        <v>-34.71</v>
       </c>
       <c r="L47" t="n">
-        <v>113.85</v>
+        <v>126.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:08:14</t>
+          <t>06:15:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="F48" t="n">
-        <v>11.95</v>
+        <v>11.87</v>
       </c>
       <c r="G48" t="n">
-        <v>206.2</v>
+        <v>187.8</v>
       </c>
       <c r="H48" t="n">
-        <v>75.8</v>
+        <v>83.7</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-115.46</v>
+        <v>-119.45</v>
       </c>
       <c r="K48" t="n">
-        <v>14.86</v>
+        <v>35.84</v>
       </c>
       <c r="L48" t="n">
-        <v>116.41</v>
+        <v>124.71</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:10:29</t>
+          <t>06:17:44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="F49" t="n">
-        <v>12.7</v>
+        <v>12.37</v>
       </c>
       <c r="G49" t="n">
-        <v>188.8</v>
+        <v>180.9</v>
       </c>
       <c r="H49" t="n">
-        <v>78.3</v>
+        <v>81.2</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>41.58</v>
+        <v>-141.51</v>
       </c>
       <c r="K49" t="n">
-        <v>12.66</v>
+        <v>0.66</v>
       </c>
       <c r="L49" t="n">
-        <v>43.46</v>
+        <v>141.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:14:17</t>
+          <t>06:22:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="F50" t="n">
-        <v>12.83</v>
+        <v>11.9</v>
       </c>
       <c r="G50" t="n">
-        <v>187.3</v>
+        <v>191.8</v>
       </c>
       <c r="H50" t="n">
-        <v>80.8</v>
+        <v>79.2</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-193.08</v>
+        <v>-364.15</v>
       </c>
       <c r="K50" t="n">
-        <v>460.76</v>
+        <v>-120.39</v>
       </c>
       <c r="L50" t="n">
-        <v>499.58</v>
+        <v>383.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:16:01</t>
+          <t>06:23:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="F51" t="n">
-        <v>11.89</v>
+        <v>13.05</v>
       </c>
       <c r="G51" t="n">
-        <v>180.1</v>
+        <v>185.8</v>
       </c>
       <c r="H51" t="n">
-        <v>79</v>
+        <v>74.7</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.57</v>
+        <v>-88.51000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-109.05</v>
+        <v>-56.23</v>
       </c>
       <c r="L51" t="n">
-        <v>109.57</v>
+        <v>104.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:17:23</t>
+          <t>06:25:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
       <c r="F52" t="n">
-        <v>11.69</v>
+        <v>11.65</v>
       </c>
       <c r="G52" t="n">
-        <v>195.3</v>
+        <v>182</v>
       </c>
       <c r="H52" t="n">
-        <v>78.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-170.01</v>
+        <v>-310.56</v>
       </c>
       <c r="K52" t="n">
-        <v>-301.99</v>
+        <v>-124.12</v>
       </c>
       <c r="L52" t="n">
-        <v>346.55</v>
+        <v>334.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:22:39</t>
+          <t>06:29:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.21</v>
+        <v>3.53</v>
       </c>
       <c r="F53" t="n">
-        <v>11.84</v>
+        <v>12.25</v>
       </c>
       <c r="G53" t="n">
-        <v>175.7</v>
+        <v>175.3</v>
       </c>
       <c r="H53" t="n">
-        <v>76.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>329.2</v>
+        <v>-117.23</v>
       </c>
       <c r="K53" t="n">
-        <v>401.9</v>
+        <v>587.97</v>
       </c>
       <c r="L53" t="n">
-        <v>519.52</v>
+        <v>599.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:24:03</t>
+          <t>06:30:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="F54" t="n">
-        <v>12.02</v>
+        <v>12.67</v>
       </c>
       <c r="G54" t="n">
-        <v>193.7</v>
+        <v>180.8</v>
       </c>
       <c r="H54" t="n">
-        <v>76.8</v>
+        <v>93</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>362.46</v>
+        <v>-79.70999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>391.37</v>
+        <v>-487.31</v>
       </c>
       <c r="L54" t="n">
-        <v>533.4299999999999</v>
+        <v>493.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:25:34</t>
+          <t>06:32:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.71</v>
+        <v>3.99</v>
       </c>
       <c r="F55" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="G55" t="n">
-        <v>199.9</v>
+        <v>183.6</v>
       </c>
       <c r="H55" t="n">
-        <v>74.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-564.09</v>
+        <v>-473.97</v>
       </c>
       <c r="K55" t="n">
-        <v>309.23</v>
+        <v>-284.37</v>
       </c>
       <c r="L55" t="n">
-        <v>643.29</v>
+        <v>552.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:31:12</t>
+          <t>06:37:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.39</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="n">
-        <v>12.54</v>
+        <v>12.07</v>
       </c>
       <c r="G56" t="n">
-        <v>191.2</v>
+        <v>186.4</v>
       </c>
       <c r="H56" t="n">
-        <v>81</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>122.5</v>
+        <v>155.11</v>
       </c>
       <c r="K56" t="n">
-        <v>-590.9</v>
+        <v>-246.13</v>
       </c>
       <c r="L56" t="n">
-        <v>603.47</v>
+        <v>290.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:32:47</t>
+          <t>06:40:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.5</v>
+        <v>3.81</v>
       </c>
       <c r="F57" t="n">
-        <v>12.21</v>
+        <v>12.37</v>
       </c>
       <c r="G57" t="n">
-        <v>182.3</v>
+        <v>181.9</v>
       </c>
       <c r="H57" t="n">
-        <v>74.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-163.52</v>
+        <v>-241.99</v>
       </c>
       <c r="K57" t="n">
-        <v>-51.04</v>
+        <v>-531.2</v>
       </c>
       <c r="L57" t="n">
-        <v>171.3</v>
+        <v>583.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:34:31</t>
+          <t>06:42:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="F58" t="n">
-        <v>12.39</v>
+        <v>11.96</v>
       </c>
       <c r="G58" t="n">
-        <v>182.7</v>
+        <v>187.7</v>
       </c>
       <c r="H58" t="n">
-        <v>75.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-379.35</v>
+        <v>32.78</v>
       </c>
       <c r="K58" t="n">
-        <v>537.49</v>
+        <v>-306.02</v>
       </c>
       <c r="L58" t="n">
-        <v>657.88</v>
+        <v>307.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:44:57</t>
+          <t>06:54:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.14</v>
+        <v>3.79</v>
       </c>
       <c r="F59" t="n">
-        <v>12.12</v>
+        <v>11.63</v>
       </c>
       <c r="G59" t="n">
-        <v>189.4</v>
+        <v>190.6</v>
       </c>
       <c r="H59" t="n">
-        <v>78</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>29.69</v>
+        <v>109.26</v>
       </c>
       <c r="K59" t="n">
-        <v>18.01</v>
+        <v>136.37</v>
       </c>
       <c r="L59" t="n">
-        <v>34.72</v>
+        <v>174.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:47:15</t>
+          <t>06:56:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="F60" t="n">
-        <v>12.67</v>
+        <v>11.78</v>
       </c>
       <c r="G60" t="n">
-        <v>208.4</v>
+        <v>185.7</v>
       </c>
       <c r="H60" t="n">
-        <v>80.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>140.93</v>
+        <v>229.55</v>
       </c>
       <c r="K60" t="n">
-        <v>86.86</v>
+        <v>227.73</v>
       </c>
       <c r="L60" t="n">
-        <v>165.55</v>
+        <v>323.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:48:26</t>
+          <t>06:58:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="F61" t="n">
-        <v>12.48</v>
+        <v>11.41</v>
       </c>
       <c r="G61" t="n">
-        <v>187.4</v>
+        <v>177.8</v>
       </c>
       <c r="H61" t="n">
-        <v>82</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>113.11</v>
+        <v>45.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-267.37</v>
+        <v>62.17</v>
       </c>
       <c r="L61" t="n">
-        <v>290.31</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:53:25</t>
+          <t>07:03:31</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.47</v>
+        <v>3.91</v>
       </c>
       <c r="F62" t="n">
-        <v>12.95</v>
+        <v>12.24</v>
       </c>
       <c r="G62" t="n">
-        <v>196.7</v>
+        <v>181.4</v>
       </c>
       <c r="H62" t="n">
-        <v>80.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>172.93</v>
+        <v>-58.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-134.92</v>
+        <v>-78.77</v>
       </c>
       <c r="L62" t="n">
-        <v>219.33</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:54:51</t>
+          <t>07:05:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.12</v>
+        <v>3.87</v>
       </c>
       <c r="F63" t="n">
-        <v>12.29</v>
+        <v>12.08</v>
       </c>
       <c r="G63" t="n">
-        <v>179.9</v>
+        <v>189.3</v>
       </c>
       <c r="H63" t="n">
-        <v>83.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>177.13</v>
+        <v>10.79</v>
       </c>
       <c r="K63" t="n">
-        <v>139.98</v>
+        <v>-67.28</v>
       </c>
       <c r="L63" t="n">
-        <v>225.76</v>
+        <v>68.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:56:17</t>
+          <t>07:07:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="F64" t="n">
-        <v>11.45</v>
+        <v>12.23</v>
       </c>
       <c r="G64" t="n">
-        <v>189.5</v>
+        <v>178.2</v>
       </c>
       <c r="H64" t="n">
-        <v>79.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-59.39</v>
+        <v>-62.19</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.53</v>
+        <v>177.51</v>
       </c>
       <c r="L64" t="n">
-        <v>89.19</v>
+        <v>188.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:59:15</t>
+          <t>07:12:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.73</v>
+        <v>4.22</v>
       </c>
       <c r="F65" t="n">
-        <v>12.47</v>
+        <v>12.07</v>
       </c>
       <c r="G65" t="n">
-        <v>173.1</v>
+        <v>173.9</v>
       </c>
       <c r="H65" t="n">
-        <v>79.7</v>
+        <v>81.8</v>
       </c>
       <c r="I65" t="n">
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>14.12</v>
+        <v>320.09</v>
       </c>
       <c r="K65" t="n">
-        <v>252.41</v>
+        <v>-158.02</v>
       </c>
       <c r="L65" t="n">
-        <v>252.81</v>
+        <v>356.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:00:54</t>
+          <t>07:15:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.34</v>
+        <v>4.12</v>
       </c>
       <c r="F66" t="n">
-        <v>11.72</v>
+        <v>12.53</v>
       </c>
       <c r="G66" t="n">
-        <v>171.7</v>
+        <v>187</v>
       </c>
       <c r="H66" t="n">
-        <v>87.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-117.13</v>
+        <v>-373.28</v>
       </c>
       <c r="K66" t="n">
-        <v>-65.23999999999999</v>
+        <v>-547.17</v>
       </c>
       <c r="L66" t="n">
-        <v>134.08</v>
+        <v>662.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:02:04</t>
+          <t>07:16:31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.13</v>
+        <v>4.33</v>
       </c>
       <c r="F67" t="n">
-        <v>12.19</v>
+        <v>12.15</v>
       </c>
       <c r="G67" t="n">
-        <v>197.7</v>
+        <v>183.6</v>
       </c>
       <c r="H67" t="n">
-        <v>80.2</v>
+        <v>77.5</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-218.25</v>
+        <v>394.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-285.09</v>
+        <v>160.9</v>
       </c>
       <c r="L67" t="n">
-        <v>359.04</v>
+        <v>426.42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:05:30</t>
+          <t>07:21:03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.32</v>
+        <v>4.17</v>
       </c>
       <c r="F68" t="n">
-        <v>11.72</v>
+        <v>12.15</v>
       </c>
       <c r="G68" t="n">
-        <v>186.2</v>
+        <v>185</v>
       </c>
       <c r="H68" t="n">
-        <v>76.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-548.9</v>
+        <v>-58.47</v>
       </c>
       <c r="K68" t="n">
-        <v>86.14</v>
+        <v>-394.34</v>
       </c>
       <c r="L68" t="n">
-        <v>555.62</v>
+        <v>398.65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:06:30</t>
+          <t>07:22:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.06</v>
+        <v>4.44</v>
       </c>
       <c r="F69" t="n">
-        <v>12.75</v>
+        <v>11.57</v>
       </c>
       <c r="G69" t="n">
-        <v>188.9</v>
+        <v>203.3</v>
       </c>
       <c r="H69" t="n">
-        <v>83.3</v>
+        <v>73.7</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>298.93</v>
+        <v>-228.94</v>
       </c>
       <c r="K69" t="n">
-        <v>210.01</v>
+        <v>386.37</v>
       </c>
       <c r="L69" t="n">
-        <v>365.33</v>
+        <v>449.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:08:57</t>
+          <t>07:23:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.48</v>
+        <v>4.13</v>
       </c>
       <c r="F70" t="n">
-        <v>11.94</v>
+        <v>12.65</v>
       </c>
       <c r="G70" t="n">
-        <v>196.6</v>
+        <v>177.1</v>
       </c>
       <c r="H70" t="n">
-        <v>83.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>135.8</v>
+        <v>456.68</v>
       </c>
       <c r="K70" t="n">
-        <v>-290.14</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>320.35</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:13:02</t>
+          <t>07:29:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.47</v>
+        <v>3.03</v>
       </c>
       <c r="F71" t="n">
-        <v>11.87</v>
+        <v>11.76</v>
       </c>
       <c r="G71" t="n">
-        <v>195.6</v>
+        <v>183.6</v>
       </c>
       <c r="H71" t="n">
-        <v>86.2</v>
+        <v>78.7</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-125.38</v>
+        <v>189.46</v>
       </c>
       <c r="K71" t="n">
-        <v>5.77</v>
+        <v>149.39</v>
       </c>
       <c r="L71" t="n">
-        <v>125.51</v>
+        <v>241.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:15:14</t>
+          <t>07:31:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="F72" t="n">
-        <v>11.8</v>
+        <v>11.19</v>
       </c>
       <c r="G72" t="n">
-        <v>172.2</v>
+        <v>187.1</v>
       </c>
       <c r="H72" t="n">
-        <v>81.2</v>
+        <v>74.8</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-688.78</v>
+        <v>-123.51</v>
       </c>
       <c r="K72" t="n">
-        <v>133.17</v>
+        <v>782.24</v>
       </c>
       <c r="L72" t="n">
-        <v>701.54</v>
+        <v>791.9299999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:16:23</t>
+          <t>07:33:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.94</v>
+        <v>3.37</v>
       </c>
       <c r="F73" t="n">
-        <v>12.18</v>
+        <v>12.48</v>
       </c>
       <c r="G73" t="n">
-        <v>191.1</v>
+        <v>189.7</v>
       </c>
       <c r="H73" t="n">
-        <v>77.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-717.87</v>
+        <v>-223.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-307.53</v>
+        <v>-33.78</v>
       </c>
       <c r="L73" t="n">
-        <v>780.96</v>
+        <v>226.17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:28:34</t>
+          <t>07:43:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.02</v>
+        <v>3.84</v>
       </c>
       <c r="F74" t="n">
-        <v>13.17</v>
+        <v>12.22</v>
       </c>
       <c r="G74" t="n">
-        <v>188.7</v>
+        <v>195.2</v>
       </c>
       <c r="H74" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>150.91</v>
+        <v>-223.26</v>
       </c>
       <c r="K74" t="n">
-        <v>98</v>
+        <v>-136.24</v>
       </c>
       <c r="L74" t="n">
-        <v>179.94</v>
+        <v>261.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:30:45</t>
+          <t>07:45:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="F75" t="n">
-        <v>12.45</v>
+        <v>11.65</v>
       </c>
       <c r="G75" t="n">
-        <v>201.8</v>
+        <v>187.9</v>
       </c>
       <c r="H75" t="n">
-        <v>79</v>
+        <v>76.7</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>122.05</v>
+        <v>76.05</v>
       </c>
       <c r="K75" t="n">
-        <v>50.04</v>
+        <v>59.67</v>
       </c>
       <c r="L75" t="n">
-        <v>131.91</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:47:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.39</v>
+        <v>3.76</v>
       </c>
       <c r="F76" t="n">
-        <v>12.43</v>
+        <v>12.09</v>
       </c>
       <c r="G76" t="n">
-        <v>191</v>
+        <v>186.4</v>
       </c>
       <c r="H76" t="n">
-        <v>81</v>
+        <v>82.3</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>132.44</v>
+        <v>-130.4</v>
       </c>
       <c r="K76" t="n">
-        <v>254.17</v>
+        <v>143.9</v>
       </c>
       <c r="L76" t="n">
-        <v>286.61</v>
+        <v>194.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:35:47</t>
+          <t>07:52:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.44</v>
+        <v>3.67</v>
       </c>
       <c r="F77" t="n">
-        <v>13.07</v>
+        <v>11.41</v>
       </c>
       <c r="G77" t="n">
-        <v>188.2</v>
+        <v>178.4</v>
       </c>
       <c r="H77" t="n">
-        <v>81.2</v>
+        <v>78.2</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-262.9</v>
+        <v>86.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-36.39</v>
+        <v>-184.01</v>
       </c>
       <c r="L77" t="n">
-        <v>265.41</v>
+        <v>203.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:36:54</t>
+          <t>07:54:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.87</v>
+        <v>4.17</v>
       </c>
       <c r="F78" t="n">
-        <v>12.79</v>
+        <v>12.17</v>
       </c>
       <c r="G78" t="n">
-        <v>179.9</v>
+        <v>178.9</v>
       </c>
       <c r="H78" t="n">
-        <v>80.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>7.07</v>
+        <v>-193</v>
       </c>
       <c r="K78" t="n">
-        <v>115.62</v>
+        <v>-115.24</v>
       </c>
       <c r="L78" t="n">
-        <v>115.84</v>
+        <v>224.79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:38:52</t>
+          <t>07:56:48</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="F79" t="n">
-        <v>12.02</v>
+        <v>11.95</v>
       </c>
       <c r="G79" t="n">
-        <v>189.1</v>
+        <v>170.5</v>
       </c>
       <c r="H79" t="n">
-        <v>74.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-138.83</v>
+        <v>-114.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-45.98</v>
+        <v>221.13</v>
       </c>
       <c r="L79" t="n">
-        <v>146.25</v>
+        <v>249.14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:43:30</t>
+          <t>08:02:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="F80" t="n">
-        <v>12.43</v>
+        <v>11.65</v>
       </c>
       <c r="G80" t="n">
-        <v>186.5</v>
+        <v>191.7</v>
       </c>
       <c r="H80" t="n">
-        <v>77.8</v>
+        <v>84.3</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>209.82</v>
+        <v>275.62</v>
       </c>
       <c r="K80" t="n">
-        <v>-197.69</v>
+        <v>-214.72</v>
       </c>
       <c r="L80" t="n">
-        <v>288.28</v>
+        <v>349.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:45:19</t>
+          <t>08:03:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.58</v>
+        <v>4.53</v>
       </c>
       <c r="F81" t="n">
-        <v>12.42</v>
+        <v>11.85</v>
       </c>
       <c r="G81" t="n">
-        <v>187.9</v>
+        <v>183.2</v>
       </c>
       <c r="H81" t="n">
-        <v>81.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>123.64</v>
+        <v>28.19</v>
       </c>
       <c r="K81" t="n">
-        <v>-116.09</v>
+        <v>113.88</v>
       </c>
       <c r="L81" t="n">
-        <v>169.6</v>
+        <v>117.32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:46:16</t>
+          <t>08:05:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.41</v>
+        <v>3.97</v>
       </c>
       <c r="F82" t="n">
-        <v>12.28</v>
+        <v>12.63</v>
       </c>
       <c r="G82" t="n">
-        <v>196.3</v>
+        <v>179.9</v>
       </c>
       <c r="H82" t="n">
-        <v>78.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-181.5</v>
+        <v>51.65</v>
       </c>
       <c r="K82" t="n">
-        <v>-60.87</v>
+        <v>-125.23</v>
       </c>
       <c r="L82" t="n">
-        <v>191.43</v>
+        <v>135.47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:52:05</t>
+          <t>08:10:21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.64</v>
+        <v>4.85</v>
       </c>
       <c r="F83" t="n">
-        <v>12.23</v>
+        <v>11.53</v>
       </c>
       <c r="G83" t="n">
-        <v>184</v>
+        <v>188.8</v>
       </c>
       <c r="H83" t="n">
-        <v>78.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-735.39</v>
+        <v>-224.1</v>
       </c>
       <c r="K83" t="n">
-        <v>288.65</v>
+        <v>-401.66</v>
       </c>
       <c r="L83" t="n">
-        <v>790.02</v>
+        <v>459.95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:54:15</t>
+          <t>08:11:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.74</v>
+        <v>3.73</v>
       </c>
       <c r="F84" t="n">
-        <v>12.84</v>
+        <v>12.25</v>
       </c>
       <c r="G84" t="n">
-        <v>187.9</v>
+        <v>181.4</v>
       </c>
       <c r="H84" t="n">
-        <v>85.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>535.1799999999999</v>
+        <v>169.38</v>
       </c>
       <c r="K84" t="n">
-        <v>177.41</v>
+        <v>-302.67</v>
       </c>
       <c r="L84" t="n">
-        <v>563.8200000000001</v>
+        <v>346.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:55:17</t>
+          <t>08:12:49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.93</v>
+        <v>4.77</v>
       </c>
       <c r="F85" t="n">
-        <v>11.99</v>
+        <v>12.48</v>
       </c>
       <c r="G85" t="n">
-        <v>209.1</v>
+        <v>181.1</v>
       </c>
       <c r="H85" t="n">
-        <v>79.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-124.24</v>
+        <v>234.84</v>
       </c>
       <c r="K85" t="n">
-        <v>313.65</v>
+        <v>-684.29</v>
       </c>
       <c r="L85" t="n">
-        <v>337.36</v>
+        <v>723.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:58:42</t>
+          <t>08:17:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="F86" t="n">
-        <v>12.31</v>
+        <v>12.7</v>
       </c>
       <c r="G86" t="n">
-        <v>193.3</v>
+        <v>187.7</v>
       </c>
       <c r="H86" t="n">
-        <v>73.7</v>
+        <v>84.8</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-230.06</v>
+        <v>-80.87</v>
       </c>
       <c r="K86" t="n">
-        <v>-106.63</v>
+        <v>299.04</v>
       </c>
       <c r="L86" t="n">
-        <v>253.57</v>
+        <v>309.79</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:00:19</t>
+          <t>08:19:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="F87" t="n">
-        <v>12.03</v>
+        <v>11.7</v>
       </c>
       <c r="G87" t="n">
-        <v>204.4</v>
+        <v>199.2</v>
       </c>
       <c r="H87" t="n">
         <v>76.3</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-77.14</v>
+        <v>308.9</v>
       </c>
       <c r="K87" t="n">
-        <v>-268.86</v>
+        <v>-455.83</v>
       </c>
       <c r="L87" t="n">
-        <v>279.71</v>
+        <v>550.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:02:28</t>
+          <t>08:20:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.23</v>
+        <v>3.42</v>
       </c>
       <c r="F88" t="n">
-        <v>12.63</v>
+        <v>11.88</v>
       </c>
       <c r="G88" t="n">
-        <v>187.1</v>
+        <v>181.2</v>
       </c>
       <c r="H88" t="n">
-        <v>79.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>732.4299999999999</v>
+        <v>446.89</v>
       </c>
       <c r="K88" t="n">
-        <v>70.09999999999999</v>
+        <v>-151.73</v>
       </c>
       <c r="L88" t="n">
-        <v>735.78</v>
+        <v>471.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>84.27</v>
+        <v>112.93</v>
       </c>
       <c r="K14" t="n">
-        <v>-101.78</v>
+        <v>-136.41</v>
       </c>
       <c r="L14" t="n">
-        <v>132.14</v>
+        <v>177.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.83</v>
+        <v>-49.79</v>
       </c>
       <c r="K15" t="n">
-        <v>-325.96</v>
+        <v>-285.54</v>
       </c>
       <c r="L15" t="n">
-        <v>330.87</v>
+        <v>289.85</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-67.5</v>
+        <v>-90.97</v>
       </c>
       <c r="K16" t="n">
-        <v>-37.61</v>
+        <v>-50.68</v>
       </c>
       <c r="L16" t="n">
-        <v>77.27</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>213.27</v>
+        <v>218.43</v>
       </c>
       <c r="K17" t="n">
-        <v>164.37</v>
+        <v>168.34</v>
       </c>
       <c r="L17" t="n">
-        <v>269.26</v>
+        <v>275.77</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>125.68</v>
+        <v>146.71</v>
       </c>
       <c r="K18" t="n">
-        <v>-229.61</v>
+        <v>-268.03</v>
       </c>
       <c r="L18" t="n">
-        <v>261.76</v>
+        <v>305.55</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>105.84</v>
+        <v>94.53</v>
       </c>
       <c r="K19" t="n">
-        <v>-437.32</v>
+        <v>-390.58</v>
       </c>
       <c r="L19" t="n">
-        <v>449.95</v>
+        <v>401.86</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-404.86</v>
+        <v>-412.82</v>
       </c>
       <c r="K20" t="n">
-        <v>-98.89</v>
+        <v>-100.83</v>
       </c>
       <c r="L20" t="n">
-        <v>416.76</v>
+        <v>424.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-214.66</v>
+        <v>-273.84</v>
       </c>
       <c r="K21" t="n">
-        <v>-81</v>
+        <v>-103.33</v>
       </c>
       <c r="L21" t="n">
-        <v>229.44</v>
+        <v>292.69</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-48.6</v>
+        <v>-127.73</v>
       </c>
       <c r="K22" t="n">
-        <v>25.35</v>
+        <v>66.63</v>
       </c>
       <c r="L22" t="n">
-        <v>54.82</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-84.19</v>
+        <v>-133.02</v>
       </c>
       <c r="K23" t="n">
-        <v>276.74</v>
+        <v>437.27</v>
       </c>
       <c r="L23" t="n">
-        <v>289.27</v>
+        <v>457.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-60.34</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-763.1</v>
+        <v>-827.15</v>
       </c>
       <c r="L24" t="n">
-        <v>765.49</v>
+        <v>829.74</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>355.03</v>
+        <v>434.74</v>
       </c>
       <c r="K25" t="n">
-        <v>-302.48</v>
+        <v>-370.4</v>
       </c>
       <c r="L25" t="n">
-        <v>466.42</v>
+        <v>571.14</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>300.51</v>
+        <v>518.95</v>
       </c>
       <c r="K26" t="n">
-        <v>71.83</v>
+        <v>124.04</v>
       </c>
       <c r="L26" t="n">
-        <v>308.97</v>
+        <v>533.5700000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-605.28</v>
+        <v>-766.12</v>
       </c>
       <c r="K27" t="n">
-        <v>-32.82</v>
+        <v>-41.54</v>
       </c>
       <c r="L27" t="n">
-        <v>606.17</v>
+        <v>767.25</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-167.13</v>
+        <v>-369.26</v>
       </c>
       <c r="K28" t="n">
-        <v>108.8</v>
+        <v>240.39</v>
       </c>
       <c r="L28" t="n">
-        <v>199.42</v>
+        <v>440.61</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.98</v>
+        <v>-33.98</v>
       </c>
       <c r="K29" t="n">
-        <v>152.92</v>
+        <v>167.69</v>
       </c>
       <c r="L29" t="n">
-        <v>156.03</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>9.59</v>
+        <v>9.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-393.17</v>
+        <v>-371.81</v>
       </c>
       <c r="L30" t="n">
-        <v>393.29</v>
+        <v>371.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-84.67</v>
+        <v>-76.98</v>
       </c>
       <c r="K31" t="n">
-        <v>244.34</v>
+        <v>222.15</v>
       </c>
       <c r="L31" t="n">
-        <v>258.6</v>
+        <v>235.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>183.73</v>
+        <v>204.79</v>
       </c>
       <c r="K32" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="L32" t="n">
-        <v>183.75</v>
+        <v>204.81</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>248.44</v>
+        <v>221.95</v>
       </c>
       <c r="K33" t="n">
-        <v>249.18</v>
+        <v>222.61</v>
       </c>
       <c r="L33" t="n">
-        <v>351.87</v>
+        <v>314.36</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>78.98</v>
+        <v>106.54</v>
       </c>
       <c r="K34" t="n">
-        <v>86.2</v>
+        <v>116.28</v>
       </c>
       <c r="L34" t="n">
-        <v>116.92</v>
+        <v>157.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>74.33</v>
+        <v>124.96</v>
       </c>
       <c r="K35" t="n">
-        <v>173.03</v>
+        <v>290.89</v>
       </c>
       <c r="L35" t="n">
-        <v>188.32</v>
+        <v>316.59</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>103.92</v>
+        <v>138.91</v>
       </c>
       <c r="K36" t="n">
-        <v>224.32</v>
+        <v>299.83</v>
       </c>
       <c r="L36" t="n">
-        <v>247.23</v>
+        <v>330.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>238.34</v>
+        <v>246.79</v>
       </c>
       <c r="K37" t="n">
-        <v>211.89</v>
+        <v>219.4</v>
       </c>
       <c r="L37" t="n">
-        <v>318.92</v>
+        <v>330.21</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-185.68</v>
+        <v>-241.88</v>
       </c>
       <c r="K38" t="n">
-        <v>415.28</v>
+        <v>540.99</v>
       </c>
       <c r="L38" t="n">
-        <v>454.9</v>
+        <v>592.6</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-20.45</v>
+        <v>-26.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-471.97</v>
+        <v>-605.08</v>
       </c>
       <c r="L39" t="n">
-        <v>472.41</v>
+        <v>605.65</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-211.48</v>
+        <v>-367.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-105.34</v>
+        <v>-183.29</v>
       </c>
       <c r="L40" t="n">
-        <v>236.27</v>
+        <v>411.07</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>535.47</v>
+        <v>616.6799999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>652.28</v>
+        <v>751.21</v>
       </c>
       <c r="L41" t="n">
-        <v>843.91</v>
+        <v>971.91</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>1247.81</v>
+        <v>1410.52</v>
       </c>
       <c r="K42" t="n">
-        <v>49.93</v>
+        <v>56.45</v>
       </c>
       <c r="L42" t="n">
-        <v>1248.81</v>
+        <v>1411.65</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-211.28</v>
+        <v>-354.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-211.76</v>
+        <v>-354.99</v>
       </c>
       <c r="L43" t="n">
-        <v>299.13</v>
+        <v>501.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>90.03</v>
+        <v>135.34</v>
       </c>
       <c r="K44" t="n">
-        <v>139.35</v>
+        <v>209.49</v>
       </c>
       <c r="L44" t="n">
-        <v>165.9</v>
+        <v>249.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-64.39</v>
+        <v>-87.18000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-61.42</v>
+        <v>-83.16</v>
       </c>
       <c r="L45" t="n">
-        <v>88.98</v>
+        <v>120.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>145.61</v>
+        <v>140.68</v>
       </c>
       <c r="K46" t="n">
-        <v>228.24</v>
+        <v>220.51</v>
       </c>
       <c r="L46" t="n">
-        <v>270.73</v>
+        <v>261.56</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>122.02</v>
+        <v>187.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.71</v>
+        <v>-53.37</v>
       </c>
       <c r="L47" t="n">
-        <v>126.85</v>
+        <v>195.07</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.45</v>
+        <v>-163.42</v>
       </c>
       <c r="K48" t="n">
-        <v>35.84</v>
+        <v>49.03</v>
       </c>
       <c r="L48" t="n">
-        <v>124.71</v>
+        <v>170.62</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-141.51</v>
+        <v>-218.11</v>
       </c>
       <c r="K49" t="n">
-        <v>0.66</v>
+        <v>1.01</v>
       </c>
       <c r="L49" t="n">
-        <v>141.52</v>
+        <v>218.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-364.15</v>
+        <v>-438.87</v>
       </c>
       <c r="K50" t="n">
-        <v>-120.39</v>
+        <v>-145.09</v>
       </c>
       <c r="L50" t="n">
-        <v>383.54</v>
+        <v>462.24</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-88.51000000000001</v>
+        <v>-144.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-56.23</v>
+        <v>-91.94</v>
       </c>
       <c r="L51" t="n">
-        <v>104.86</v>
+        <v>171.44</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-310.56</v>
+        <v>-358.29</v>
       </c>
       <c r="K52" t="n">
-        <v>-124.12</v>
+        <v>-143.19</v>
       </c>
       <c r="L52" t="n">
-        <v>334.45</v>
+        <v>385.84</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-117.23</v>
+        <v>-139.04</v>
       </c>
       <c r="K53" t="n">
-        <v>587.97</v>
+        <v>697.38</v>
       </c>
       <c r="L53" t="n">
-        <v>599.54</v>
+        <v>711.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-79.70999999999999</v>
+        <v>-105.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-487.31</v>
+        <v>-643.79</v>
       </c>
       <c r="L54" t="n">
-        <v>493.78</v>
+        <v>652.34</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-473.97</v>
+        <v>-616.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-284.37</v>
+        <v>-369.76</v>
       </c>
       <c r="L55" t="n">
-        <v>552.73</v>
+        <v>718.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>155.11</v>
+        <v>304.85</v>
       </c>
       <c r="K56" t="n">
-        <v>-246.13</v>
+        <v>-483.73</v>
       </c>
       <c r="L56" t="n">
-        <v>290.93</v>
+        <v>571.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-241.99</v>
+        <v>-321.96</v>
       </c>
       <c r="K57" t="n">
-        <v>-531.2</v>
+        <v>-706.73</v>
       </c>
       <c r="L57" t="n">
-        <v>583.72</v>
+        <v>776.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>32.78</v>
+        <v>58.72</v>
       </c>
       <c r="K58" t="n">
-        <v>-306.02</v>
+        <v>-548.12</v>
       </c>
       <c r="L58" t="n">
-        <v>307.77</v>
+        <v>551.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>109.26</v>
+        <v>130.1</v>
       </c>
       <c r="K59" t="n">
-        <v>136.37</v>
+        <v>162.38</v>
       </c>
       <c r="L59" t="n">
-        <v>174.74</v>
+        <v>208.07</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>229.55</v>
+        <v>213.74</v>
       </c>
       <c r="K60" t="n">
-        <v>227.73</v>
+        <v>212.05</v>
       </c>
       <c r="L60" t="n">
-        <v>323.34</v>
+        <v>301.08</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>45.55</v>
+        <v>65.78</v>
       </c>
       <c r="K61" t="n">
-        <v>62.17</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>77.06999999999999</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-58.03</v>
+        <v>-95.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-78.77</v>
+        <v>-129.07</v>
       </c>
       <c r="L62" t="n">
-        <v>97.84</v>
+        <v>160.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>10.79</v>
+        <v>19.16</v>
       </c>
       <c r="K63" t="n">
-        <v>-67.28</v>
+        <v>-119.49</v>
       </c>
       <c r="L63" t="n">
-        <v>68.14</v>
+        <v>121.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-62.19</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>177.51</v>
+        <v>212.92</v>
       </c>
       <c r="L64" t="n">
-        <v>188.09</v>
+        <v>225.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>320.09</v>
+        <v>427.32</v>
       </c>
       <c r="K65" t="n">
-        <v>-158.02</v>
+        <v>-210.95</v>
       </c>
       <c r="L65" t="n">
-        <v>356.97</v>
+        <v>476.55</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-373.28</v>
+        <v>-397.91</v>
       </c>
       <c r="K66" t="n">
-        <v>-547.17</v>
+        <v>-583.27</v>
       </c>
       <c r="L66" t="n">
-        <v>662.37</v>
+        <v>706.0700000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>394.9</v>
+        <v>453.29</v>
       </c>
       <c r="K67" t="n">
-        <v>160.9</v>
+        <v>184.7</v>
       </c>
       <c r="L67" t="n">
-        <v>426.42</v>
+        <v>489.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-58.47</v>
+        <v>-77.02</v>
       </c>
       <c r="K68" t="n">
-        <v>-394.34</v>
+        <v>-519.46</v>
       </c>
       <c r="L68" t="n">
-        <v>398.65</v>
+        <v>525.14</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-228.94</v>
+        <v>-310.67</v>
       </c>
       <c r="K69" t="n">
-        <v>386.37</v>
+        <v>524.3</v>
       </c>
       <c r="L69" t="n">
-        <v>449.11</v>
+        <v>609.4299999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>456.68</v>
+        <v>640.02</v>
       </c>
       <c r="K70" t="n">
-        <v>82.09999999999999</v>
+        <v>115.06</v>
       </c>
       <c r="L70" t="n">
-        <v>464</v>
+        <v>650.28</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>189.46</v>
+        <v>342.22</v>
       </c>
       <c r="K71" t="n">
-        <v>149.39</v>
+        <v>269.83</v>
       </c>
       <c r="L71" t="n">
-        <v>241.27</v>
+        <v>435.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-123.51</v>
+        <v>-137.54</v>
       </c>
       <c r="K72" t="n">
-        <v>782.24</v>
+        <v>871.08</v>
       </c>
       <c r="L72" t="n">
-        <v>791.9299999999999</v>
+        <v>881.87</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-223.63</v>
+        <v>-388.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-33.78</v>
+        <v>-58.74</v>
       </c>
       <c r="L73" t="n">
-        <v>226.17</v>
+        <v>393.26</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-223.26</v>
+        <v>-230.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-136.24</v>
+        <v>-140.41</v>
       </c>
       <c r="L74" t="n">
-        <v>261.55</v>
+        <v>269.54</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>76.05</v>
+        <v>140.39</v>
       </c>
       <c r="K75" t="n">
-        <v>59.67</v>
+        <v>110.16</v>
       </c>
       <c r="L75" t="n">
-        <v>96.66</v>
+        <v>178.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-130.4</v>
+        <v>-144.82</v>
       </c>
       <c r="K76" t="n">
-        <v>143.9</v>
+        <v>159.81</v>
       </c>
       <c r="L76" t="n">
-        <v>194.2</v>
+        <v>215.67</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>86.45</v>
+        <v>106.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-184.01</v>
+        <v>-226.19</v>
       </c>
       <c r="L77" t="n">
-        <v>203.31</v>
+        <v>249.91</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-193</v>
+        <v>-217.34</v>
       </c>
       <c r="K78" t="n">
-        <v>-115.24</v>
+        <v>-129.78</v>
       </c>
       <c r="L78" t="n">
-        <v>224.79</v>
+        <v>253.14</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-114.78</v>
+        <v>-124.14</v>
       </c>
       <c r="K79" t="n">
-        <v>221.13</v>
+        <v>239.15</v>
       </c>
       <c r="L79" t="n">
-        <v>249.14</v>
+        <v>269.44</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>275.62</v>
+        <v>351.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-214.72</v>
+        <v>-273.49</v>
       </c>
       <c r="L80" t="n">
-        <v>349.39</v>
+        <v>445.02</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>28.19</v>
+        <v>57.99</v>
       </c>
       <c r="K81" t="n">
-        <v>113.88</v>
+        <v>234.23</v>
       </c>
       <c r="L81" t="n">
-        <v>117.32</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>51.65</v>
+        <v>98.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-125.23</v>
+        <v>-239.71</v>
       </c>
       <c r="L82" t="n">
-        <v>135.47</v>
+        <v>259.3</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-224.1</v>
+        <v>-335.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-401.66</v>
+        <v>-600.51</v>
       </c>
       <c r="L83" t="n">
-        <v>459.95</v>
+        <v>687.66</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>169.38</v>
+        <v>239.83</v>
       </c>
       <c r="K84" t="n">
-        <v>-302.67</v>
+        <v>-428.56</v>
       </c>
       <c r="L84" t="n">
-        <v>346.84</v>
+        <v>491.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>234.84</v>
+        <v>286.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-684.29</v>
+        <v>-834.7</v>
       </c>
       <c r="L85" t="n">
-        <v>723.47</v>
+        <v>882.49</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-80.87</v>
+        <v>-157.76</v>
       </c>
       <c r="K86" t="n">
-        <v>299.04</v>
+        <v>583.42</v>
       </c>
       <c r="L86" t="n">
-        <v>309.79</v>
+        <v>604.38</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>308.9</v>
+        <v>493.77</v>
       </c>
       <c r="K87" t="n">
-        <v>-455.83</v>
+        <v>-728.63</v>
       </c>
       <c r="L87" t="n">
-        <v>550.63</v>
+        <v>880.17</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>446.89</v>
+        <v>589.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-151.73</v>
+        <v>-200.05</v>
       </c>
       <c r="L88" t="n">
-        <v>471.94</v>
+        <v>622.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>112.93</v>
+        <v>78.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-136.41</v>
+        <v>-95.15000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>177.09</v>
+        <v>123.52</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-49.79</v>
+        <v>-39.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-285.54</v>
+        <v>-227.14</v>
       </c>
       <c r="L15" t="n">
-        <v>289.85</v>
+        <v>230.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-90.97</v>
+        <v>-74.61</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.68</v>
+        <v>-41.56</v>
       </c>
       <c r="L16" t="n">
-        <v>104.14</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>218.43</v>
+        <v>163.81</v>
       </c>
       <c r="K17" t="n">
-        <v>168.34</v>
+        <v>126.25</v>
       </c>
       <c r="L17" t="n">
-        <v>275.77</v>
+        <v>206.82</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>146.71</v>
+        <v>100.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-268.03</v>
+        <v>-184.49</v>
       </c>
       <c r="L18" t="n">
-        <v>305.55</v>
+        <v>210.32</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>94.53</v>
+        <v>67.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-390.58</v>
+        <v>-279.85</v>
       </c>
       <c r="L19" t="n">
-        <v>401.86</v>
+        <v>287.93</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-412.82</v>
+        <v>-274.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-100.83</v>
+        <v>-67.08</v>
       </c>
       <c r="L20" t="n">
-        <v>424.95</v>
+        <v>282.7</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-273.84</v>
+        <v>-168.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-103.33</v>
+        <v>-63.55</v>
       </c>
       <c r="L21" t="n">
-        <v>292.69</v>
+        <v>180.02</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-127.73</v>
+        <v>-86.45999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>66.63</v>
+        <v>45.1</v>
       </c>
       <c r="L22" t="n">
-        <v>144.06</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-133.02</v>
+        <v>-73.48999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>437.27</v>
+        <v>241.58</v>
       </c>
       <c r="L23" t="n">
-        <v>457.05</v>
+        <v>252.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-65.40000000000001</v>
+        <v>-33.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-827.15</v>
+        <v>-427.22</v>
       </c>
       <c r="L24" t="n">
-        <v>829.74</v>
+        <v>428.55</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>434.74</v>
+        <v>228.54</v>
       </c>
       <c r="K25" t="n">
-        <v>-370.4</v>
+        <v>-194.72</v>
       </c>
       <c r="L25" t="n">
-        <v>571.14</v>
+        <v>300.24</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>518.95</v>
+        <v>260.19</v>
       </c>
       <c r="K26" t="n">
-        <v>124.04</v>
+        <v>62.19</v>
       </c>
       <c r="L26" t="n">
-        <v>533.5700000000001</v>
+        <v>267.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-766.12</v>
+        <v>-379.61</v>
       </c>
       <c r="K27" t="n">
-        <v>-41.54</v>
+        <v>-20.58</v>
       </c>
       <c r="L27" t="n">
-        <v>767.25</v>
+        <v>380.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-369.26</v>
+        <v>-172.97</v>
       </c>
       <c r="K28" t="n">
-        <v>240.39</v>
+        <v>112.61</v>
       </c>
       <c r="L28" t="n">
-        <v>440.61</v>
+        <v>206.4</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.98</v>
+        <v>-23.75</v>
       </c>
       <c r="K29" t="n">
-        <v>167.69</v>
+        <v>117.19</v>
       </c>
       <c r="L29" t="n">
-        <v>171.1</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>9.07</v>
+        <v>6.46</v>
       </c>
       <c r="K30" t="n">
-        <v>-371.81</v>
+        <v>-264.75</v>
       </c>
       <c r="L30" t="n">
-        <v>371.92</v>
+        <v>264.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-76.98</v>
+        <v>-60.19</v>
       </c>
       <c r="K31" t="n">
-        <v>222.15</v>
+        <v>173.7</v>
       </c>
       <c r="L31" t="n">
-        <v>235.11</v>
+        <v>183.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>204.79</v>
+        <v>144.76</v>
       </c>
       <c r="K32" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="L32" t="n">
-        <v>204.81</v>
+        <v>144.76</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>221.95</v>
+        <v>150.19</v>
       </c>
       <c r="K33" t="n">
-        <v>222.61</v>
+        <v>150.64</v>
       </c>
       <c r="L33" t="n">
-        <v>314.36</v>
+        <v>212.72</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>106.54</v>
+        <v>78.87</v>
       </c>
       <c r="K34" t="n">
-        <v>116.28</v>
+        <v>86.08</v>
       </c>
       <c r="L34" t="n">
-        <v>157.71</v>
+        <v>116.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>124.96</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>290.89</v>
+        <v>159.8</v>
       </c>
       <c r="L35" t="n">
-        <v>316.59</v>
+        <v>173.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>138.91</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>299.83</v>
+        <v>180.22</v>
       </c>
       <c r="L36" t="n">
-        <v>330.45</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>246.79</v>
+        <v>167.69</v>
       </c>
       <c r="K37" t="n">
-        <v>219.4</v>
+        <v>149.08</v>
       </c>
       <c r="L37" t="n">
-        <v>330.21</v>
+        <v>224.38</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-241.88</v>
+        <v>-125.02</v>
       </c>
       <c r="K38" t="n">
-        <v>540.99</v>
+        <v>279.63</v>
       </c>
       <c r="L38" t="n">
-        <v>592.6</v>
+        <v>306.3</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-26.21</v>
+        <v>-14.54</v>
       </c>
       <c r="K39" t="n">
-        <v>-605.08</v>
+        <v>-335.64</v>
       </c>
       <c r="L39" t="n">
-        <v>605.65</v>
+        <v>335.95</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-367.95</v>
+        <v>-185.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-183.29</v>
+        <v>-92.28</v>
       </c>
       <c r="L40" t="n">
-        <v>411.07</v>
+        <v>206.96</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>616.6799999999999</v>
+        <v>328.33</v>
       </c>
       <c r="K41" t="n">
-        <v>751.21</v>
+        <v>399.96</v>
       </c>
       <c r="L41" t="n">
-        <v>971.91</v>
+        <v>517.46</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>1410.52</v>
+        <v>668.3099999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>56.45</v>
+        <v>26.74</v>
       </c>
       <c r="L42" t="n">
-        <v>1411.65</v>
+        <v>668.84</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-354.2</v>
+        <v>-175.51</v>
       </c>
       <c r="K43" t="n">
-        <v>-354.99</v>
+        <v>-175.9</v>
       </c>
       <c r="L43" t="n">
-        <v>501.48</v>
+        <v>248.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>135.34</v>
+        <v>85.63</v>
       </c>
       <c r="K44" t="n">
-        <v>209.49</v>
+        <v>132.53</v>
       </c>
       <c r="L44" t="n">
-        <v>249.41</v>
+        <v>157.79</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-87.18000000000001</v>
+        <v>-67.83</v>
       </c>
       <c r="K45" t="n">
-        <v>-83.16</v>
+        <v>-64.7</v>
       </c>
       <c r="L45" t="n">
-        <v>120.48</v>
+        <v>93.73999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>140.68</v>
+        <v>102.36</v>
       </c>
       <c r="K46" t="n">
-        <v>220.51</v>
+        <v>160.45</v>
       </c>
       <c r="L46" t="n">
-        <v>261.56</v>
+        <v>190.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>187.63</v>
+        <v>129.31</v>
       </c>
       <c r="K47" t="n">
-        <v>-53.37</v>
+        <v>-36.78</v>
       </c>
       <c r="L47" t="n">
-        <v>195.07</v>
+        <v>134.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-163.42</v>
+        <v>-122.22</v>
       </c>
       <c r="K48" t="n">
-        <v>49.03</v>
+        <v>36.67</v>
       </c>
       <c r="L48" t="n">
-        <v>170.62</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-218.11</v>
+        <v>-135.94</v>
       </c>
       <c r="K49" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="L49" t="n">
-        <v>218.12</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-438.87</v>
+        <v>-253.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-145.09</v>
+        <v>-83.8</v>
       </c>
       <c r="L50" t="n">
-        <v>462.24</v>
+        <v>266.96</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-144.71</v>
+        <v>-98.44</v>
       </c>
       <c r="K51" t="n">
-        <v>-91.94</v>
+        <v>-62.54</v>
       </c>
       <c r="L51" t="n">
-        <v>171.44</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-358.29</v>
+        <v>-227.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-143.19</v>
+        <v>-90.90000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>385.84</v>
+        <v>244.93</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-139.04</v>
+        <v>-70.61</v>
       </c>
       <c r="K53" t="n">
-        <v>697.38</v>
+        <v>354.12</v>
       </c>
       <c r="L53" t="n">
-        <v>711.1</v>
+        <v>361.09</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-105.3</v>
+        <v>-54.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-643.79</v>
+        <v>-335.15</v>
       </c>
       <c r="L54" t="n">
-        <v>652.34</v>
+        <v>339.6</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-616.28</v>
+        <v>-305.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-369.76</v>
+        <v>-183.54</v>
       </c>
       <c r="L55" t="n">
-        <v>718.7</v>
+        <v>356.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>304.85</v>
+        <v>136.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-483.73</v>
+        <v>-216</v>
       </c>
       <c r="L56" t="n">
-        <v>571.78</v>
+        <v>255.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-321.96</v>
+        <v>-157.19</v>
       </c>
       <c r="K57" t="n">
-        <v>-706.73</v>
+        <v>-345.05</v>
       </c>
       <c r="L57" t="n">
-        <v>776.61</v>
+        <v>379.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>58.72</v>
+        <v>29.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-548.12</v>
+        <v>-271.1</v>
       </c>
       <c r="L58" t="n">
-        <v>551.26</v>
+        <v>272.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>130.1</v>
+        <v>88.69</v>
       </c>
       <c r="K59" t="n">
-        <v>162.38</v>
+        <v>110.7</v>
       </c>
       <c r="L59" t="n">
-        <v>208.07</v>
+        <v>141.85</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>213.74</v>
+        <v>162.54</v>
       </c>
       <c r="K60" t="n">
-        <v>212.05</v>
+        <v>161.25</v>
       </c>
       <c r="L60" t="n">
-        <v>301.08</v>
+        <v>228.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>65.78</v>
+        <v>51.31</v>
       </c>
       <c r="K61" t="n">
-        <v>89.79000000000001</v>
+        <v>70.03</v>
       </c>
       <c r="L61" t="n">
-        <v>111.31</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.08</v>
+        <v>-64.98999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-129.07</v>
+        <v>-88.23</v>
       </c>
       <c r="L62" t="n">
-        <v>160.31</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>19.16</v>
+        <v>14.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.49</v>
+        <v>-90.64</v>
       </c>
       <c r="L63" t="n">
-        <v>121.02</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-74.59999999999999</v>
+        <v>-51.25</v>
       </c>
       <c r="K64" t="n">
-        <v>212.92</v>
+        <v>146.27</v>
       </c>
       <c r="L64" t="n">
-        <v>225.61</v>
+        <v>154.98</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>427.32</v>
+        <v>231.67</v>
       </c>
       <c r="K65" t="n">
-        <v>-210.95</v>
+        <v>-114.37</v>
       </c>
       <c r="L65" t="n">
-        <v>476.55</v>
+        <v>258.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-397.91</v>
+        <v>-228.81</v>
       </c>
       <c r="K66" t="n">
-        <v>-583.27</v>
+        <v>-335.39</v>
       </c>
       <c r="L66" t="n">
-        <v>706.0700000000001</v>
+        <v>406.01</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>453.29</v>
+        <v>275.13</v>
       </c>
       <c r="K67" t="n">
-        <v>184.7</v>
+        <v>112.1</v>
       </c>
       <c r="L67" t="n">
-        <v>489.48</v>
+        <v>297.1</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-77.02</v>
+        <v>-42.96</v>
       </c>
       <c r="K68" t="n">
-        <v>-519.46</v>
+        <v>-289.71</v>
       </c>
       <c r="L68" t="n">
-        <v>525.14</v>
+        <v>292.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-310.67</v>
+        <v>-165.8</v>
       </c>
       <c r="K69" t="n">
-        <v>524.3</v>
+        <v>279.81</v>
       </c>
       <c r="L69" t="n">
-        <v>609.4299999999999</v>
+        <v>325.24</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>640.02</v>
+        <v>315.82</v>
       </c>
       <c r="K70" t="n">
-        <v>115.06</v>
+        <v>56.78</v>
       </c>
       <c r="L70" t="n">
-        <v>650.28</v>
+        <v>320.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>342.22</v>
+        <v>163.18</v>
       </c>
       <c r="K71" t="n">
-        <v>269.83</v>
+        <v>128.66</v>
       </c>
       <c r="L71" t="n">
-        <v>435.8</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-137.54</v>
+        <v>-74.33</v>
       </c>
       <c r="K72" t="n">
-        <v>871.08</v>
+        <v>470.75</v>
       </c>
       <c r="L72" t="n">
-        <v>881.87</v>
+        <v>476.59</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-388.85</v>
+        <v>-206.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-58.74</v>
+        <v>-31.16</v>
       </c>
       <c r="L73" t="n">
-        <v>393.26</v>
+        <v>208.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-230.08</v>
+        <v>-160.91</v>
       </c>
       <c r="K74" t="n">
-        <v>-140.41</v>
+        <v>-98.2</v>
       </c>
       <c r="L74" t="n">
-        <v>269.54</v>
+        <v>188.51</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>140.39</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>110.16</v>
+        <v>70.59</v>
       </c>
       <c r="L75" t="n">
-        <v>178.45</v>
+        <v>114.35</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-144.82</v>
+        <v>-101.73</v>
       </c>
       <c r="K76" t="n">
-        <v>159.81</v>
+        <v>112.26</v>
       </c>
       <c r="L76" t="n">
-        <v>215.67</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>106.27</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-226.19</v>
+        <v>-144</v>
       </c>
       <c r="L77" t="n">
-        <v>249.91</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-217.34</v>
+        <v>-156.62</v>
       </c>
       <c r="K78" t="n">
-        <v>-129.78</v>
+        <v>-93.52</v>
       </c>
       <c r="L78" t="n">
-        <v>253.14</v>
+        <v>182.41</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-124.14</v>
+        <v>-85.52</v>
       </c>
       <c r="K79" t="n">
-        <v>239.15</v>
+        <v>164.76</v>
       </c>
       <c r="L79" t="n">
-        <v>269.44</v>
+        <v>185.63</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>351.06</v>
+        <v>193.45</v>
       </c>
       <c r="K80" t="n">
-        <v>-273.49</v>
+        <v>-150.71</v>
       </c>
       <c r="L80" t="n">
-        <v>445.02</v>
+        <v>245.23</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>57.99</v>
+        <v>34.95</v>
       </c>
       <c r="K81" t="n">
-        <v>234.23</v>
+        <v>141.18</v>
       </c>
       <c r="L81" t="n">
-        <v>241.3</v>
+        <v>145.45</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>98.87</v>
+        <v>55.6</v>
       </c>
       <c r="K82" t="n">
-        <v>-239.71</v>
+        <v>-134.8</v>
       </c>
       <c r="L82" t="n">
-        <v>259.3</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-335.05</v>
+        <v>-166.78</v>
       </c>
       <c r="K83" t="n">
-        <v>-600.51</v>
+        <v>-298.93</v>
       </c>
       <c r="L83" t="n">
-        <v>687.66</v>
+        <v>342.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>239.83</v>
+        <v>123.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-428.56</v>
+        <v>-221.51</v>
       </c>
       <c r="L84" t="n">
-        <v>491.1</v>
+        <v>253.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>286.46</v>
+        <v>152.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-834.7</v>
+        <v>-443.03</v>
       </c>
       <c r="L85" t="n">
-        <v>882.49</v>
+        <v>468.4</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-157.76</v>
+        <v>-71.45</v>
       </c>
       <c r="K86" t="n">
-        <v>583.42</v>
+        <v>264.23</v>
       </c>
       <c r="L86" t="n">
-        <v>604.38</v>
+        <v>273.72</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>493.77</v>
+        <v>216.11</v>
       </c>
       <c r="K87" t="n">
-        <v>-728.63</v>
+        <v>-318.91</v>
       </c>
       <c r="L87" t="n">
-        <v>880.17</v>
+        <v>385.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>589.2</v>
+        <v>301.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-200.05</v>
+        <v>-102.37</v>
       </c>
       <c r="L88" t="n">
-        <v>622.23</v>
+        <v>318.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>78.77</v>
+        <v>83.44</v>
       </c>
       <c r="K14" t="n">
-        <v>-95.15000000000001</v>
+        <v>-100.79</v>
       </c>
       <c r="L14" t="n">
-        <v>123.52</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-39.6</v>
+        <v>-40.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-227.14</v>
+        <v>-235.02</v>
       </c>
       <c r="L15" t="n">
-        <v>230.57</v>
+        <v>238.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-74.61</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.56</v>
+        <v>-42.78</v>
       </c>
       <c r="L16" t="n">
-        <v>85.40000000000001</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>163.81</v>
+        <v>172.54</v>
       </c>
       <c r="K17" t="n">
-        <v>126.25</v>
+        <v>132.98</v>
       </c>
       <c r="L17" t="n">
-        <v>206.82</v>
+        <v>217.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>100.98</v>
+        <v>107.68</v>
       </c>
       <c r="K18" t="n">
-        <v>-184.49</v>
+        <v>-196.73</v>
       </c>
       <c r="L18" t="n">
-        <v>210.32</v>
+        <v>224.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>67.73</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-279.85</v>
+        <v>-299.54</v>
       </c>
       <c r="L19" t="n">
-        <v>287.93</v>
+        <v>308.18</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-274.63</v>
+        <v>-301.08</v>
       </c>
       <c r="K20" t="n">
-        <v>-67.08</v>
+        <v>-73.54000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>282.7</v>
+        <v>309.93</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-168.42</v>
+        <v>-186.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-63.55</v>
+        <v>-70.45999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>180.02</v>
+        <v>199.59</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-86.45999999999999</v>
+        <v>-94.19</v>
       </c>
       <c r="K22" t="n">
-        <v>45.1</v>
+        <v>49.13</v>
       </c>
       <c r="L22" t="n">
-        <v>97.51000000000001</v>
+        <v>106.23</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-73.48999999999999</v>
+        <v>-83.31999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>241.58</v>
+        <v>273.9</v>
       </c>
       <c r="L23" t="n">
-        <v>252.51</v>
+        <v>286.29</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-33.78</v>
+        <v>-38.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-427.22</v>
+        <v>-492.07</v>
       </c>
       <c r="L24" t="n">
-        <v>428.55</v>
+        <v>493.6</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>228.54</v>
+        <v>262.37</v>
       </c>
       <c r="K25" t="n">
-        <v>-194.72</v>
+        <v>-223.54</v>
       </c>
       <c r="L25" t="n">
-        <v>300.24</v>
+        <v>344.68</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>260.19</v>
+        <v>303.01</v>
       </c>
       <c r="K26" t="n">
-        <v>62.19</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>267.52</v>
+        <v>311.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-379.61</v>
+        <v>-442.15</v>
       </c>
       <c r="K27" t="n">
-        <v>-20.58</v>
+        <v>-23.97</v>
       </c>
       <c r="L27" t="n">
-        <v>380.17</v>
+        <v>442.8</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-172.97</v>
+        <v>-202.13</v>
       </c>
       <c r="K28" t="n">
-        <v>112.61</v>
+        <v>131.59</v>
       </c>
       <c r="L28" t="n">
-        <v>206.4</v>
+        <v>241.19</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.75</v>
+        <v>-24.94</v>
       </c>
       <c r="K29" t="n">
-        <v>117.19</v>
+        <v>123.06</v>
       </c>
       <c r="L29" t="n">
-        <v>119.57</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>6.46</v>
+        <v>6.88</v>
       </c>
       <c r="K30" t="n">
-        <v>-264.75</v>
+        <v>-282.2</v>
       </c>
       <c r="L30" t="n">
-        <v>264.83</v>
+        <v>282.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-60.19</v>
+        <v>-62.85</v>
       </c>
       <c r="K31" t="n">
-        <v>173.7</v>
+        <v>181.38</v>
       </c>
       <c r="L31" t="n">
-        <v>183.83</v>
+        <v>191.96</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>144.76</v>
+        <v>157.51</v>
       </c>
       <c r="K32" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="L32" t="n">
-        <v>144.76</v>
+        <v>157.52</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>150.19</v>
+        <v>164.07</v>
       </c>
       <c r="K33" t="n">
-        <v>150.64</v>
+        <v>164.56</v>
       </c>
       <c r="L33" t="n">
-        <v>212.72</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>78.87</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>86.08</v>
+        <v>91.52</v>
       </c>
       <c r="L34" t="n">
-        <v>116.75</v>
+        <v>124.12</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>68.65000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K35" t="n">
-        <v>159.8</v>
+        <v>180.47</v>
       </c>
       <c r="L35" t="n">
-        <v>173.92</v>
+        <v>196.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>83.48999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="K36" t="n">
-        <v>180.22</v>
+        <v>200.56</v>
       </c>
       <c r="L36" t="n">
-        <v>198.62</v>
+        <v>221.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>167.69</v>
+        <v>184.18</v>
       </c>
       <c r="K37" t="n">
-        <v>149.08</v>
+        <v>163.74</v>
       </c>
       <c r="L37" t="n">
-        <v>224.38</v>
+        <v>246.45</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-125.02</v>
+        <v>-144.98</v>
       </c>
       <c r="K38" t="n">
-        <v>279.63</v>
+        <v>324.27</v>
       </c>
       <c r="L38" t="n">
-        <v>306.3</v>
+        <v>355.2</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.54</v>
+        <v>-16.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-335.64</v>
+        <v>-383.07</v>
       </c>
       <c r="L39" t="n">
-        <v>335.95</v>
+        <v>383.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-185.25</v>
+        <v>-212.32</v>
       </c>
       <c r="K40" t="n">
-        <v>-92.28</v>
+        <v>-105.76</v>
       </c>
       <c r="L40" t="n">
-        <v>206.96</v>
+        <v>237.2</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>328.33</v>
+        <v>377.17</v>
       </c>
       <c r="K41" t="n">
-        <v>399.96</v>
+        <v>459.44</v>
       </c>
       <c r="L41" t="n">
-        <v>517.46</v>
+        <v>594.42</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>668.3099999999999</v>
+        <v>776.23</v>
       </c>
       <c r="K42" t="n">
-        <v>26.74</v>
+        <v>31.06</v>
       </c>
       <c r="L42" t="n">
-        <v>668.84</v>
+        <v>776.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-175.51</v>
+        <v>-201.9</v>
       </c>
       <c r="K43" t="n">
-        <v>-175.9</v>
+        <v>-202.35</v>
       </c>
       <c r="L43" t="n">
-        <v>248.48</v>
+        <v>285.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>85.63</v>
+        <v>94.09</v>
       </c>
       <c r="K44" t="n">
-        <v>132.53</v>
+        <v>145.64</v>
       </c>
       <c r="L44" t="n">
-        <v>157.79</v>
+        <v>173.39</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-67.83</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-64.7</v>
+        <v>-67.64</v>
       </c>
       <c r="L45" t="n">
-        <v>93.73999999999999</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>102.36</v>
+        <v>106.38</v>
       </c>
       <c r="K46" t="n">
-        <v>160.45</v>
+        <v>166.75</v>
       </c>
       <c r="L46" t="n">
-        <v>190.32</v>
+        <v>197.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>129.31</v>
+        <v>137.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-36.78</v>
+        <v>-39.15</v>
       </c>
       <c r="L47" t="n">
-        <v>134.44</v>
+        <v>143.09</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-122.22</v>
+        <v>-130.05</v>
       </c>
       <c r="K48" t="n">
-        <v>36.67</v>
+        <v>39.02</v>
       </c>
       <c r="L48" t="n">
-        <v>127.6</v>
+        <v>135.78</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-135.94</v>
+        <v>-148.39</v>
       </c>
       <c r="K49" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>135.94</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-253.47</v>
+        <v>-283.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.8</v>
+        <v>-93.8</v>
       </c>
       <c r="L50" t="n">
-        <v>266.96</v>
+        <v>298.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.44</v>
+        <v>-107.43</v>
       </c>
       <c r="K51" t="n">
-        <v>-62.54</v>
+        <v>-68.25</v>
       </c>
       <c r="L51" t="n">
-        <v>116.63</v>
+        <v>127.28</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-227.44</v>
+        <v>-250.62</v>
       </c>
       <c r="K52" t="n">
-        <v>-90.90000000000001</v>
+        <v>-100.16</v>
       </c>
       <c r="L52" t="n">
-        <v>244.93</v>
+        <v>269.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-70.61</v>
+        <v>-81.43000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>354.12</v>
+        <v>408.41</v>
       </c>
       <c r="L53" t="n">
-        <v>361.09</v>
+        <v>416.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-54.82</v>
+        <v>-63.96</v>
       </c>
       <c r="K54" t="n">
-        <v>-335.15</v>
+        <v>-391.04</v>
       </c>
       <c r="L54" t="n">
-        <v>339.6</v>
+        <v>396.24</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-305.91</v>
+        <v>-355.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-183.54</v>
+        <v>-213.31</v>
       </c>
       <c r="L55" t="n">
-        <v>356.75</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>136.12</v>
+        <v>162.32</v>
       </c>
       <c r="K56" t="n">
-        <v>-216</v>
+        <v>-257.56</v>
       </c>
       <c r="L56" t="n">
-        <v>255.31</v>
+        <v>304.44</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-157.19</v>
+        <v>-182.59</v>
       </c>
       <c r="K57" t="n">
-        <v>-345.05</v>
+        <v>-400.81</v>
       </c>
       <c r="L57" t="n">
-        <v>379.16</v>
+        <v>440.44</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>29.04</v>
+        <v>33.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-271.1</v>
+        <v>-316.59</v>
       </c>
       <c r="L58" t="n">
-        <v>272.65</v>
+        <v>318.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>88.69</v>
+        <v>94.08</v>
       </c>
       <c r="K59" t="n">
-        <v>110.7</v>
+        <v>117.42</v>
       </c>
       <c r="L59" t="n">
-        <v>141.85</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>162.54</v>
+        <v>172.11</v>
       </c>
       <c r="K60" t="n">
-        <v>161.25</v>
+        <v>170.75</v>
       </c>
       <c r="L60" t="n">
-        <v>228.95</v>
+        <v>242.44</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>51.31</v>
+        <v>53.53</v>
       </c>
       <c r="K61" t="n">
-        <v>70.03</v>
+        <v>73.06</v>
       </c>
       <c r="L61" t="n">
-        <v>86.81</v>
+        <v>90.56999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.98999999999999</v>
+        <v>-69.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-88.23</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>109.58</v>
+        <v>117.04</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>14.54</v>
+        <v>15.28</v>
       </c>
       <c r="K63" t="n">
-        <v>-90.64</v>
+        <v>-95.27</v>
       </c>
       <c r="L63" t="n">
-        <v>91.8</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-51.25</v>
+        <v>-55.42</v>
       </c>
       <c r="K64" t="n">
-        <v>146.27</v>
+        <v>158.19</v>
       </c>
       <c r="L64" t="n">
-        <v>154.98</v>
+        <v>167.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>231.67</v>
+        <v>262.51</v>
       </c>
       <c r="K65" t="n">
-        <v>-114.37</v>
+        <v>-129.59</v>
       </c>
       <c r="L65" t="n">
-        <v>258.36</v>
+        <v>292.75</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-228.81</v>
+        <v>-258.03</v>
       </c>
       <c r="K66" t="n">
-        <v>-335.39</v>
+        <v>-378.23</v>
       </c>
       <c r="L66" t="n">
-        <v>406.01</v>
+        <v>457.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>275.13</v>
+        <v>304.42</v>
       </c>
       <c r="K67" t="n">
-        <v>112.1</v>
+        <v>124.04</v>
       </c>
       <c r="L67" t="n">
-        <v>297.1</v>
+        <v>328.72</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-42.96</v>
+        <v>-48.71</v>
       </c>
       <c r="K68" t="n">
-        <v>-289.71</v>
+        <v>-328.54</v>
       </c>
       <c r="L68" t="n">
-        <v>292.88</v>
+        <v>332.13</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-165.8</v>
+        <v>-187.89</v>
       </c>
       <c r="K69" t="n">
-        <v>279.81</v>
+        <v>317.1</v>
       </c>
       <c r="L69" t="n">
-        <v>325.24</v>
+        <v>368.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>315.82</v>
+        <v>363.72</v>
       </c>
       <c r="K70" t="n">
-        <v>56.78</v>
+        <v>65.39</v>
       </c>
       <c r="L70" t="n">
-        <v>320.88</v>
+        <v>369.55</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>163.18</v>
+        <v>189.54</v>
       </c>
       <c r="K71" t="n">
-        <v>128.66</v>
+        <v>149.45</v>
       </c>
       <c r="L71" t="n">
-        <v>207.8</v>
+        <v>241.38</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-74.33</v>
+        <v>-84.73999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>470.75</v>
+        <v>536.6900000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>476.59</v>
+        <v>543.34</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-206.29</v>
+        <v>-238.16</v>
       </c>
       <c r="K73" t="n">
-        <v>-31.16</v>
+        <v>-35.97</v>
       </c>
       <c r="L73" t="n">
-        <v>208.63</v>
+        <v>240.86</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-160.91</v>
+        <v>-168.61</v>
       </c>
       <c r="K74" t="n">
-        <v>-98.2</v>
+        <v>-102.89</v>
       </c>
       <c r="L74" t="n">
-        <v>188.51</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>89.95999999999999</v>
+        <v>96.67</v>
       </c>
       <c r="K75" t="n">
-        <v>70.59</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>114.35</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-101.73</v>
+        <v>-107.63</v>
       </c>
       <c r="K76" t="n">
-        <v>112.26</v>
+        <v>118.77</v>
       </c>
       <c r="L76" t="n">
-        <v>151.5</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>67.65000000000001</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-144</v>
+        <v>-157.06</v>
       </c>
       <c r="L77" t="n">
-        <v>159.1</v>
+        <v>173.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-156.62</v>
+        <v>-166.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-93.52</v>
+        <v>-99.42</v>
       </c>
       <c r="L78" t="n">
-        <v>182.41</v>
+        <v>193.93</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-85.52</v>
+        <v>-92.03</v>
       </c>
       <c r="K79" t="n">
-        <v>164.76</v>
+        <v>177.3</v>
       </c>
       <c r="L79" t="n">
-        <v>185.63</v>
+        <v>199.76</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>193.45</v>
+        <v>219.93</v>
       </c>
       <c r="K80" t="n">
-        <v>-150.71</v>
+        <v>-171.34</v>
       </c>
       <c r="L80" t="n">
-        <v>245.23</v>
+        <v>278.79</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>34.95</v>
+        <v>38.53</v>
       </c>
       <c r="K81" t="n">
-        <v>141.18</v>
+        <v>155.63</v>
       </c>
       <c r="L81" t="n">
-        <v>145.45</v>
+        <v>160.32</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>55.6</v>
+        <v>62.66</v>
       </c>
       <c r="K82" t="n">
-        <v>-134.8</v>
+        <v>-151.91</v>
       </c>
       <c r="L82" t="n">
-        <v>145.82</v>
+        <v>164.32</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-166.78</v>
+        <v>-193.75</v>
       </c>
       <c r="K83" t="n">
-        <v>-298.93</v>
+        <v>-347.26</v>
       </c>
       <c r="L83" t="n">
-        <v>342.31</v>
+        <v>397.65</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>123.96</v>
+        <v>140.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-221.51</v>
+        <v>-251.58</v>
       </c>
       <c r="L84" t="n">
-        <v>253.84</v>
+        <v>288.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>152.04</v>
+        <v>174.57</v>
       </c>
       <c r="K85" t="n">
-        <v>-443.03</v>
+        <v>-508.68</v>
       </c>
       <c r="L85" t="n">
-        <v>468.4</v>
+        <v>537.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-71.45</v>
+        <v>-85.28</v>
       </c>
       <c r="K86" t="n">
-        <v>264.23</v>
+        <v>315.35</v>
       </c>
       <c r="L86" t="n">
-        <v>273.72</v>
+        <v>326.68</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>216.11</v>
+        <v>256.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-318.91</v>
+        <v>-378.98</v>
       </c>
       <c r="L87" t="n">
-        <v>385.23</v>
+        <v>457.8</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>301.52</v>
+        <v>350.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-102.37</v>
+        <v>-119.09</v>
       </c>
       <c r="L88" t="n">
-        <v>318.43</v>
+        <v>370.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>83.44</v>
+        <v>38.89</v>
       </c>
       <c r="K14" t="n">
-        <v>-100.79</v>
+        <v>-46.98</v>
       </c>
       <c r="L14" t="n">
-        <v>130.85</v>
+        <v>60.99</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-40.98</v>
+        <v>-19.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-235.02</v>
+        <v>-109.3</v>
       </c>
       <c r="L15" t="n">
-        <v>238.56</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-76.79000000000001</v>
+        <v>-40.22</v>
       </c>
       <c r="K16" t="n">
-        <v>-42.78</v>
+        <v>-22.4</v>
       </c>
       <c r="L16" t="n">
-        <v>87.91</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>172.54</v>
+        <v>78.89</v>
       </c>
       <c r="K17" t="n">
-        <v>132.98</v>
+        <v>60.8</v>
       </c>
       <c r="L17" t="n">
-        <v>217.84</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>107.68</v>
+        <v>46.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-196.73</v>
+        <v>-85.03</v>
       </c>
       <c r="L18" t="n">
-        <v>224.27</v>
+        <v>96.93000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>72.48999999999999</v>
+        <v>35.91</v>
       </c>
       <c r="K19" t="n">
-        <v>-299.54</v>
+        <v>-148.37</v>
       </c>
       <c r="L19" t="n">
-        <v>308.18</v>
+        <v>152.65</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-301.08</v>
+        <v>-150.21</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.54000000000001</v>
+        <v>-36.69</v>
       </c>
       <c r="L20" t="n">
-        <v>309.93</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-186.74</v>
+        <v>-95.77</v>
       </c>
       <c r="K21" t="n">
-        <v>-70.45999999999999</v>
+        <v>-36.14</v>
       </c>
       <c r="L21" t="n">
-        <v>199.59</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-94.19</v>
+        <v>-18.49</v>
       </c>
       <c r="K22" t="n">
-        <v>49.13</v>
+        <v>9.65</v>
       </c>
       <c r="L22" t="n">
-        <v>106.23</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-83.31999999999999</v>
+        <v>-38.22</v>
       </c>
       <c r="K23" t="n">
-        <v>273.9</v>
+        <v>125.63</v>
       </c>
       <c r="L23" t="n">
-        <v>286.29</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-38.91</v>
+        <v>-22.51</v>
       </c>
       <c r="K24" t="n">
-        <v>-492.07</v>
+        <v>-284.7</v>
       </c>
       <c r="L24" t="n">
-        <v>493.6</v>
+        <v>285.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>262.37</v>
+        <v>145.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-223.54</v>
+        <v>-124.38</v>
       </c>
       <c r="L25" t="n">
-        <v>344.68</v>
+        <v>191.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>303.01</v>
+        <v>165.38</v>
       </c>
       <c r="K26" t="n">
-        <v>72.43000000000001</v>
+        <v>39.53</v>
       </c>
       <c r="L26" t="n">
-        <v>311.55</v>
+        <v>170.04</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-442.15</v>
+        <v>-248.08</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.97</v>
+        <v>-13.45</v>
       </c>
       <c r="L27" t="n">
-        <v>442.8</v>
+        <v>248.45</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-202.13</v>
+        <v>-113.74</v>
       </c>
       <c r="K28" t="n">
-        <v>131.59</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>241.19</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.94</v>
+        <v>-13.93</v>
       </c>
       <c r="K29" t="n">
-        <v>123.06</v>
+        <v>68.75</v>
       </c>
       <c r="L29" t="n">
-        <v>125.57</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>6.88</v>
+        <v>3.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-282.2</v>
+        <v>-126.42</v>
       </c>
       <c r="L30" t="n">
-        <v>282.29</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-62.85</v>
+        <v>-31.53</v>
       </c>
       <c r="K31" t="n">
-        <v>181.38</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>191.96</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>157.51</v>
+        <v>82.38</v>
       </c>
       <c r="K32" t="n">
-        <v>1.82</v>
+        <v>0.95</v>
       </c>
       <c r="L32" t="n">
-        <v>157.52</v>
+        <v>82.39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>164.07</v>
+        <v>95.27</v>
       </c>
       <c r="K33" t="n">
-        <v>164.56</v>
+        <v>95.55</v>
       </c>
       <c r="L33" t="n">
-        <v>232.37</v>
+        <v>134.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>83.84999999999999</v>
+        <v>41.37</v>
       </c>
       <c r="K34" t="n">
-        <v>91.52</v>
+        <v>45.15</v>
       </c>
       <c r="L34" t="n">
-        <v>124.12</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>77.53</v>
+        <v>38.47</v>
       </c>
       <c r="K35" t="n">
-        <v>180.47</v>
+        <v>89.55</v>
       </c>
       <c r="L35" t="n">
-        <v>196.42</v>
+        <v>97.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>92.92</v>
+        <v>46.38</v>
       </c>
       <c r="K36" t="n">
-        <v>200.56</v>
+        <v>100.12</v>
       </c>
       <c r="L36" t="n">
-        <v>221.04</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>184.18</v>
+        <v>94.22</v>
       </c>
       <c r="K37" t="n">
-        <v>163.74</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>246.45</v>
+        <v>126.06</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-144.98</v>
+        <v>-75.51000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>324.27</v>
+        <v>168.9</v>
       </c>
       <c r="L38" t="n">
-        <v>355.2</v>
+        <v>185.01</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.59</v>
+        <v>-7.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-383.07</v>
+        <v>-179.02</v>
       </c>
       <c r="L39" t="n">
-        <v>383.43</v>
+        <v>179.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-212.32</v>
+        <v>-111.49</v>
       </c>
       <c r="K40" t="n">
-        <v>-105.76</v>
+        <v>-55.54</v>
       </c>
       <c r="L40" t="n">
-        <v>237.2</v>
+        <v>124.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>377.17</v>
+        <v>202.96</v>
       </c>
       <c r="K41" t="n">
-        <v>459.44</v>
+        <v>247.24</v>
       </c>
       <c r="L41" t="n">
-        <v>594.42</v>
+        <v>319.87</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>776.23</v>
+        <v>426.77</v>
       </c>
       <c r="K42" t="n">
-        <v>31.06</v>
+        <v>17.08</v>
       </c>
       <c r="L42" t="n">
-        <v>776.85</v>
+        <v>427.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-201.9</v>
+        <v>-113.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-202.35</v>
+        <v>-113.54</v>
       </c>
       <c r="L43" t="n">
-        <v>285.85</v>
+        <v>160.39</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>94.09</v>
+        <v>37.54</v>
       </c>
       <c r="K44" t="n">
-        <v>145.64</v>
+        <v>58.11</v>
       </c>
       <c r="L44" t="n">
-        <v>173.39</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-70.90000000000001</v>
+        <v>-34.89</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.64</v>
+        <v>-33.28</v>
       </c>
       <c r="L45" t="n">
-        <v>97.98999999999999</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>106.38</v>
+        <v>52.1</v>
       </c>
       <c r="K46" t="n">
-        <v>166.75</v>
+        <v>81.67</v>
       </c>
       <c r="L46" t="n">
-        <v>197.8</v>
+        <v>96.87</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>137.63</v>
+        <v>59.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-39.15</v>
+        <v>-16.99</v>
       </c>
       <c r="L47" t="n">
-        <v>143.09</v>
+        <v>62.12</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-130.05</v>
+        <v>-58.88</v>
       </c>
       <c r="K48" t="n">
-        <v>39.02</v>
+        <v>17.67</v>
       </c>
       <c r="L48" t="n">
-        <v>135.78</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-148.39</v>
+        <v>-68.31</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="L49" t="n">
-        <v>148.4</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-283.73</v>
+        <v>-139.93</v>
       </c>
       <c r="K50" t="n">
-        <v>-93.8</v>
+        <v>-46.26</v>
       </c>
       <c r="L50" t="n">
-        <v>298.83</v>
+        <v>147.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.43</v>
+        <v>-55.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-68.25</v>
+        <v>-34.96</v>
       </c>
       <c r="L51" t="n">
-        <v>127.28</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-250.62</v>
+        <v>-123.41</v>
       </c>
       <c r="K52" t="n">
-        <v>-100.16</v>
+        <v>-49.32</v>
       </c>
       <c r="L52" t="n">
-        <v>269.89</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-81.43000000000001</v>
+        <v>-44.23</v>
       </c>
       <c r="K53" t="n">
-        <v>408.41</v>
+        <v>221.82</v>
       </c>
       <c r="L53" t="n">
-        <v>416.45</v>
+        <v>226.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-63.96</v>
+        <v>-30.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-391.04</v>
+        <v>-184.66</v>
       </c>
       <c r="L54" t="n">
-        <v>396.24</v>
+        <v>187.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-355.53</v>
+        <v>-176</v>
       </c>
       <c r="K55" t="n">
-        <v>-213.31</v>
+        <v>-105.6</v>
       </c>
       <c r="L55" t="n">
-        <v>414.61</v>
+        <v>205.25</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>162.32</v>
+        <v>88.72</v>
       </c>
       <c r="K56" t="n">
-        <v>-257.56</v>
+        <v>-140.77</v>
       </c>
       <c r="L56" t="n">
-        <v>304.44</v>
+        <v>166.4</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-182.59</v>
+        <v>-100.39</v>
       </c>
       <c r="K57" t="n">
-        <v>-400.81</v>
+        <v>-220.36</v>
       </c>
       <c r="L57" t="n">
-        <v>440.44</v>
+        <v>242.15</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>33.91</v>
+        <v>18.16</v>
       </c>
       <c r="K58" t="n">
-        <v>-316.59</v>
+        <v>-169.5</v>
       </c>
       <c r="L58" t="n">
-        <v>318.4</v>
+        <v>170.46</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>94.08</v>
+        <v>44.82</v>
       </c>
       <c r="K59" t="n">
-        <v>117.42</v>
+        <v>55.94</v>
       </c>
       <c r="L59" t="n">
-        <v>150.45</v>
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>172.11</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>170.75</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>242.44</v>
+        <v>108.61</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>53.53</v>
+        <v>26.59</v>
       </c>
       <c r="K61" t="n">
-        <v>73.06</v>
+        <v>36.3</v>
       </c>
       <c r="L61" t="n">
-        <v>90.56999999999999</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-69.42</v>
+        <v>-32.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-94.23999999999999</v>
+        <v>-44.45</v>
       </c>
       <c r="L62" t="n">
-        <v>117.04</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>15.28</v>
+        <v>7.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-95.27</v>
+        <v>-45.26</v>
       </c>
       <c r="L63" t="n">
-        <v>96.48999999999999</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.42</v>
+        <v>-26.57</v>
       </c>
       <c r="K64" t="n">
-        <v>158.19</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>167.62</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>262.51</v>
+        <v>128.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-129.59</v>
+        <v>-63.26</v>
       </c>
       <c r="L65" t="n">
-        <v>292.75</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-258.03</v>
+        <v>-126.57</v>
       </c>
       <c r="K66" t="n">
-        <v>-378.23</v>
+        <v>-185.52</v>
       </c>
       <c r="L66" t="n">
-        <v>457.87</v>
+        <v>224.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>304.42</v>
+        <v>147.86</v>
       </c>
       <c r="K67" t="n">
-        <v>124.04</v>
+        <v>60.25</v>
       </c>
       <c r="L67" t="n">
-        <v>328.72</v>
+        <v>159.67</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-48.71</v>
+        <v>-23.33</v>
       </c>
       <c r="K68" t="n">
-        <v>-328.54</v>
+        <v>-157.36</v>
       </c>
       <c r="L68" t="n">
-        <v>332.13</v>
+        <v>159.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-187.89</v>
+        <v>-85.89</v>
       </c>
       <c r="K69" t="n">
-        <v>317.1</v>
+        <v>144.96</v>
       </c>
       <c r="L69" t="n">
-        <v>368.58</v>
+        <v>168.5</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>363.72</v>
+        <v>175.47</v>
       </c>
       <c r="K70" t="n">
-        <v>65.39</v>
+        <v>31.54</v>
       </c>
       <c r="L70" t="n">
-        <v>369.55</v>
+        <v>178.28</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>189.54</v>
+        <v>111.52</v>
       </c>
       <c r="K71" t="n">
-        <v>149.45</v>
+        <v>87.94</v>
       </c>
       <c r="L71" t="n">
-        <v>241.38</v>
+        <v>142.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-84.73999999999999</v>
+        <v>-46.57</v>
       </c>
       <c r="K72" t="n">
-        <v>536.6900000000001</v>
+        <v>294.92</v>
       </c>
       <c r="L72" t="n">
-        <v>543.34</v>
+        <v>298.58</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-238.16</v>
+        <v>-134.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-35.97</v>
+        <v>-20.25</v>
       </c>
       <c r="L73" t="n">
-        <v>240.86</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-168.61</v>
+        <v>-79.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-102.89</v>
+        <v>-48.48</v>
       </c>
       <c r="L74" t="n">
-        <v>197.52</v>
+        <v>93.06999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>96.67</v>
+        <v>39.54</v>
       </c>
       <c r="K75" t="n">
-        <v>75.84999999999999</v>
+        <v>31.03</v>
       </c>
       <c r="L75" t="n">
-        <v>122.87</v>
+        <v>50.27</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-107.63</v>
+        <v>-51.63</v>
       </c>
       <c r="K76" t="n">
-        <v>118.77</v>
+        <v>56.97</v>
       </c>
       <c r="L76" t="n">
-        <v>160.28</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>73.79000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-157.06</v>
+        <v>-77.48999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>173.53</v>
+        <v>85.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-166.51</v>
+        <v>-75.14</v>
       </c>
       <c r="K78" t="n">
-        <v>-99.42</v>
+        <v>-44.87</v>
       </c>
       <c r="L78" t="n">
-        <v>193.93</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-92.03</v>
+        <v>-44.54</v>
       </c>
       <c r="K79" t="n">
-        <v>177.3</v>
+        <v>85.81</v>
       </c>
       <c r="L79" t="n">
-        <v>199.76</v>
+        <v>96.68000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>219.93</v>
+        <v>109.54</v>
       </c>
       <c r="K80" t="n">
-        <v>-171.34</v>
+        <v>-85.34</v>
       </c>
       <c r="L80" t="n">
-        <v>278.79</v>
+        <v>138.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>38.53</v>
+        <v>18.55</v>
       </c>
       <c r="K81" t="n">
-        <v>155.63</v>
+        <v>74.94</v>
       </c>
       <c r="L81" t="n">
-        <v>160.32</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>62.66</v>
+        <v>30.96</v>
       </c>
       <c r="K82" t="n">
-        <v>-151.91</v>
+        <v>-75.06999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>164.32</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-193.75</v>
+        <v>-84.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-347.26</v>
+        <v>-152.05</v>
       </c>
       <c r="L83" t="n">
-        <v>397.65</v>
+        <v>174.11</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>140.79</v>
+        <v>73.33</v>
       </c>
       <c r="K84" t="n">
-        <v>-251.58</v>
+        <v>-131.04</v>
       </c>
       <c r="L84" t="n">
-        <v>288.3</v>
+        <v>150.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>174.57</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-508.68</v>
+        <v>-221.57</v>
       </c>
       <c r="L85" t="n">
-        <v>537.8</v>
+        <v>234.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-85.28</v>
+        <v>-45.79</v>
       </c>
       <c r="K86" t="n">
-        <v>315.35</v>
+        <v>169.33</v>
       </c>
       <c r="L86" t="n">
-        <v>326.68</v>
+        <v>175.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>256.82</v>
+        <v>136.88</v>
       </c>
       <c r="K87" t="n">
-        <v>-378.98</v>
+        <v>-201.98</v>
       </c>
       <c r="L87" t="n">
-        <v>457.8</v>
+        <v>243.99</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>350.75</v>
+        <v>196.91</v>
       </c>
       <c r="K88" t="n">
-        <v>-119.09</v>
+        <v>-66.86</v>
       </c>
       <c r="L88" t="n">
-        <v>370.41</v>
+        <v>207.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>38.89</v>
+        <v>39.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.98</v>
+        <v>-47.5</v>
       </c>
       <c r="L14" t="n">
-        <v>60.99</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.06</v>
+        <v>-17.84</v>
       </c>
       <c r="K15" t="n">
-        <v>-109.3</v>
+        <v>-102.3</v>
       </c>
       <c r="L15" t="n">
-        <v>110.95</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.22</v>
+        <v>-42.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.4</v>
+        <v>-23.63</v>
       </c>
       <c r="L16" t="n">
-        <v>46.04</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>78.89</v>
+        <v>75.47</v>
       </c>
       <c r="K17" t="n">
-        <v>60.8</v>
+        <v>58.17</v>
       </c>
       <c r="L17" t="n">
-        <v>99.61</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>46.54</v>
+        <v>44.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-85.03</v>
+        <v>-81.5</v>
       </c>
       <c r="L18" t="n">
-        <v>96.93000000000001</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>35.91</v>
+        <v>33.51</v>
       </c>
       <c r="K19" t="n">
-        <v>-148.37</v>
+        <v>-138.46</v>
       </c>
       <c r="L19" t="n">
-        <v>152.65</v>
+        <v>142.46</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-150.21</v>
+        <v>-145.05</v>
       </c>
       <c r="K20" t="n">
-        <v>-36.69</v>
+        <v>-35.43</v>
       </c>
       <c r="L20" t="n">
-        <v>154.62</v>
+        <v>149.32</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-95.77</v>
+        <v>-97.29000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-36.14</v>
+        <v>-36.71</v>
       </c>
       <c r="L21" t="n">
-        <v>102.36</v>
+        <v>103.98</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.49</v>
+        <v>-18.1</v>
       </c>
       <c r="K22" t="n">
-        <v>9.65</v>
+        <v>9.44</v>
       </c>
       <c r="L22" t="n">
-        <v>20.85</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-38.22</v>
+        <v>-39.94</v>
       </c>
       <c r="K23" t="n">
-        <v>125.63</v>
+        <v>131.28</v>
       </c>
       <c r="L23" t="n">
-        <v>131.31</v>
+        <v>137.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-22.51</v>
+        <v>-18.1</v>
       </c>
       <c r="K24" t="n">
-        <v>-284.7</v>
+        <v>-228.91</v>
       </c>
       <c r="L24" t="n">
-        <v>285.59</v>
+        <v>229.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>145.98</v>
+        <v>144.02</v>
       </c>
       <c r="K25" t="n">
-        <v>-124.38</v>
+        <v>-122.7</v>
       </c>
       <c r="L25" t="n">
-        <v>191.78</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>165.38</v>
+        <v>180.1</v>
       </c>
       <c r="K26" t="n">
-        <v>39.53</v>
+        <v>43.05</v>
       </c>
       <c r="L26" t="n">
-        <v>170.04</v>
+        <v>185.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-248.08</v>
+        <v>-247.58</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.45</v>
+        <v>-13.42</v>
       </c>
       <c r="L27" t="n">
-        <v>248.45</v>
+        <v>247.94</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-113.74</v>
+        <v>-124.26</v>
       </c>
       <c r="K28" t="n">
-        <v>74.04000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>135.72</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.93</v>
+        <v>-13.99</v>
       </c>
       <c r="K29" t="n">
-        <v>68.75</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>70.15000000000001</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="K30" t="n">
-        <v>-126.42</v>
+        <v>-117.25</v>
       </c>
       <c r="L30" t="n">
-        <v>126.46</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.53</v>
+        <v>-30.2</v>
       </c>
       <c r="K31" t="n">
-        <v>90.98999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="L31" t="n">
-        <v>96.29000000000001</v>
+        <v>92.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>82.38</v>
+        <v>82.31</v>
       </c>
       <c r="K32" t="n">
         <v>0.95</v>
       </c>
       <c r="L32" t="n">
-        <v>82.39</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>95.27</v>
+        <v>90.83</v>
       </c>
       <c r="K33" t="n">
-        <v>95.55</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>134.93</v>
+        <v>128.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>41.37</v>
+        <v>42.61</v>
       </c>
       <c r="K34" t="n">
-        <v>45.15</v>
+        <v>46.5</v>
       </c>
       <c r="L34" t="n">
-        <v>61.24</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>38.47</v>
+        <v>40.04</v>
       </c>
       <c r="K35" t="n">
-        <v>89.55</v>
+        <v>93.22</v>
       </c>
       <c r="L35" t="n">
-        <v>97.47</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>46.38</v>
+        <v>46.91</v>
       </c>
       <c r="K36" t="n">
-        <v>100.12</v>
+        <v>101.25</v>
       </c>
       <c r="L36" t="n">
-        <v>110.34</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>94.22</v>
+        <v>92.69</v>
       </c>
       <c r="K37" t="n">
-        <v>83.76000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="L37" t="n">
-        <v>126.06</v>
+        <v>124.03</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-75.51000000000001</v>
+        <v>-75.22</v>
       </c>
       <c r="K38" t="n">
-        <v>168.9</v>
+        <v>168.24</v>
       </c>
       <c r="L38" t="n">
-        <v>185.01</v>
+        <v>184.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.76</v>
+        <v>-7.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-179.02</v>
+        <v>-179.26</v>
       </c>
       <c r="L39" t="n">
-        <v>179.19</v>
+        <v>179.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-111.49</v>
+        <v>-117.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-55.54</v>
+        <v>-58.42</v>
       </c>
       <c r="L40" t="n">
-        <v>124.56</v>
+        <v>131.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>202.96</v>
+        <v>206.95</v>
       </c>
       <c r="K41" t="n">
-        <v>247.24</v>
+        <v>252.09</v>
       </c>
       <c r="L41" t="n">
-        <v>319.87</v>
+        <v>326.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>426.77</v>
+        <v>416.16</v>
       </c>
       <c r="K42" t="n">
-        <v>17.08</v>
+        <v>16.65</v>
       </c>
       <c r="L42" t="n">
-        <v>427.11</v>
+        <v>416.49</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-113.28</v>
+        <v>-119.73</v>
       </c>
       <c r="K43" t="n">
-        <v>-113.54</v>
+        <v>-120</v>
       </c>
       <c r="L43" t="n">
-        <v>160.39</v>
+        <v>169.51</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>37.54</v>
+        <v>35.42</v>
       </c>
       <c r="K44" t="n">
-        <v>58.11</v>
+        <v>54.82</v>
       </c>
       <c r="L44" t="n">
-        <v>69.18000000000001</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.89</v>
+        <v>-36.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-33.28</v>
+        <v>-34.44</v>
       </c>
       <c r="L45" t="n">
-        <v>48.22</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>52.1</v>
+        <v>49.57</v>
       </c>
       <c r="K46" t="n">
-        <v>81.67</v>
+        <v>77.7</v>
       </c>
       <c r="L46" t="n">
-        <v>96.87</v>
+        <v>92.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>59.75</v>
+        <v>60.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-16.99</v>
+        <v>-17.18</v>
       </c>
       <c r="L47" t="n">
-        <v>62.12</v>
+        <v>62.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.88</v>
+        <v>-59.5</v>
       </c>
       <c r="K48" t="n">
-        <v>17.67</v>
+        <v>17.85</v>
       </c>
       <c r="L48" t="n">
-        <v>61.47</v>
+        <v>62.12</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-68.31</v>
+        <v>-69.2</v>
       </c>
       <c r="K49" t="n">
         <v>0.32</v>
       </c>
       <c r="L49" t="n">
-        <v>68.31</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-139.93</v>
+        <v>-136.18</v>
       </c>
       <c r="K50" t="n">
-        <v>-46.26</v>
+        <v>-45.02</v>
       </c>
       <c r="L50" t="n">
-        <v>147.37</v>
+        <v>143.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-55.02</v>
+        <v>-58.87</v>
       </c>
       <c r="K51" t="n">
-        <v>-34.96</v>
+        <v>-37.4</v>
       </c>
       <c r="L51" t="n">
-        <v>65.19</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-123.41</v>
+        <v>-120.71</v>
       </c>
       <c r="K52" t="n">
-        <v>-49.32</v>
+        <v>-48.24</v>
       </c>
       <c r="L52" t="n">
-        <v>132.9</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-44.23</v>
+        <v>-42.78</v>
       </c>
       <c r="K53" t="n">
-        <v>221.82</v>
+        <v>214.58</v>
       </c>
       <c r="L53" t="n">
-        <v>226.18</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-30.2</v>
+        <v>-30.03</v>
       </c>
       <c r="K54" t="n">
-        <v>-184.66</v>
+        <v>-183.58</v>
       </c>
       <c r="L54" t="n">
-        <v>187.11</v>
+        <v>186.02</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-176</v>
+        <v>-173.08</v>
       </c>
       <c r="K55" t="n">
-        <v>-105.6</v>
+        <v>-103.84</v>
       </c>
       <c r="L55" t="n">
-        <v>205.25</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>88.72</v>
+        <v>97.02</v>
       </c>
       <c r="K56" t="n">
-        <v>-140.77</v>
+        <v>-153.94</v>
       </c>
       <c r="L56" t="n">
-        <v>166.4</v>
+        <v>181.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-100.39</v>
+        <v>-102.37</v>
       </c>
       <c r="K57" t="n">
-        <v>-220.36</v>
+        <v>-224.7</v>
       </c>
       <c r="L57" t="n">
-        <v>242.15</v>
+        <v>246.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>18.16</v>
+        <v>20.31</v>
       </c>
       <c r="K58" t="n">
-        <v>-169.5</v>
+        <v>-189.56</v>
       </c>
       <c r="L58" t="n">
-        <v>170.46</v>
+        <v>190.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>44.82</v>
+        <v>44.15</v>
       </c>
       <c r="K59" t="n">
-        <v>55.94</v>
+        <v>55.1</v>
       </c>
       <c r="L59" t="n">
-        <v>71.68000000000001</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>77.09999999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>76.48999999999999</v>
+        <v>71.25</v>
       </c>
       <c r="L60" t="n">
-        <v>108.61</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>26.59</v>
+        <v>27.86</v>
       </c>
       <c r="K61" t="n">
-        <v>36.3</v>
+        <v>38.03</v>
       </c>
       <c r="L61" t="n">
-        <v>45</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-32.74</v>
+        <v>-34.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.45</v>
+        <v>-46.24</v>
       </c>
       <c r="L62" t="n">
-        <v>55.21</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>7.26</v>
+        <v>7.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-45.26</v>
+        <v>-48.2</v>
       </c>
       <c r="L63" t="n">
-        <v>45.84</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.57</v>
+        <v>-26.21</v>
       </c>
       <c r="K64" t="n">
-        <v>75.84999999999999</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>80.37</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>128.15</v>
+        <v>125.97</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.26</v>
+        <v>-62.18</v>
       </c>
       <c r="L65" t="n">
-        <v>142.92</v>
+        <v>140.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-126.57</v>
+        <v>-118.79</v>
       </c>
       <c r="K66" t="n">
-        <v>-185.52</v>
+        <v>-174.12</v>
       </c>
       <c r="L66" t="n">
-        <v>224.58</v>
+        <v>210.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>147.86</v>
+        <v>142.46</v>
       </c>
       <c r="K67" t="n">
-        <v>60.25</v>
+        <v>58.05</v>
       </c>
       <c r="L67" t="n">
-        <v>159.67</v>
+        <v>153.84</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-23.33</v>
+        <v>-23.46</v>
       </c>
       <c r="K68" t="n">
-        <v>-157.36</v>
+        <v>-158.21</v>
       </c>
       <c r="L68" t="n">
-        <v>159.08</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-85.89</v>
+        <v>-86.25</v>
       </c>
       <c r="K69" t="n">
-        <v>144.96</v>
+        <v>145.56</v>
       </c>
       <c r="L69" t="n">
-        <v>168.5</v>
+        <v>169.2</v>
       </c>
     </row>
     <row r="70">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>111.52</v>
+        <v>117.71</v>
       </c>
       <c r="K71" t="n">
-        <v>87.94</v>
+        <v>92.81</v>
       </c>
       <c r="L71" t="n">
-        <v>142.02</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-46.57</v>
+        <v>-46.24</v>
       </c>
       <c r="K72" t="n">
-        <v>294.92</v>
+        <v>292.87</v>
       </c>
       <c r="L72" t="n">
-        <v>298.58</v>
+        <v>296.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-134.09</v>
+        <v>-142.93</v>
       </c>
       <c r="K73" t="n">
-        <v>-20.25</v>
+        <v>-21.59</v>
       </c>
       <c r="L73" t="n">
-        <v>135.61</v>
+        <v>144.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-79.44</v>
+        <v>-75.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-48.48</v>
+        <v>-46.19</v>
       </c>
       <c r="L74" t="n">
-        <v>93.06999999999999</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>39.54</v>
+        <v>40.58</v>
       </c>
       <c r="K75" t="n">
-        <v>31.03</v>
+        <v>31.84</v>
       </c>
       <c r="L75" t="n">
-        <v>50.27</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.63</v>
+        <v>-50.34</v>
       </c>
       <c r="K76" t="n">
-        <v>56.97</v>
+        <v>55.55</v>
       </c>
       <c r="L76" t="n">
-        <v>76.88</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>36.4</v>
+        <v>35.93</v>
       </c>
       <c r="K77" t="n">
-        <v>-77.48999999999999</v>
+        <v>-76.48999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>85.61</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-75.14</v>
+        <v>-72.5</v>
       </c>
       <c r="K78" t="n">
-        <v>-44.87</v>
+        <v>-43.29</v>
       </c>
       <c r="L78" t="n">
-        <v>87.52</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-44.54</v>
+        <v>-43</v>
       </c>
       <c r="K79" t="n">
-        <v>85.81</v>
+        <v>82.84</v>
       </c>
       <c r="L79" t="n">
-        <v>96.68000000000001</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>109.54</v>
+        <v>107.67</v>
       </c>
       <c r="K80" t="n">
-        <v>-85.34</v>
+        <v>-83.88</v>
       </c>
       <c r="L80" t="n">
-        <v>138.86</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>18.55</v>
+        <v>19.84</v>
       </c>
       <c r="K81" t="n">
-        <v>74.94</v>
+        <v>80.13</v>
       </c>
       <c r="L81" t="n">
-        <v>77.2</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>30.96</v>
+        <v>32.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-75.06999999999999</v>
+        <v>-79.63</v>
       </c>
       <c r="L82" t="n">
-        <v>81.2</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-84.83</v>
+        <v>-90.29000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-152.05</v>
+        <v>-161.82</v>
       </c>
       <c r="L83" t="n">
-        <v>174.11</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>73.33</v>
+        <v>74.16</v>
       </c>
       <c r="K84" t="n">
-        <v>-131.04</v>
+        <v>-132.52</v>
       </c>
       <c r="L84" t="n">
-        <v>150.16</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>76.04000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-221.57</v>
+        <v>-226.49</v>
       </c>
       <c r="L85" t="n">
-        <v>234.25</v>
+        <v>239.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-45.79</v>
+        <v>-50.85</v>
       </c>
       <c r="K86" t="n">
-        <v>169.33</v>
+        <v>188.06</v>
       </c>
       <c r="L86" t="n">
-        <v>175.41</v>
+        <v>194.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>136.88</v>
+        <v>149.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.98</v>
+        <v>-221.09</v>
       </c>
       <c r="L87" t="n">
-        <v>243.99</v>
+        <v>267.07</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>196.91</v>
+        <v>198.6</v>
       </c>
       <c r="K88" t="n">
-        <v>-66.86</v>
+        <v>-67.43000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>207.95</v>
+        <v>209.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>39.33</v>
+        <v>40.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-47.5</v>
+        <v>-49.09</v>
       </c>
       <c r="L14" t="n">
-        <v>61.67</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.84</v>
+        <v>-16.86</v>
       </c>
       <c r="K15" t="n">
-        <v>-102.3</v>
+        <v>-96.67</v>
       </c>
       <c r="L15" t="n">
-        <v>103.85</v>
+        <v>98.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-42.42</v>
+        <v>-45.14</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.63</v>
+        <v>-25.15</v>
       </c>
       <c r="L16" t="n">
-        <v>48.56</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>75.47</v>
+        <v>73.72</v>
       </c>
       <c r="K17" t="n">
-        <v>58.17</v>
+        <v>56.82</v>
       </c>
       <c r="L17" t="n">
-        <v>95.29000000000001</v>
+        <v>93.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>44.61</v>
+        <v>44.15</v>
       </c>
       <c r="K18" t="n">
-        <v>-81.5</v>
+        <v>-80.66</v>
       </c>
       <c r="L18" t="n">
-        <v>92.91</v>
+        <v>91.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>33.51</v>
+        <v>31.26</v>
       </c>
       <c r="K19" t="n">
-        <v>-138.46</v>
+        <v>-129.18</v>
       </c>
       <c r="L19" t="n">
-        <v>142.46</v>
+        <v>132.91</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-145.05</v>
+        <v>-140.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-35.43</v>
+        <v>-34.23</v>
       </c>
       <c r="L20" t="n">
-        <v>149.32</v>
+        <v>144.28</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-97.29000000000001</v>
+        <v>-99.12</v>
       </c>
       <c r="K21" t="n">
-        <v>-36.71</v>
+        <v>-37.4</v>
       </c>
       <c r="L21" t="n">
-        <v>103.98</v>
+        <v>105.94</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.1</v>
+        <v>-19.47</v>
       </c>
       <c r="K22" t="n">
-        <v>9.44</v>
+        <v>10.15</v>
       </c>
       <c r="L22" t="n">
-        <v>20.41</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-39.94</v>
+        <v>-41.54</v>
       </c>
       <c r="K23" t="n">
-        <v>131.28</v>
+        <v>136.57</v>
       </c>
       <c r="L23" t="n">
-        <v>137.22</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-18.1</v>
+        <v>-17.35</v>
       </c>
       <c r="K24" t="n">
-        <v>-228.91</v>
+        <v>-219.38</v>
       </c>
       <c r="L24" t="n">
-        <v>229.62</v>
+        <v>220.07</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>144.02</v>
+        <v>141.56</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.7</v>
+        <v>-120.61</v>
       </c>
       <c r="L25" t="n">
-        <v>189.2</v>
+        <v>185.98</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>180.1</v>
+        <v>190.34</v>
       </c>
       <c r="K26" t="n">
-        <v>43.05</v>
+        <v>45.49</v>
       </c>
       <c r="L26" t="n">
-        <v>185.18</v>
+        <v>195.7</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-247.58</v>
+        <v>-244.26</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.42</v>
+        <v>-13.24</v>
       </c>
       <c r="L27" t="n">
-        <v>247.94</v>
+        <v>244.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-124.26</v>
+        <v>-135.4</v>
       </c>
       <c r="K28" t="n">
-        <v>80.90000000000001</v>
+        <v>88.14</v>
       </c>
       <c r="L28" t="n">
-        <v>148.28</v>
+        <v>161.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.99</v>
+        <v>-14.07</v>
       </c>
       <c r="K29" t="n">
-        <v>69.06999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="L29" t="n">
-        <v>70.47</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-117.25</v>
+        <v>-110.21</v>
       </c>
       <c r="L30" t="n">
-        <v>117.28</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.2</v>
+        <v>-29.03</v>
       </c>
       <c r="K31" t="n">
-        <v>87.16</v>
+        <v>83.77</v>
       </c>
       <c r="L31" t="n">
-        <v>92.23999999999999</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>82.31</v>
+        <v>82.62</v>
       </c>
       <c r="K32" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L32" t="n">
-        <v>82.31</v>
+        <v>82.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>90.83</v>
+        <v>85.75</v>
       </c>
       <c r="K33" t="n">
-        <v>91.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>128.64</v>
+        <v>121.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>42.61</v>
+        <v>44.61</v>
       </c>
       <c r="K34" t="n">
-        <v>46.5</v>
+        <v>48.69</v>
       </c>
       <c r="L34" t="n">
-        <v>63.07</v>
+        <v>66.03</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>40.04</v>
+        <v>42.14</v>
       </c>
       <c r="K35" t="n">
-        <v>93.22</v>
+        <v>98.09</v>
       </c>
       <c r="L35" t="n">
-        <v>101.46</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>46.91</v>
+        <v>47.8</v>
       </c>
       <c r="K36" t="n">
-        <v>101.25</v>
+        <v>103.19</v>
       </c>
       <c r="L36" t="n">
-        <v>111.59</v>
+        <v>113.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>92.69</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>82.41</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>124.03</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-75.22</v>
+        <v>-74.59</v>
       </c>
       <c r="K38" t="n">
-        <v>168.24</v>
+        <v>166.82</v>
       </c>
       <c r="L38" t="n">
-        <v>184.29</v>
+        <v>182.74</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.77</v>
+        <v>-7.71</v>
       </c>
       <c r="K39" t="n">
-        <v>-179.26</v>
+        <v>-178.01</v>
       </c>
       <c r="L39" t="n">
-        <v>179.43</v>
+        <v>178.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-117.28</v>
+        <v>-123.49</v>
       </c>
       <c r="K40" t="n">
-        <v>-58.42</v>
+        <v>-61.51</v>
       </c>
       <c r="L40" t="n">
-        <v>131.02</v>
+        <v>137.96</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>206.95</v>
+        <v>200.17</v>
       </c>
       <c r="K41" t="n">
-        <v>252.09</v>
+        <v>243.83</v>
       </c>
       <c r="L41" t="n">
-        <v>326.16</v>
+        <v>315.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>416.16</v>
+        <v>390.03</v>
       </c>
       <c r="K42" t="n">
-        <v>16.65</v>
+        <v>15.61</v>
       </c>
       <c r="L42" t="n">
-        <v>416.49</v>
+        <v>390.35</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-119.73</v>
+        <v>-125.86</v>
       </c>
       <c r="K43" t="n">
-        <v>-120</v>
+        <v>-126.14</v>
       </c>
       <c r="L43" t="n">
-        <v>169.51</v>
+        <v>178.2</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>35.42</v>
+        <v>36.33</v>
       </c>
       <c r="K44" t="n">
-        <v>54.82</v>
+        <v>56.23</v>
       </c>
       <c r="L44" t="n">
-        <v>65.27</v>
+        <v>66.94</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.1</v>
+        <v>-37.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-34.44</v>
+        <v>-36.2</v>
       </c>
       <c r="L45" t="n">
-        <v>49.89</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>49.57</v>
+        <v>47.41</v>
       </c>
       <c r="K46" t="n">
-        <v>77.7</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>92.16</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>60.38</v>
+        <v>63.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-17.18</v>
+        <v>-18</v>
       </c>
       <c r="L47" t="n">
-        <v>62.78</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-59.5</v>
+        <v>-61.91</v>
       </c>
       <c r="K48" t="n">
-        <v>17.85</v>
+        <v>18.57</v>
       </c>
       <c r="L48" t="n">
-        <v>62.12</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-69.2</v>
+        <v>-71.97</v>
       </c>
       <c r="K49" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="L49" t="n">
-        <v>69.2</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-136.18</v>
+        <v>-133.16</v>
       </c>
       <c r="K50" t="n">
-        <v>-45.02</v>
+        <v>-44.02</v>
       </c>
       <c r="L50" t="n">
-        <v>143.43</v>
+        <v>140.24</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-58.87</v>
+        <v>-63.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-37.4</v>
+        <v>-40.25</v>
       </c>
       <c r="L51" t="n">
-        <v>69.75</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-120.71</v>
+        <v>-118.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-48.24</v>
+        <v>-47.46</v>
       </c>
       <c r="L52" t="n">
-        <v>129.99</v>
+        <v>127.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-42.78</v>
+        <v>-41.03</v>
       </c>
       <c r="K53" t="n">
-        <v>214.58</v>
+        <v>205.79</v>
       </c>
       <c r="L53" t="n">
-        <v>218.81</v>
+        <v>209.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-30.03</v>
+        <v>-29.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-183.58</v>
+        <v>-180.85</v>
       </c>
       <c r="L54" t="n">
-        <v>186.02</v>
+        <v>183.25</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-173.08</v>
+        <v>-168.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.84</v>
+        <v>-101.2</v>
       </c>
       <c r="L55" t="n">
-        <v>201.84</v>
+        <v>196.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>97.02</v>
+        <v>103.1</v>
       </c>
       <c r="K56" t="n">
-        <v>-153.94</v>
+        <v>-163.6</v>
       </c>
       <c r="L56" t="n">
-        <v>181.96</v>
+        <v>193.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-102.37</v>
+        <v>-101.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-224.7</v>
+        <v>-222.49</v>
       </c>
       <c r="L57" t="n">
-        <v>246.92</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>20.31</v>
+        <v>21.56</v>
       </c>
       <c r="K58" t="n">
-        <v>-189.56</v>
+        <v>-201.29</v>
       </c>
       <c r="L58" t="n">
-        <v>190.65</v>
+        <v>202.44</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>44.15</v>
+        <v>44.18</v>
       </c>
       <c r="K59" t="n">
-        <v>55.1</v>
+        <v>55.15</v>
       </c>
       <c r="L59" t="n">
-        <v>70.61</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>71.81999999999999</v>
+        <v>67.89</v>
       </c>
       <c r="K60" t="n">
-        <v>71.25</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>101.17</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>27.86</v>
+        <v>29.64</v>
       </c>
       <c r="K61" t="n">
-        <v>38.03</v>
+        <v>40.45</v>
       </c>
       <c r="L61" t="n">
-        <v>47.15</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-34.06</v>
+        <v>-36.27</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.24</v>
+        <v>-49.24</v>
       </c>
       <c r="L62" t="n">
-        <v>57.43</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>7.73</v>
+        <v>8.41</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.2</v>
+        <v>-52.46</v>
       </c>
       <c r="L63" t="n">
-        <v>48.81</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.21</v>
+        <v>-26.31</v>
       </c>
       <c r="K64" t="n">
-        <v>74.81999999999999</v>
+        <v>75.09</v>
       </c>
       <c r="L64" t="n">
-        <v>79.28</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>125.97</v>
+        <v>124.88</v>
       </c>
       <c r="K65" t="n">
-        <v>-62.18</v>
+        <v>-61.65</v>
       </c>
       <c r="L65" t="n">
-        <v>140.48</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-118.79</v>
+        <v>-111.18</v>
       </c>
       <c r="K66" t="n">
-        <v>-174.12</v>
+        <v>-162.97</v>
       </c>
       <c r="L66" t="n">
-        <v>210.78</v>
+        <v>197.29</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>142.46</v>
+        <v>138.09</v>
       </c>
       <c r="K67" t="n">
-        <v>58.05</v>
+        <v>56.26</v>
       </c>
       <c r="L67" t="n">
-        <v>153.84</v>
+        <v>149.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-23.46</v>
+        <v>-23.43</v>
       </c>
       <c r="K68" t="n">
-        <v>-158.21</v>
+        <v>-158.01</v>
       </c>
       <c r="L68" t="n">
-        <v>159.94</v>
+        <v>159.74</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-86.25</v>
+        <v>-85.84</v>
       </c>
       <c r="K69" t="n">
-        <v>145.56</v>
+        <v>144.87</v>
       </c>
       <c r="L69" t="n">
-        <v>169.2</v>
+        <v>168.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>175.47</v>
+        <v>174.22</v>
       </c>
       <c r="K70" t="n">
-        <v>31.54</v>
+        <v>31.32</v>
       </c>
       <c r="L70" t="n">
-        <v>178.28</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>117.71</v>
+        <v>124.78</v>
       </c>
       <c r="K71" t="n">
-        <v>92.81</v>
+        <v>98.39</v>
       </c>
       <c r="L71" t="n">
-        <v>149.9</v>
+        <v>158.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-46.24</v>
+        <v>-44.33</v>
       </c>
       <c r="K72" t="n">
-        <v>292.87</v>
+        <v>280.73</v>
       </c>
       <c r="L72" t="n">
-        <v>296.5</v>
+        <v>284.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-142.93</v>
+        <v>-152.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-21.59</v>
+        <v>-22.97</v>
       </c>
       <c r="L73" t="n">
-        <v>144.55</v>
+        <v>153.77</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-75.69</v>
+        <v>-72.97</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.19</v>
+        <v>-44.53</v>
       </c>
       <c r="L74" t="n">
-        <v>88.67</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>40.58</v>
+        <v>43.38</v>
       </c>
       <c r="K75" t="n">
-        <v>31.84</v>
+        <v>34.04</v>
       </c>
       <c r="L75" t="n">
-        <v>51.58</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-50.34</v>
+        <v>-49.76</v>
       </c>
       <c r="K76" t="n">
-        <v>55.55</v>
+        <v>54.91</v>
       </c>
       <c r="L76" t="n">
-        <v>74.97</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>35.93</v>
+        <v>35.91</v>
       </c>
       <c r="K77" t="n">
-        <v>-76.48999999999999</v>
+        <v>-76.44</v>
       </c>
       <c r="L77" t="n">
-        <v>84.51000000000001</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-72.5</v>
+        <v>-71.70999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-43.29</v>
+        <v>-42.82</v>
       </c>
       <c r="L78" t="n">
-        <v>84.44</v>
+        <v>83.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-43</v>
+        <v>-42.02</v>
       </c>
       <c r="K79" t="n">
-        <v>82.84</v>
+        <v>80.94</v>
       </c>
       <c r="L79" t="n">
-        <v>93.33</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>107.67</v>
+        <v>106.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.88</v>
+        <v>-82.81</v>
       </c>
       <c r="L80" t="n">
-        <v>136.49</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>19.84</v>
+        <v>21.56</v>
       </c>
       <c r="K81" t="n">
-        <v>80.13</v>
+        <v>87.09</v>
       </c>
       <c r="L81" t="n">
-        <v>82.55</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>32.85</v>
+        <v>35.26</v>
       </c>
       <c r="K82" t="n">
-        <v>-79.63</v>
+        <v>-85.48</v>
       </c>
       <c r="L82" t="n">
-        <v>86.14</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-90.29000000000001</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-161.82</v>
+        <v>-163.28</v>
       </c>
       <c r="L83" t="n">
-        <v>185.3</v>
+        <v>186.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>74.16</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-132.52</v>
+        <v>-133.69</v>
       </c>
       <c r="L84" t="n">
-        <v>151.86</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>77.73</v>
+        <v>74.92</v>
       </c>
       <c r="K85" t="n">
-        <v>-226.49</v>
+        <v>-218.31</v>
       </c>
       <c r="L85" t="n">
-        <v>239.46</v>
+        <v>230.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-50.85</v>
+        <v>-54.22</v>
       </c>
       <c r="K86" t="n">
-        <v>188.06</v>
+        <v>200.49</v>
       </c>
       <c r="L86" t="n">
-        <v>194.81</v>
+        <v>207.69</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>149.82</v>
+        <v>152.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-221.09</v>
+        <v>-225.18</v>
       </c>
       <c r="L87" t="n">
-        <v>267.07</v>
+        <v>272.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>198.6</v>
+        <v>198.47</v>
       </c>
       <c r="K88" t="n">
-        <v>-67.43000000000001</v>
+        <v>-67.38</v>
       </c>
       <c r="L88" t="n">
-        <v>209.73</v>
+        <v>209.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="F14" t="n">
-        <v>12.2</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>204.1</v>
+        <v>186.2</v>
       </c>
       <c r="H14" t="n">
-        <v>81.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>40.64</v>
+        <v>-51.61</v>
       </c>
       <c r="K14" t="n">
-        <v>-49.09</v>
+        <v>-47.91</v>
       </c>
       <c r="L14" t="n">
-        <v>63.73</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:30:53</t>
+          <t>04:32:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="F15" t="n">
-        <v>11.76</v>
+        <v>9.33</v>
       </c>
       <c r="G15" t="n">
-        <v>184.3</v>
+        <v>196.4</v>
       </c>
       <c r="H15" t="n">
-        <v>77.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.86</v>
+        <v>-15.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.67</v>
+        <v>-55.05</v>
       </c>
       <c r="L15" t="n">
-        <v>98.13</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:32:25</t>
+          <t>04:34:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>12.37</v>
+        <v>8.82</v>
       </c>
       <c r="G16" t="n">
-        <v>194.4</v>
+        <v>179</v>
       </c>
       <c r="H16" t="n">
         <v>82.8</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.14</v>
+        <v>34.63</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.15</v>
+        <v>16.92</v>
       </c>
       <c r="L16" t="n">
-        <v>51.67</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:37:26</t>
+          <t>04:39:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.09</v>
+        <v>3.25</v>
       </c>
       <c r="F17" t="n">
-        <v>12.32</v>
+        <v>13.2</v>
       </c>
       <c r="G17" t="n">
-        <v>176.2</v>
+        <v>165.1</v>
       </c>
       <c r="H17" t="n">
-        <v>75.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>73.72</v>
+        <v>-119.83</v>
       </c>
       <c r="K17" t="n">
-        <v>56.82</v>
+        <v>-39.1</v>
       </c>
       <c r="L17" t="n">
-        <v>93.06999999999999</v>
+        <v>126.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:38:40</t>
+          <t>04:42:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.45</v>
+        <v>3.01</v>
       </c>
       <c r="F18" t="n">
-        <v>12.48</v>
+        <v>10.26</v>
       </c>
       <c r="G18" t="n">
-        <v>177.7</v>
+        <v>185.2</v>
       </c>
       <c r="H18" t="n">
-        <v>79.2</v>
+        <v>72.8</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>44.15</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.66</v>
+        <v>21.14</v>
       </c>
       <c r="L18" t="n">
-        <v>91.95</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:39:12</t>
+          <t>04:44:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="F19" t="n">
-        <v>13.02</v>
+        <v>11.78</v>
       </c>
       <c r="G19" t="n">
-        <v>197.6</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
-        <v>77.5</v>
+        <v>76.5</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>31.26</v>
+        <v>-35.06</v>
       </c>
       <c r="K19" t="n">
-        <v>-129.18</v>
+        <v>-114.71</v>
       </c>
       <c r="L19" t="n">
-        <v>132.91</v>
+        <v>119.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:43:05</t>
+          <t>04:47:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.79</v>
+        <v>3.28</v>
       </c>
       <c r="F20" t="n">
-        <v>12.11</v>
+        <v>8.81</v>
       </c>
       <c r="G20" t="n">
-        <v>177.6</v>
+        <v>189.2</v>
       </c>
       <c r="H20" t="n">
-        <v>78.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.16</v>
+        <v>-2.97</v>
       </c>
       <c r="K20" t="n">
-        <v>-34.23</v>
+        <v>113.54</v>
       </c>
       <c r="L20" t="n">
-        <v>144.28</v>
+        <v>113.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:44:38</t>
+          <t>04:49:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="F21" t="n">
-        <v>12.82</v>
+        <v>9.67</v>
       </c>
       <c r="G21" t="n">
-        <v>184.3</v>
+        <v>195.2</v>
       </c>
       <c r="H21" t="n">
-        <v>75.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-99.12</v>
+        <v>-10.4</v>
       </c>
       <c r="K21" t="n">
-        <v>-37.4</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>105.94</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:45:47</t>
+          <t>04:51:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.44</v>
+        <v>3.23</v>
       </c>
       <c r="F22" t="n">
-        <v>12.76</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>182.7</v>
+        <v>172</v>
       </c>
       <c r="H22" t="n">
-        <v>73.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.47</v>
+        <v>36.17</v>
       </c>
       <c r="K22" t="n">
-        <v>10.15</v>
+        <v>140.28</v>
       </c>
       <c r="L22" t="n">
-        <v>21.96</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:50:24</t>
+          <t>04:57:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.42</v>
+        <v>3.8</v>
       </c>
       <c r="F23" t="n">
-        <v>12.21</v>
+        <v>8.84</v>
       </c>
       <c r="G23" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H23" t="n">
-        <v>77.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-41.54</v>
+        <v>151.78</v>
       </c>
       <c r="K23" t="n">
-        <v>136.57</v>
+        <v>-25.36</v>
       </c>
       <c r="L23" t="n">
-        <v>142.75</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:52:15</t>
+          <t>04:58:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="F24" t="n">
-        <v>12.64</v>
+        <v>13.38</v>
       </c>
       <c r="G24" t="n">
-        <v>181.5</v>
+        <v>190.8</v>
       </c>
       <c r="H24" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-17.35</v>
+        <v>-12.48</v>
       </c>
       <c r="K24" t="n">
-        <v>-219.38</v>
+        <v>-79.69</v>
       </c>
       <c r="L24" t="n">
-        <v>220.07</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:54:13</t>
+          <t>05:00:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="F25" t="n">
-        <v>11.72</v>
+        <v>9.48</v>
       </c>
       <c r="G25" t="n">
-        <v>197.1</v>
+        <v>174.1</v>
       </c>
       <c r="H25" t="n">
-        <v>82.5</v>
+        <v>80.5</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>141.56</v>
+        <v>-137.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.61</v>
+        <v>30.57</v>
       </c>
       <c r="L25" t="n">
-        <v>185.98</v>
+        <v>141.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:00:25</t>
+          <t>05:04:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.96</v>
+        <v>4.38</v>
       </c>
       <c r="F26" t="n">
-        <v>11.81</v>
+        <v>14.03</v>
       </c>
       <c r="G26" t="n">
-        <v>185.5</v>
+        <v>190.9</v>
       </c>
       <c r="H26" t="n">
-        <v>81.3</v>
+        <v>79.3</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>190.34</v>
+        <v>262.88</v>
       </c>
       <c r="K26" t="n">
-        <v>45.49</v>
+        <v>-100.25</v>
       </c>
       <c r="L26" t="n">
-        <v>195.7</v>
+        <v>281.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:02:28</t>
+          <t>05:07:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.43</v>
+        <v>3.59</v>
       </c>
       <c r="F27" t="n">
-        <v>12.49</v>
+        <v>10.68</v>
       </c>
       <c r="G27" t="n">
-        <v>191.3</v>
+        <v>197.5</v>
       </c>
       <c r="H27" t="n">
-        <v>85.7</v>
+        <v>79.3</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-244.26</v>
+        <v>-148.64</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.24</v>
+        <v>236.92</v>
       </c>
       <c r="L27" t="n">
-        <v>244.62</v>
+        <v>279.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:03:10</t>
+          <t>05:08:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="F28" t="n">
-        <v>11.42</v>
+        <v>10.85</v>
       </c>
       <c r="G28" t="n">
-        <v>204</v>
+        <v>167.1</v>
       </c>
       <c r="H28" t="n">
-        <v>82.2</v>
+        <v>80.5</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-135.4</v>
+        <v>-210.52</v>
       </c>
       <c r="K28" t="n">
-        <v>88.14</v>
+        <v>204.21</v>
       </c>
       <c r="L28" t="n">
-        <v>161.56</v>
+        <v>293.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:13:27</t>
+          <t>05:19:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.08</v>
+        <v>4.27</v>
       </c>
       <c r="F29" t="n">
-        <v>12.23</v>
+        <v>12.19</v>
       </c>
       <c r="G29" t="n">
-        <v>172.6</v>
+        <v>203.6</v>
       </c>
       <c r="H29" t="n">
-        <v>80</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-14.07</v>
+        <v>-101.77</v>
       </c>
       <c r="K29" t="n">
-        <v>69.42</v>
+        <v>41.94</v>
       </c>
       <c r="L29" t="n">
-        <v>70.83</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:14:44</t>
+          <t>05:22:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="F30" t="n">
-        <v>12.22</v>
+        <v>14.03</v>
       </c>
       <c r="G30" t="n">
         <v>188.5</v>
       </c>
       <c r="H30" t="n">
-        <v>86.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>2.69</v>
+        <v>2.31</v>
       </c>
       <c r="K30" t="n">
-        <v>-110.21</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>110.24</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:17:16</t>
+          <t>05:24:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="F31" t="n">
-        <v>12.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>194.9</v>
+        <v>203.1</v>
       </c>
       <c r="H31" t="n">
-        <v>86.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.03</v>
+        <v>19.06</v>
       </c>
       <c r="K31" t="n">
-        <v>83.77</v>
+        <v>-74.14</v>
       </c>
       <c r="L31" t="n">
-        <v>88.66</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:21:09</t>
+          <t>05:28:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.39</v>
+        <v>3.93</v>
       </c>
       <c r="F32" t="n">
-        <v>12.86</v>
+        <v>8.84</v>
       </c>
       <c r="G32" t="n">
-        <v>200.1</v>
+        <v>192.4</v>
       </c>
       <c r="H32" t="n">
-        <v>84.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>82.62</v>
+        <v>80.73</v>
       </c>
       <c r="K32" t="n">
-        <v>0.96</v>
+        <v>96.58</v>
       </c>
       <c r="L32" t="n">
-        <v>82.63</v>
+        <v>125.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:03</t>
+          <t>05:30:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="F33" t="n">
-        <v>11.81</v>
+        <v>10.88</v>
       </c>
       <c r="G33" t="n">
-        <v>186.7</v>
+        <v>193.5</v>
       </c>
       <c r="H33" t="n">
-        <v>79.7</v>
+        <v>81.3</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>85.75</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>86.01000000000001</v>
+        <v>-46.97</v>
       </c>
       <c r="L33" t="n">
-        <v>121.46</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:24:21</t>
+          <t>05:33:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="F34" t="n">
-        <v>12.9</v>
+        <v>11.08</v>
       </c>
       <c r="G34" t="n">
-        <v>193.2</v>
+        <v>195.9</v>
       </c>
       <c r="H34" t="n">
-        <v>76.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>44.61</v>
+        <v>-40.05</v>
       </c>
       <c r="K34" t="n">
-        <v>48.69</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>66.03</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:29:51</t>
+          <t>05:39:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="F35" t="n">
-        <v>12.23</v>
+        <v>10.63</v>
       </c>
       <c r="G35" t="n">
-        <v>193.5</v>
+        <v>197</v>
       </c>
       <c r="H35" t="n">
-        <v>79.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>42.14</v>
+        <v>-75.23999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>98.09</v>
+        <v>137.1</v>
       </c>
       <c r="L35" t="n">
-        <v>106.76</v>
+        <v>156.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:32:21</t>
+          <t>05:41:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.78</v>
+        <v>4.06</v>
       </c>
       <c r="F36" t="n">
-        <v>11.86</v>
+        <v>14.03</v>
       </c>
       <c r="G36" t="n">
-        <v>184.5</v>
+        <v>199.4</v>
       </c>
       <c r="H36" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>47.8</v>
+        <v>-137.97</v>
       </c>
       <c r="K36" t="n">
-        <v>103.19</v>
+        <v>47.54</v>
       </c>
       <c r="L36" t="n">
-        <v>113.72</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:34:39</t>
+          <t>05:42:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.37</v>
+        <v>4.03</v>
       </c>
       <c r="F37" t="n">
-        <v>12.13</v>
+        <v>10.7</v>
       </c>
       <c r="G37" t="n">
-        <v>188.3</v>
+        <v>178.2</v>
       </c>
       <c r="H37" t="n">
-        <v>79.5</v>
+        <v>80.3</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>91.09999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="K37" t="n">
-        <v>80.98999999999999</v>
+        <v>-135.51</v>
       </c>
       <c r="L37" t="n">
-        <v>121.9</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:40:21</t>
+          <t>05:48:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="F38" t="n">
-        <v>12.02</v>
+        <v>12.09</v>
       </c>
       <c r="G38" t="n">
-        <v>195</v>
+        <v>186.9</v>
       </c>
       <c r="H38" t="n">
-        <v>87.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-74.59</v>
+        <v>36.23</v>
       </c>
       <c r="K38" t="n">
-        <v>166.82</v>
+        <v>152.56</v>
       </c>
       <c r="L38" t="n">
-        <v>182.74</v>
+        <v>156.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:42:43</t>
+          <t>05:49:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.31</v>
+        <v>3.86</v>
       </c>
       <c r="F39" t="n">
-        <v>11.9</v>
+        <v>10.58</v>
       </c>
       <c r="G39" t="n">
-        <v>209</v>
+        <v>198.5</v>
       </c>
       <c r="H39" t="n">
-        <v>83.3</v>
+        <v>84.7</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.71</v>
+        <v>1.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-178.01</v>
+        <v>139.56</v>
       </c>
       <c r="L39" t="n">
-        <v>178.17</v>
+        <v>139.56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:44:01</t>
+          <t>05:51:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.69</v>
+        <v>3.19</v>
       </c>
       <c r="F40" t="n">
-        <v>12.58</v>
+        <v>7.62</v>
       </c>
       <c r="G40" t="n">
-        <v>190.6</v>
+        <v>212.3</v>
       </c>
       <c r="H40" t="n">
-        <v>76</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-123.49</v>
+        <v>-165.17</v>
       </c>
       <c r="K40" t="n">
-        <v>-61.51</v>
+        <v>20.09</v>
       </c>
       <c r="L40" t="n">
-        <v>137.96</v>
+        <v>166.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:49:27</t>
+          <t>05:56:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.27</v>
+        <v>3.57</v>
       </c>
       <c r="F41" t="n">
-        <v>12.27</v>
+        <v>14.03</v>
       </c>
       <c r="G41" t="n">
-        <v>183.6</v>
+        <v>185</v>
       </c>
       <c r="H41" t="n">
-        <v>74.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>200.17</v>
+        <v>283.41</v>
       </c>
       <c r="K41" t="n">
-        <v>243.83</v>
+        <v>-17.28</v>
       </c>
       <c r="L41" t="n">
-        <v>315.47</v>
+        <v>283.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:51:49</t>
+          <t>05:58:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.81</v>
+        <v>2.58</v>
       </c>
       <c r="F42" t="n">
-        <v>11.77</v>
+        <v>8.15</v>
       </c>
       <c r="G42" t="n">
-        <v>191.5</v>
+        <v>196.8</v>
       </c>
       <c r="H42" t="n">
-        <v>74.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>390.03</v>
+        <v>132.2</v>
       </c>
       <c r="K42" t="n">
-        <v>15.61</v>
+        <v>-166.41</v>
       </c>
       <c r="L42" t="n">
-        <v>390.35</v>
+        <v>212.53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:54:17</t>
+          <t>06:00:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.43</v>
+        <v>3.31</v>
       </c>
       <c r="F43" t="n">
-        <v>12.63</v>
+        <v>12.7</v>
       </c>
       <c r="G43" t="n">
-        <v>204.9</v>
+        <v>197.9</v>
       </c>
       <c r="H43" t="n">
-        <v>76.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-125.86</v>
+        <v>-140.71</v>
       </c>
       <c r="K43" t="n">
-        <v>-126.14</v>
+        <v>-198.81</v>
       </c>
       <c r="L43" t="n">
-        <v>178.2</v>
+        <v>243.57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:36</t>
+          <t>06:10:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.94</v>
+        <v>3.8</v>
       </c>
       <c r="F44" t="n">
-        <v>12.34</v>
+        <v>10.58</v>
       </c>
       <c r="G44" t="n">
-        <v>189.6</v>
+        <v>189.9</v>
       </c>
       <c r="H44" t="n">
-        <v>89.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>36.33</v>
+        <v>84.2</v>
       </c>
       <c r="K44" t="n">
-        <v>56.23</v>
+        <v>67.34</v>
       </c>
       <c r="L44" t="n">
-        <v>66.94</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:08:07</t>
+          <t>06:11:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.65</v>
+        <v>4.18</v>
       </c>
       <c r="F45" t="n">
-        <v>11.91</v>
+        <v>11.59</v>
       </c>
       <c r="G45" t="n">
-        <v>182.9</v>
+        <v>194.7</v>
       </c>
       <c r="H45" t="n">
-        <v>85.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-37.94</v>
+        <v>-12.06</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.2</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>52.44</v>
+        <v>66.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:53</t>
+          <t>06:12:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.67</v>
+        <v>4.32</v>
       </c>
       <c r="F46" t="n">
-        <v>12.29</v>
+        <v>13.12</v>
       </c>
       <c r="G46" t="n">
-        <v>183.8</v>
+        <v>181.2</v>
       </c>
       <c r="H46" t="n">
-        <v>73.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I46" t="n">
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>47.41</v>
+        <v>29.92</v>
       </c>
       <c r="K46" t="n">
-        <v>74.31999999999999</v>
+        <v>54.28</v>
       </c>
       <c r="L46" t="n">
-        <v>88.16</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:14:10</t>
+          <t>06:17:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.42</v>
+        <v>3.29</v>
       </c>
       <c r="F47" t="n">
-        <v>12.43</v>
+        <v>10.52</v>
       </c>
       <c r="G47" t="n">
-        <v>188.2</v>
+        <v>185.6</v>
       </c>
       <c r="H47" t="n">
-        <v>77.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>63.28</v>
+        <v>9.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-18</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>65.79000000000001</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:15:44</t>
+          <t>06:19:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="F48" t="n">
-        <v>11.87</v>
+        <v>11.65</v>
       </c>
       <c r="G48" t="n">
-        <v>187.8</v>
+        <v>174.8</v>
       </c>
       <c r="H48" t="n">
-        <v>83.7</v>
+        <v>77.2</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-61.91</v>
+        <v>-28.69</v>
       </c>
       <c r="K48" t="n">
-        <v>18.57</v>
+        <v>-98.37</v>
       </c>
       <c r="L48" t="n">
-        <v>64.63</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:17:44</t>
+          <t>06:22:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="F49" t="n">
-        <v>12.37</v>
+        <v>8.84</v>
       </c>
       <c r="G49" t="n">
-        <v>180.9</v>
+        <v>191.4</v>
       </c>
       <c r="H49" t="n">
-        <v>81.2</v>
+        <v>88.7</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-71.97</v>
+        <v>-30.12</v>
       </c>
       <c r="K49" t="n">
-        <v>0.33</v>
+        <v>58.13</v>
       </c>
       <c r="L49" t="n">
-        <v>71.98</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:22:45</t>
+          <t>06:27:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.01</v>
+        <v>4.54</v>
       </c>
       <c r="F50" t="n">
-        <v>11.9</v>
+        <v>12.55</v>
       </c>
       <c r="G50" t="n">
-        <v>191.8</v>
+        <v>188.9</v>
       </c>
       <c r="H50" t="n">
-        <v>79.2</v>
+        <v>74.7</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-133.16</v>
+        <v>-60.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-44.02</v>
+        <v>-140.9</v>
       </c>
       <c r="L50" t="n">
-        <v>140.24</v>
+        <v>153.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:58</t>
+          <t>06:29:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="F51" t="n">
-        <v>13.05</v>
+        <v>13.98</v>
       </c>
       <c r="G51" t="n">
-        <v>185.8</v>
+        <v>189.2</v>
       </c>
       <c r="H51" t="n">
-        <v>74.7</v>
+        <v>80.5</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.34</v>
+        <v>-43.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-40.25</v>
+        <v>183.22</v>
       </c>
       <c r="L51" t="n">
-        <v>75.05</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:12</t>
+          <t>06:30:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.04</v>
+        <v>4.25</v>
       </c>
       <c r="F52" t="n">
-        <v>11.65</v>
+        <v>14.03</v>
       </c>
       <c r="G52" t="n">
-        <v>182</v>
+        <v>197.4</v>
       </c>
       <c r="H52" t="n">
-        <v>78.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-118.76</v>
+        <v>-31.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.46</v>
+        <v>-154.44</v>
       </c>
       <c r="L52" t="n">
-        <v>127.89</v>
+        <v>157.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:33</t>
+          <t>06:36:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="F53" t="n">
-        <v>12.25</v>
+        <v>11.82</v>
       </c>
       <c r="G53" t="n">
-        <v>175.3</v>
+        <v>190.7</v>
       </c>
       <c r="H53" t="n">
-        <v>81.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-41.03</v>
+        <v>-177.89</v>
       </c>
       <c r="K53" t="n">
-        <v>205.79</v>
+        <v>-130.37</v>
       </c>
       <c r="L53" t="n">
-        <v>209.84</v>
+        <v>220.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:34</t>
+          <t>06:37:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="F54" t="n">
-        <v>12.67</v>
+        <v>14.03</v>
       </c>
       <c r="G54" t="n">
-        <v>180.8</v>
+        <v>185.6</v>
       </c>
       <c r="H54" t="n">
-        <v>93</v>
+        <v>79.3</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.58</v>
+        <v>61.1</v>
       </c>
       <c r="K54" t="n">
-        <v>-180.85</v>
+        <v>-146</v>
       </c>
       <c r="L54" t="n">
-        <v>183.25</v>
+        <v>158.27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:38</t>
+          <t>06:39:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.99</v>
+        <v>3.81</v>
       </c>
       <c r="F55" t="n">
-        <v>12.33</v>
+        <v>12.83</v>
       </c>
       <c r="G55" t="n">
-        <v>183.6</v>
+        <v>191.6</v>
       </c>
       <c r="H55" t="n">
-        <v>84.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-168.67</v>
+        <v>-85.69</v>
       </c>
       <c r="K55" t="n">
-        <v>-101.2</v>
+        <v>-193.12</v>
       </c>
       <c r="L55" t="n">
-        <v>196.7</v>
+        <v>211.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:37:41</t>
+          <t>06:44:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="F56" t="n">
-        <v>12.07</v>
+        <v>12.61</v>
       </c>
       <c r="G56" t="n">
-        <v>186.4</v>
+        <v>183.3</v>
       </c>
       <c r="H56" t="n">
-        <v>85.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>103.1</v>
+        <v>23.15</v>
       </c>
       <c r="K56" t="n">
-        <v>-163.6</v>
+        <v>-256.67</v>
       </c>
       <c r="L56" t="n">
-        <v>193.38</v>
+        <v>257.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:40:11</t>
+          <t>06:45:59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="F57" t="n">
-        <v>12.37</v>
+        <v>9.56</v>
       </c>
       <c r="G57" t="n">
-        <v>181.9</v>
+        <v>176.7</v>
       </c>
       <c r="H57" t="n">
-        <v>77.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-101.36</v>
+        <v>187.82</v>
       </c>
       <c r="K57" t="n">
-        <v>-222.49</v>
+        <v>137.29</v>
       </c>
       <c r="L57" t="n">
-        <v>244.5</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:42:11</t>
+          <t>06:47:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.39</v>
+        <v>4.06</v>
       </c>
       <c r="F58" t="n">
-        <v>11.96</v>
+        <v>14.03</v>
       </c>
       <c r="G58" t="n">
-        <v>187.7</v>
+        <v>179.7</v>
       </c>
       <c r="H58" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I58" t="n">
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>21.56</v>
+        <v>279.22</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.29</v>
+        <v>217.43</v>
       </c>
       <c r="L58" t="n">
-        <v>202.44</v>
+        <v>353.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:54:06</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.79</v>
+        <v>3.62</v>
       </c>
       <c r="F59" t="n">
-        <v>11.63</v>
+        <v>10.72</v>
       </c>
       <c r="G59" t="n">
-        <v>190.6</v>
+        <v>172.4</v>
       </c>
       <c r="H59" t="n">
-        <v>80.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>44.18</v>
+        <v>41.09</v>
       </c>
       <c r="K59" t="n">
-        <v>55.15</v>
+        <v>52.67</v>
       </c>
       <c r="L59" t="n">
-        <v>70.66</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:18</t>
+          <t>07:01:37</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="F60" t="n">
-        <v>11.78</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>185.7</v>
+        <v>188.9</v>
       </c>
       <c r="H60" t="n">
-        <v>88.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I60" t="n">
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>67.89</v>
+        <v>-34.56</v>
       </c>
       <c r="K60" t="n">
-        <v>67.34999999999999</v>
+        <v>-46.09</v>
       </c>
       <c r="L60" t="n">
-        <v>95.63</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:47</t>
+          <t>07:02:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.61</v>
+        <v>3.87</v>
       </c>
       <c r="F61" t="n">
-        <v>11.41</v>
+        <v>10.27</v>
       </c>
       <c r="G61" t="n">
-        <v>177.8</v>
+        <v>185.7</v>
       </c>
       <c r="H61" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>29.64</v>
+        <v>9.32</v>
       </c>
       <c r="K61" t="n">
-        <v>40.45</v>
+        <v>-55.73</v>
       </c>
       <c r="L61" t="n">
-        <v>50.15</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:31</t>
+          <t>07:08:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
       <c r="F62" t="n">
-        <v>12.24</v>
+        <v>13.27</v>
       </c>
       <c r="G62" t="n">
-        <v>181.4</v>
+        <v>188.6</v>
       </c>
       <c r="H62" t="n">
-        <v>74.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-36.27</v>
+        <v>-33.87</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.24</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>61.16</v>
+        <v>95.13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:10</t>
+          <t>07:10:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.87</v>
+        <v>4.21</v>
       </c>
       <c r="F63" t="n">
-        <v>12.08</v>
+        <v>13.85</v>
       </c>
       <c r="G63" t="n">
-        <v>189.3</v>
+        <v>185.6</v>
       </c>
       <c r="H63" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>8.41</v>
+        <v>91.66</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.46</v>
+        <v>-46.15</v>
       </c>
       <c r="L63" t="n">
-        <v>53.13</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:07:37</t>
+          <t>07:12:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="F64" t="n">
-        <v>12.23</v>
+        <v>14.03</v>
       </c>
       <c r="G64" t="n">
-        <v>178.2</v>
+        <v>194.7</v>
       </c>
       <c r="H64" t="n">
-        <v>82.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.31</v>
+        <v>-91.31</v>
       </c>
       <c r="K64" t="n">
-        <v>75.09</v>
+        <v>-132.67</v>
       </c>
       <c r="L64" t="n">
-        <v>79.56</v>
+        <v>161.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:12:44</t>
+          <t>07:17:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="F65" t="n">
-        <v>12.07</v>
+        <v>14.03</v>
       </c>
       <c r="G65" t="n">
-        <v>173.9</v>
+        <v>187.1</v>
       </c>
       <c r="H65" t="n">
-        <v>81.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>124.88</v>
+        <v>160.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-61.65</v>
+        <v>51.02</v>
       </c>
       <c r="L65" t="n">
-        <v>139.27</v>
+        <v>167.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:15:03</t>
+          <t>07:18:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="F66" t="n">
-        <v>12.53</v>
+        <v>12.66</v>
       </c>
       <c r="G66" t="n">
-        <v>187</v>
+        <v>187.1</v>
       </c>
       <c r="H66" t="n">
-        <v>84.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-111.18</v>
+        <v>-22.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-162.97</v>
+        <v>-147.77</v>
       </c>
       <c r="L66" t="n">
-        <v>197.29</v>
+        <v>149.44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:16:31</t>
+          <t>07:21:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="F67" t="n">
-        <v>12.15</v>
+        <v>14.03</v>
       </c>
       <c r="G67" t="n">
-        <v>183.6</v>
+        <v>175.5</v>
       </c>
       <c r="H67" t="n">
-        <v>77.5</v>
+        <v>87.8</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>138.09</v>
+        <v>-79.8</v>
       </c>
       <c r="K67" t="n">
-        <v>56.26</v>
+        <v>137.84</v>
       </c>
       <c r="L67" t="n">
-        <v>149.11</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:21:03</t>
+          <t>07:27:33</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="F68" t="n">
-        <v>12.15</v>
+        <v>11.65</v>
       </c>
       <c r="G68" t="n">
-        <v>185</v>
+        <v>197.2</v>
       </c>
       <c r="H68" t="n">
-        <v>79.2</v>
+        <v>74.7</v>
       </c>
       <c r="I68" t="n">
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-23.43</v>
+        <v>179.43</v>
       </c>
       <c r="K68" t="n">
-        <v>-158.01</v>
+        <v>2.14</v>
       </c>
       <c r="L68" t="n">
-        <v>159.74</v>
+        <v>179.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:22:15</t>
+          <t>07:29:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.44</v>
+        <v>3.03</v>
       </c>
       <c r="F69" t="n">
-        <v>11.57</v>
+        <v>10.48</v>
       </c>
       <c r="G69" t="n">
-        <v>203.3</v>
+        <v>179.3</v>
       </c>
       <c r="H69" t="n">
-        <v>73.7</v>
+        <v>78</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-85.84</v>
+        <v>131.8</v>
       </c>
       <c r="K69" t="n">
-        <v>144.87</v>
+        <v>53.1</v>
       </c>
       <c r="L69" t="n">
-        <v>168.4</v>
+        <v>142.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:23:55</t>
+          <t>07:31:36</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.13</v>
+        <v>3.82</v>
       </c>
       <c r="F70" t="n">
-        <v>12.65</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>177.1</v>
+        <v>167.9</v>
       </c>
       <c r="H70" t="n">
-        <v>77</v>
+        <v>79.7</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>174.22</v>
+        <v>-25.67</v>
       </c>
       <c r="K70" t="n">
-        <v>31.32</v>
+        <v>213.43</v>
       </c>
       <c r="L70" t="n">
-        <v>177.01</v>
+        <v>214.97</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:29:33</t>
+          <t>07:36:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.03</v>
+        <v>3.38</v>
       </c>
       <c r="F71" t="n">
-        <v>11.76</v>
+        <v>11.16</v>
       </c>
       <c r="G71" t="n">
-        <v>183.6</v>
+        <v>193.7</v>
       </c>
       <c r="H71" t="n">
-        <v>78.7</v>
+        <v>81</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>124.78</v>
+        <v>-196.13</v>
       </c>
       <c r="K71" t="n">
-        <v>98.39</v>
+        <v>-99.28</v>
       </c>
       <c r="L71" t="n">
-        <v>158.91</v>
+        <v>219.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:28</t>
+          <t>07:38:14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="F72" t="n">
-        <v>11.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>187.1</v>
+        <v>188.4</v>
       </c>
       <c r="H72" t="n">
-        <v>74.8</v>
+        <v>83.8</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-44.33</v>
+        <v>-269.36</v>
       </c>
       <c r="K72" t="n">
-        <v>280.73</v>
+        <v>-217.76</v>
       </c>
       <c r="L72" t="n">
-        <v>284.21</v>
+        <v>346.37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:33:55</t>
+          <t>07:40:22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.37</v>
+        <v>4.56</v>
       </c>
       <c r="F73" t="n">
-        <v>12.48</v>
+        <v>14.03</v>
       </c>
       <c r="G73" t="n">
-        <v>189.7</v>
+        <v>177.1</v>
       </c>
       <c r="H73" t="n">
-        <v>87.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.05</v>
+        <v>233.31</v>
       </c>
       <c r="K73" t="n">
-        <v>-22.97</v>
+        <v>-47.08</v>
       </c>
       <c r="L73" t="n">
-        <v>153.77</v>
+        <v>238.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:43:53</t>
+          <t>07:48:14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="F74" t="n">
-        <v>12.22</v>
+        <v>13.03</v>
       </c>
       <c r="G74" t="n">
-        <v>195.2</v>
+        <v>185.8</v>
       </c>
       <c r="H74" t="n">
-        <v>73.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-72.97</v>
+        <v>-63.68</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.53</v>
+        <v>68.77</v>
       </c>
       <c r="L74" t="n">
-        <v>85.48</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:45:32</t>
+          <t>07:50:33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.57</v>
+        <v>3.67</v>
       </c>
       <c r="F75" t="n">
-        <v>11.65</v>
+        <v>13.08</v>
       </c>
       <c r="G75" t="n">
-        <v>187.9</v>
+        <v>172.3</v>
       </c>
       <c r="H75" t="n">
-        <v>76.7</v>
+        <v>75.3</v>
       </c>
       <c r="I75" t="n">
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>43.38</v>
+        <v>37.54</v>
       </c>
       <c r="K75" t="n">
-        <v>34.04</v>
+        <v>-79.26000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>55.14</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:47:43</t>
+          <t>07:52:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.76</v>
+        <v>4.16</v>
       </c>
       <c r="F76" t="n">
-        <v>12.09</v>
+        <v>12.9</v>
       </c>
       <c r="G76" t="n">
-        <v>186.4</v>
+        <v>187.5</v>
       </c>
       <c r="H76" t="n">
-        <v>82.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.76</v>
+        <v>-76.01000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>54.91</v>
+        <v>-45.19</v>
       </c>
       <c r="L76" t="n">
-        <v>74.09999999999999</v>
+        <v>88.43000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:52:34</t>
+          <t>07:55:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="F77" t="n">
-        <v>11.41</v>
+        <v>14.03</v>
       </c>
       <c r="G77" t="n">
-        <v>178.4</v>
+        <v>183.1</v>
       </c>
       <c r="H77" t="n">
-        <v>78.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>35.91</v>
+        <v>-56.46</v>
       </c>
       <c r="K77" t="n">
-        <v>-76.44</v>
+        <v>103.4</v>
       </c>
       <c r="L77" t="n">
-        <v>84.45999999999999</v>
+        <v>117.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:54:45</t>
+          <t>07:56:35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="F78" t="n">
-        <v>12.17</v>
+        <v>14.03</v>
       </c>
       <c r="G78" t="n">
-        <v>178.9</v>
+        <v>177.1</v>
       </c>
       <c r="H78" t="n">
-        <v>79.3</v>
+        <v>82</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.70999999999999</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-42.82</v>
+        <v>-67.79000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>83.52</v>
+        <v>111.51</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:56:48</t>
+          <t>07:58:17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.77</v>
+        <v>4.52</v>
       </c>
       <c r="F79" t="n">
-        <v>11.95</v>
+        <v>14.03</v>
       </c>
       <c r="G79" t="n">
-        <v>170.5</v>
+        <v>181.1</v>
       </c>
       <c r="H79" t="n">
-        <v>78.8</v>
+        <v>77.8</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.02</v>
+        <v>19.3</v>
       </c>
       <c r="K79" t="n">
-        <v>80.94</v>
+        <v>74.13</v>
       </c>
       <c r="L79" t="n">
-        <v>91.2</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:02:33</t>
+          <t>08:02:05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="F80" t="n">
-        <v>11.65</v>
+        <v>13.09</v>
       </c>
       <c r="G80" t="n">
-        <v>191.7</v>
+        <v>196.7</v>
       </c>
       <c r="H80" t="n">
-        <v>84.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>106.3</v>
+        <v>20.35</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.81</v>
+        <v>-108.81</v>
       </c>
       <c r="L80" t="n">
-        <v>134.75</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:03:53</t>
+          <t>08:04:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.53</v>
+        <v>4.84</v>
       </c>
       <c r="F81" t="n">
-        <v>11.85</v>
+        <v>13.62</v>
       </c>
       <c r="G81" t="n">
-        <v>183.2</v>
+        <v>174.6</v>
       </c>
       <c r="H81" t="n">
-        <v>74.7</v>
+        <v>80.5</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>21.56</v>
+        <v>-69.44</v>
       </c>
       <c r="K81" t="n">
-        <v>87.09</v>
+        <v>-153.07</v>
       </c>
       <c r="L81" t="n">
-        <v>89.72</v>
+        <v>168.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:05:01</t>
+          <t>08:05:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="F82" t="n">
-        <v>12.63</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>179.9</v>
+        <v>189.1</v>
       </c>
       <c r="H82" t="n">
-        <v>80.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>35.26</v>
+        <v>51.89</v>
       </c>
       <c r="K82" t="n">
-        <v>-85.48</v>
+        <v>-107.39</v>
       </c>
       <c r="L82" t="n">
-        <v>92.45999999999999</v>
+        <v>119.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:10:21</t>
+          <t>08:10:53</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.85</v>
+        <v>4.77</v>
       </c>
       <c r="F83" t="n">
-        <v>11.53</v>
+        <v>14.03</v>
       </c>
       <c r="G83" t="n">
-        <v>188.8</v>
+        <v>193.7</v>
       </c>
       <c r="H83" t="n">
-        <v>84.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-91.09999999999999</v>
+        <v>75.63</v>
       </c>
       <c r="K83" t="n">
-        <v>-163.28</v>
+        <v>-280.66</v>
       </c>
       <c r="L83" t="n">
-        <v>186.97</v>
+        <v>290.67</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:11:52</t>
+          <t>08:12:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.73</v>
+        <v>4.31</v>
       </c>
       <c r="F84" t="n">
-        <v>12.25</v>
+        <v>14.03</v>
       </c>
       <c r="G84" t="n">
-        <v>181.4</v>
+        <v>198.1</v>
       </c>
       <c r="H84" t="n">
-        <v>72.3</v>
+        <v>80</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>74.81999999999999</v>
+        <v>-83.31</v>
       </c>
       <c r="K84" t="n">
-        <v>-133.69</v>
+        <v>134.82</v>
       </c>
       <c r="L84" t="n">
-        <v>153.2</v>
+        <v>158.48</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:12:49</t>
+          <t>08:13:14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.77</v>
+        <v>4.49</v>
       </c>
       <c r="F85" t="n">
-        <v>12.48</v>
+        <v>10.25</v>
       </c>
       <c r="G85" t="n">
-        <v>181.1</v>
+        <v>178.1</v>
       </c>
       <c r="H85" t="n">
-        <v>82.2</v>
+        <v>85.7</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>74.92</v>
+        <v>98.37</v>
       </c>
       <c r="K85" t="n">
-        <v>-218.31</v>
+        <v>-153.83</v>
       </c>
       <c r="L85" t="n">
-        <v>230.8</v>
+        <v>182.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:17:27</t>
+          <t>08:17:43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.32</v>
+        <v>3.41</v>
       </c>
       <c r="F86" t="n">
-        <v>12.7</v>
+        <v>14.03</v>
       </c>
       <c r="G86" t="n">
-        <v>187.7</v>
+        <v>181.7</v>
       </c>
       <c r="H86" t="n">
-        <v>84.8</v>
+        <v>76.7</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-54.22</v>
+        <v>261.26</v>
       </c>
       <c r="K86" t="n">
-        <v>200.49</v>
+        <v>-139.6</v>
       </c>
       <c r="L86" t="n">
-        <v>207.69</v>
+        <v>296.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:19:09</t>
+          <t>08:19:37</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="F87" t="n">
-        <v>11.7</v>
+        <v>13.89</v>
       </c>
       <c r="G87" t="n">
-        <v>199.2</v>
+        <v>197.4</v>
       </c>
       <c r="H87" t="n">
-        <v>76.3</v>
+        <v>75.3</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>152.6</v>
+        <v>-255.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-225.18</v>
+        <v>-330.83</v>
       </c>
       <c r="L87" t="n">
-        <v>272.01</v>
+        <v>417.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:27</t>
+          <t>08:20:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="F88" t="n">
-        <v>11.88</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>181.2</v>
+        <v>180.7</v>
       </c>
       <c r="H88" t="n">
-        <v>88.5</v>
+        <v>75.8</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>198.47</v>
+        <v>265.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-67.38</v>
+        <v>-104.84</v>
       </c>
       <c r="L88" t="n">
-        <v>209.59</v>
+        <v>285.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.61</v>
+        <v>-51.48</v>
       </c>
       <c r="K14" t="n">
-        <v>-47.91</v>
+        <v>-47.79</v>
       </c>
       <c r="L14" t="n">
-        <v>70.42</v>
+        <v>70.23999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.68</v>
+        <v>-17.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-55.05</v>
+        <v>-60.05</v>
       </c>
       <c r="L15" t="n">
-        <v>57.24</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>34.63</v>
+        <v>35.31</v>
       </c>
       <c r="K16" t="n">
-        <v>16.92</v>
+        <v>17.25</v>
       </c>
       <c r="L16" t="n">
-        <v>38.55</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-119.83</v>
+        <v>-130.72</v>
       </c>
       <c r="K17" t="n">
-        <v>-39.1</v>
+        <v>-42.66</v>
       </c>
       <c r="L17" t="n">
-        <v>126.04</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="18">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-35.06</v>
+        <v>-38.81</v>
       </c>
       <c r="K19" t="n">
-        <v>-114.71</v>
+        <v>-127</v>
       </c>
       <c r="L19" t="n">
-        <v>119.95</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.97</v>
+        <v>-3.19</v>
       </c>
       <c r="K20" t="n">
-        <v>113.54</v>
+        <v>121.94</v>
       </c>
       <c r="L20" t="n">
-        <v>113.57</v>
+        <v>121.98</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.4</v>
+        <v>-10.99</v>
       </c>
       <c r="K21" t="n">
-        <v>99.51000000000001</v>
+        <v>105.12</v>
       </c>
       <c r="L21" t="n">
-        <v>100.05</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>36.17</v>
+        <v>39.46</v>
       </c>
       <c r="K22" t="n">
-        <v>140.28</v>
+        <v>153.03</v>
       </c>
       <c r="L22" t="n">
-        <v>144.87</v>
+        <v>158.04</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>151.78</v>
+        <v>163.13</v>
       </c>
       <c r="K23" t="n">
-        <v>-25.36</v>
+        <v>-27.25</v>
       </c>
       <c r="L23" t="n">
-        <v>153.88</v>
+        <v>165.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-12.48</v>
+        <v>-13.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-79.69</v>
+        <v>-84.22</v>
       </c>
       <c r="L24" t="n">
-        <v>80.66</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-137.98</v>
+        <v>-148.28</v>
       </c>
       <c r="K25" t="n">
-        <v>30.57</v>
+        <v>32.85</v>
       </c>
       <c r="L25" t="n">
-        <v>141.32</v>
+        <v>151.88</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>262.88</v>
+        <v>276.83</v>
       </c>
       <c r="K26" t="n">
-        <v>-100.25</v>
+        <v>-105.57</v>
       </c>
       <c r="L26" t="n">
-        <v>281.35</v>
+        <v>296.28</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-148.64</v>
+        <v>-162.61</v>
       </c>
       <c r="K27" t="n">
-        <v>236.92</v>
+        <v>259.2</v>
       </c>
       <c r="L27" t="n">
-        <v>279.69</v>
+        <v>305.99</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-210.52</v>
+        <v>-219.31</v>
       </c>
       <c r="K28" t="n">
-        <v>204.21</v>
+        <v>212.74</v>
       </c>
       <c r="L28" t="n">
-        <v>293.29</v>
+        <v>305.54</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-101.77</v>
+        <v>-103.26</v>
       </c>
       <c r="K29" t="n">
-        <v>41.94</v>
+        <v>42.55</v>
       </c>
       <c r="L29" t="n">
-        <v>110.07</v>
+        <v>111.68</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="K30" t="n">
-        <v>66.23999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="L30" t="n">
-        <v>66.28</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>19.06</v>
+        <v>20.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-74.14</v>
+        <v>-80.73</v>
       </c>
       <c r="L31" t="n">
-        <v>76.55</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>80.73</v>
+        <v>85.02</v>
       </c>
       <c r="K32" t="n">
-        <v>96.58</v>
+        <v>101.71</v>
       </c>
       <c r="L32" t="n">
-        <v>125.88</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.90000000000001</v>
+        <v>-81.11</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.97</v>
+        <v>-49.54</v>
       </c>
       <c r="L33" t="n">
-        <v>90.11</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-40.05</v>
+        <v>-42.26</v>
       </c>
       <c r="K34" t="n">
-        <v>97.84999999999999</v>
+        <v>103.25</v>
       </c>
       <c r="L34" t="n">
-        <v>105.73</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-75.23999999999999</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>137.1</v>
+        <v>137</v>
       </c>
       <c r="L35" t="n">
-        <v>156.39</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-137.97</v>
+        <v>-147.99</v>
       </c>
       <c r="K36" t="n">
-        <v>47.54</v>
+        <v>50.99</v>
       </c>
       <c r="L36" t="n">
-        <v>145.93</v>
+        <v>156.53</v>
       </c>
     </row>
     <row r="37">
@@ -1609,10 +1609,10 @@
         <v>1.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-135.51</v>
+        <v>-135.33</v>
       </c>
       <c r="L37" t="n">
-        <v>135.51</v>
+        <v>135.33</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>36.23</v>
+        <v>36.97</v>
       </c>
       <c r="K38" t="n">
-        <v>152.56</v>
+        <v>155.67</v>
       </c>
       <c r="L38" t="n">
-        <v>156.81</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="K39" t="n">
-        <v>139.56</v>
+        <v>147.56</v>
       </c>
       <c r="L39" t="n">
-        <v>139.56</v>
+        <v>147.57</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-165.17</v>
+        <v>-180.18</v>
       </c>
       <c r="K40" t="n">
-        <v>20.09</v>
+        <v>21.92</v>
       </c>
       <c r="L40" t="n">
-        <v>166.39</v>
+        <v>181.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>283.41</v>
+        <v>284.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-17.28</v>
+        <v>-17.32</v>
       </c>
       <c r="L41" t="n">
-        <v>283.94</v>
+        <v>284.71</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>132.2</v>
+        <v>137.28</v>
       </c>
       <c r="K42" t="n">
-        <v>-166.41</v>
+        <v>-172.81</v>
       </c>
       <c r="L42" t="n">
-        <v>212.53</v>
+        <v>220.71</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-140.71</v>
+        <v>-153.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-198.81</v>
+        <v>-217</v>
       </c>
       <c r="L43" t="n">
-        <v>243.57</v>
+        <v>265.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>84.2</v>
+        <v>92.97</v>
       </c>
       <c r="K44" t="n">
-        <v>67.34</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>107.81</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.06</v>
+        <v>-12.69</v>
       </c>
       <c r="K45" t="n">
-        <v>65.73999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>66.83</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>29.92</v>
+        <v>30.91</v>
       </c>
       <c r="K46" t="n">
-        <v>54.28</v>
+        <v>56.08</v>
       </c>
       <c r="L46" t="n">
-        <v>61.98</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>9.48</v>
+        <v>10.02</v>
       </c>
       <c r="K47" t="n">
-        <v>65.15000000000001</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>65.83</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-28.69</v>
+        <v>-31.26</v>
       </c>
       <c r="K48" t="n">
-        <v>-98.37</v>
+        <v>-107.17</v>
       </c>
       <c r="L48" t="n">
-        <v>102.47</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-30.12</v>
+        <v>-31.75</v>
       </c>
       <c r="K49" t="n">
-        <v>58.13</v>
+        <v>61.28</v>
       </c>
       <c r="L49" t="n">
-        <v>65.47</v>
+        <v>69.01000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-60.3</v>
+        <v>-65.64</v>
       </c>
       <c r="K50" t="n">
-        <v>-140.9</v>
+        <v>-153.39</v>
       </c>
       <c r="L50" t="n">
-        <v>153.26</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-43.97</v>
+        <v>-47.88</v>
       </c>
       <c r="K51" t="n">
-        <v>183.22</v>
+        <v>199.53</v>
       </c>
       <c r="L51" t="n">
-        <v>188.42</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-31.14</v>
+        <v>-31.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-154.44</v>
+        <v>-157.21</v>
       </c>
       <c r="L52" t="n">
-        <v>157.55</v>
+        <v>160.37</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-177.89</v>
+        <v>-188.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-130.37</v>
+        <v>-137.87</v>
       </c>
       <c r="L53" t="n">
-        <v>220.54</v>
+        <v>233.23</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>61.1</v>
+        <v>62.35</v>
       </c>
       <c r="K54" t="n">
-        <v>-146</v>
+        <v>-148.98</v>
       </c>
       <c r="L54" t="n">
-        <v>158.27</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-85.69</v>
+        <v>-90.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-193.12</v>
+        <v>-204.18</v>
       </c>
       <c r="L55" t="n">
-        <v>211.27</v>
+        <v>223.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>23.15</v>
+        <v>24.81</v>
       </c>
       <c r="K56" t="n">
-        <v>-256.67</v>
+        <v>-275.05</v>
       </c>
       <c r="L56" t="n">
-        <v>257.71</v>
+        <v>276.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>187.82</v>
+        <v>202.58</v>
       </c>
       <c r="K57" t="n">
-        <v>137.29</v>
+        <v>148.09</v>
       </c>
       <c r="L57" t="n">
-        <v>232.65</v>
+        <v>250.93</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>279.22</v>
+        <v>286.47</v>
       </c>
       <c r="K58" t="n">
-        <v>217.43</v>
+        <v>223.07</v>
       </c>
       <c r="L58" t="n">
-        <v>353.89</v>
+        <v>363.08</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>41.09</v>
+        <v>45.41</v>
       </c>
       <c r="K59" t="n">
-        <v>52.67</v>
+        <v>58.2</v>
       </c>
       <c r="L59" t="n">
-        <v>66.8</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.56</v>
+        <v>-34.45</v>
       </c>
       <c r="K60" t="n">
-        <v>-46.09</v>
+        <v>-45.94</v>
       </c>
       <c r="L60" t="n">
-        <v>57.61</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>9.32</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-55.73</v>
+        <v>-56.66</v>
       </c>
       <c r="L61" t="n">
-        <v>56.51</v>
+        <v>57.44</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-33.87</v>
+        <v>-35.07</v>
       </c>
       <c r="K62" t="n">
-        <v>88.90000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="L62" t="n">
-        <v>95.13</v>
+        <v>98.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>91.66</v>
+        <v>94.75</v>
       </c>
       <c r="K63" t="n">
-        <v>-46.15</v>
+        <v>-47.71</v>
       </c>
       <c r="L63" t="n">
-        <v>102.62</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-91.31</v>
+        <v>-100.68</v>
       </c>
       <c r="K64" t="n">
-        <v>-132.67</v>
+        <v>-146.27</v>
       </c>
       <c r="L64" t="n">
-        <v>161.06</v>
+        <v>177.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>160.05</v>
+        <v>159.77</v>
       </c>
       <c r="K65" t="n">
-        <v>51.02</v>
+        <v>50.93</v>
       </c>
       <c r="L65" t="n">
-        <v>167.99</v>
+        <v>167.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.27</v>
+        <v>-22.67</v>
       </c>
       <c r="K66" t="n">
-        <v>-147.77</v>
+        <v>-150.44</v>
       </c>
       <c r="L66" t="n">
-        <v>149.44</v>
+        <v>152.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-79.8</v>
+        <v>-85.55</v>
       </c>
       <c r="K67" t="n">
-        <v>137.84</v>
+        <v>147.77</v>
       </c>
       <c r="L67" t="n">
-        <v>159.28</v>
+        <v>170.75</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>179.43</v>
+        <v>179.61</v>
       </c>
       <c r="K68" t="n">
         <v>2.14</v>
       </c>
       <c r="L68" t="n">
-        <v>179.44</v>
+        <v>179.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>131.8</v>
+        <v>139.26</v>
       </c>
       <c r="K69" t="n">
-        <v>53.1</v>
+        <v>56.1</v>
       </c>
       <c r="L69" t="n">
-        <v>142.09</v>
+        <v>150.13</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-25.67</v>
+        <v>-26.19</v>
       </c>
       <c r="K70" t="n">
-        <v>213.43</v>
+        <v>217.76</v>
       </c>
       <c r="L70" t="n">
-        <v>214.97</v>
+        <v>219.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-196.13</v>
+        <v>-214.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-99.28</v>
+        <v>-108.43</v>
       </c>
       <c r="L71" t="n">
-        <v>219.83</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-269.36</v>
+        <v>-295.21</v>
       </c>
       <c r="K72" t="n">
-        <v>-217.76</v>
+        <v>-238.66</v>
       </c>
       <c r="L72" t="n">
-        <v>346.37</v>
+        <v>379.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>233.31</v>
+        <v>241.56</v>
       </c>
       <c r="K73" t="n">
-        <v>-47.08</v>
+        <v>-48.74</v>
       </c>
       <c r="L73" t="n">
-        <v>238.01</v>
+        <v>246.43</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.68</v>
+        <v>-70.33</v>
       </c>
       <c r="K74" t="n">
-        <v>68.77</v>
+        <v>75.95</v>
       </c>
       <c r="L74" t="n">
-        <v>93.73</v>
+        <v>103.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>37.54</v>
+        <v>40.87</v>
       </c>
       <c r="K75" t="n">
-        <v>-79.26000000000001</v>
+        <v>-86.29000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>87.7</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-76.01000000000001</v>
+        <v>-81.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.19</v>
+        <v>-48.33</v>
       </c>
       <c r="L76" t="n">
-        <v>88.43000000000001</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.46</v>
+        <v>-62.35</v>
       </c>
       <c r="K77" t="n">
-        <v>103.4</v>
+        <v>114.19</v>
       </c>
       <c r="L77" t="n">
-        <v>117.81</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>88.54000000000001</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-67.79000000000001</v>
+        <v>-72.61</v>
       </c>
       <c r="L78" t="n">
-        <v>111.51</v>
+        <v>119.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="K79" t="n">
-        <v>74.13</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>76.59999999999999</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>20.35</v>
+        <v>20.32</v>
       </c>
       <c r="K80" t="n">
-        <v>-108.81</v>
+        <v>-108.67</v>
       </c>
       <c r="L80" t="n">
-        <v>110.69</v>
+        <v>110.56</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-69.44</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-153.07</v>
+        <v>-166.58</v>
       </c>
       <c r="L81" t="n">
-        <v>168.08</v>
+        <v>182.92</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>51.89</v>
+        <v>51.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-107.39</v>
+        <v>-107.3</v>
       </c>
       <c r="L82" t="n">
-        <v>119.27</v>
+        <v>119.17</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>75.63</v>
+        <v>83.19</v>
       </c>
       <c r="K83" t="n">
-        <v>-280.66</v>
+        <v>-308.74</v>
       </c>
       <c r="L83" t="n">
-        <v>290.67</v>
+        <v>319.75</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-83.31</v>
+        <v>-89.59</v>
       </c>
       <c r="K84" t="n">
-        <v>134.82</v>
+        <v>144.98</v>
       </c>
       <c r="L84" t="n">
-        <v>158.48</v>
+        <v>170.43</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>98.37</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-153.83</v>
+        <v>-154.05</v>
       </c>
       <c r="L85" t="n">
-        <v>182.59</v>
+        <v>182.85</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>261.26</v>
+        <v>289.66</v>
       </c>
       <c r="K86" t="n">
-        <v>-139.6</v>
+        <v>-154.77</v>
       </c>
       <c r="L86" t="n">
-        <v>296.22</v>
+        <v>328.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-255.01</v>
+        <v>-270.93</v>
       </c>
       <c r="K87" t="n">
-        <v>-330.83</v>
+        <v>-351.48</v>
       </c>
       <c r="L87" t="n">
-        <v>417.71</v>
+        <v>443.77</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>265.4</v>
+        <v>276.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-104.84</v>
+        <v>-109.32</v>
       </c>
       <c r="L88" t="n">
-        <v>285.35</v>
+        <v>297.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="F14" t="n">
-        <v>9.550000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="G14" t="n">
-        <v>186.2</v>
+        <v>172.7</v>
       </c>
       <c r="H14" t="n">
-        <v>78.40000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.48</v>
+        <v>60.42</v>
       </c>
       <c r="K14" t="n">
-        <v>-47.79</v>
+        <v>15.13</v>
       </c>
       <c r="L14" t="n">
-        <v>70.23999999999999</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:32:38</t>
+          <t>04:32:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.05</v>
+        <v>4.32</v>
       </c>
       <c r="F15" t="n">
-        <v>9.33</v>
+        <v>11.45</v>
       </c>
       <c r="G15" t="n">
-        <v>196.4</v>
+        <v>186.8</v>
       </c>
       <c r="H15" t="n">
-        <v>85.3</v>
+        <v>59.6</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.11</v>
+        <v>48.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.05</v>
+        <v>20.93</v>
       </c>
       <c r="L15" t="n">
-        <v>62.44</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:34:29</t>
+          <t>04:33:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>3.59</v>
       </c>
       <c r="F16" t="n">
-        <v>8.82</v>
+        <v>12.14</v>
       </c>
       <c r="G16" t="n">
-        <v>179</v>
+        <v>187.6</v>
       </c>
       <c r="H16" t="n">
-        <v>82.8</v>
+        <v>42.6</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>35.31</v>
+        <v>-46.86</v>
       </c>
       <c r="K16" t="n">
-        <v>17.25</v>
+        <v>22.35</v>
       </c>
       <c r="L16" t="n">
-        <v>39.3</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:39:53</t>
+          <t>04:38:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="F17" t="n">
-        <v>13.2</v>
+        <v>8.27</v>
       </c>
       <c r="G17" t="n">
-        <v>165.1</v>
+        <v>198.7</v>
       </c>
       <c r="H17" t="n">
-        <v>83.09999999999999</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-130.72</v>
+        <v>-78.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-42.66</v>
+        <v>-53.84</v>
       </c>
       <c r="L17" t="n">
-        <v>137.5</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:04</t>
+          <t>04:40:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.01</v>
+        <v>3.92</v>
       </c>
       <c r="F18" t="n">
-        <v>10.26</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="n">
-        <v>185.2</v>
+        <v>203.5</v>
       </c>
       <c r="H18" t="n">
-        <v>72.8</v>
+        <v>63.6</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>93.26000000000001</v>
+        <v>-71.87</v>
       </c>
       <c r="K18" t="n">
-        <v>21.14</v>
+        <v>-44.98</v>
       </c>
       <c r="L18" t="n">
-        <v>95.63</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:44:07</t>
+          <t>04:42:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="F19" t="n">
-        <v>11.78</v>
+        <v>11.95</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>179.9</v>
       </c>
       <c r="H19" t="n">
-        <v>76.5</v>
+        <v>57.1</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-38.81</v>
+        <v>73.16</v>
       </c>
       <c r="K19" t="n">
-        <v>-127</v>
+        <v>34.2</v>
       </c>
       <c r="L19" t="n">
-        <v>132.8</v>
+        <v>80.76000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:56</t>
+          <t>04:49:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="F20" t="n">
-        <v>8.81</v>
+        <v>8.01</v>
       </c>
       <c r="G20" t="n">
-        <v>189.2</v>
+        <v>178.1</v>
       </c>
       <c r="H20" t="n">
-        <v>79.8</v>
+        <v>61.7</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.19</v>
+        <v>105.05</v>
       </c>
       <c r="K20" t="n">
-        <v>121.94</v>
+        <v>-14.15</v>
       </c>
       <c r="L20" t="n">
-        <v>121.98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:49:49</t>
+          <t>04:50:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.32</v>
+        <v>3.51</v>
       </c>
       <c r="F21" t="n">
-        <v>9.67</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>195.2</v>
+        <v>188</v>
       </c>
       <c r="H21" t="n">
-        <v>79.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.99</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>105.12</v>
+        <v>-101.3</v>
       </c>
       <c r="L21" t="n">
-        <v>105.7</v>
+        <v>101.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:03</t>
+          <t>04:51:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.23</v>
+        <v>2.04</v>
       </c>
       <c r="F22" t="n">
-        <v>9.529999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="H22" t="n">
-        <v>79.5</v>
+        <v>56.9</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>39.46</v>
+        <v>-29.15</v>
       </c>
       <c r="K22" t="n">
-        <v>153.03</v>
+        <v>-61.35</v>
       </c>
       <c r="L22" t="n">
-        <v>158.04</v>
+        <v>67.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:57:00</t>
+          <t>04:56:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="F23" t="n">
-        <v>8.84</v>
+        <v>12.9</v>
       </c>
       <c r="G23" t="n">
-        <v>181</v>
+        <v>189.5</v>
       </c>
       <c r="H23" t="n">
-        <v>85.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>163.13</v>
+        <v>124.82</v>
       </c>
       <c r="K23" t="n">
-        <v>-27.25</v>
+        <v>-95.56</v>
       </c>
       <c r="L23" t="n">
-        <v>165.39</v>
+        <v>157.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>04:56:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="F24" t="n">
-        <v>13.38</v>
+        <v>10.1</v>
       </c>
       <c r="G24" t="n">
-        <v>190.8</v>
+        <v>186</v>
       </c>
       <c r="H24" t="n">
-        <v>82.7</v>
+        <v>41.7</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-13.19</v>
+        <v>-134.49</v>
       </c>
       <c r="K24" t="n">
-        <v>-84.22</v>
+        <v>-25.8</v>
       </c>
       <c r="L24" t="n">
-        <v>85.25</v>
+        <v>136.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:00:30</t>
+          <t>04:57:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.74</v>
+        <v>3.19</v>
       </c>
       <c r="F25" t="n">
-        <v>9.48</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>174.1</v>
+        <v>192.5</v>
       </c>
       <c r="H25" t="n">
-        <v>80.5</v>
+        <v>72.2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-148.28</v>
+        <v>-188.12</v>
       </c>
       <c r="K25" t="n">
-        <v>32.85</v>
+        <v>-49.35</v>
       </c>
       <c r="L25" t="n">
-        <v>151.88</v>
+        <v>194.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:04:39</t>
+          <t>05:03:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.38</v>
+        <v>3.6</v>
       </c>
       <c r="F26" t="n">
-        <v>14.03</v>
+        <v>10.41</v>
       </c>
       <c r="G26" t="n">
-        <v>190.9</v>
+        <v>185.9</v>
       </c>
       <c r="H26" t="n">
-        <v>79.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>276.83</v>
+        <v>-153.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-105.57</v>
+        <v>-130.11</v>
       </c>
       <c r="L26" t="n">
-        <v>296.28</v>
+        <v>201.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:07:03</t>
+          <t>05:05:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="F27" t="n">
-        <v>10.68</v>
+        <v>13.32</v>
       </c>
       <c r="G27" t="n">
-        <v>197.5</v>
+        <v>190.5</v>
       </c>
       <c r="H27" t="n">
-        <v>79.3</v>
+        <v>34.8</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-162.61</v>
+        <v>-258.71</v>
       </c>
       <c r="K27" t="n">
-        <v>259.2</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>305.99</v>
+        <v>271.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:08:39</t>
+          <t>05:07:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.63</v>
+        <v>4.03</v>
       </c>
       <c r="F28" t="n">
-        <v>10.85</v>
+        <v>13.65</v>
       </c>
       <c r="G28" t="n">
-        <v>167.1</v>
+        <v>187.6</v>
       </c>
       <c r="H28" t="n">
-        <v>80.5</v>
+        <v>38.3</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>-219.31</v>
+        <v>-185.22</v>
       </c>
       <c r="K28" t="n">
-        <v>212.74</v>
+        <v>-245.35</v>
       </c>
       <c r="L28" t="n">
-        <v>305.54</v>
+        <v>307.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:19:46</t>
+          <t>05:18:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="F29" t="n">
-        <v>12.19</v>
+        <v>11.97</v>
       </c>
       <c r="G29" t="n">
-        <v>203.6</v>
+        <v>189.6</v>
       </c>
       <c r="H29" t="n">
-        <v>77.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-103.26</v>
+        <v>23.8</v>
       </c>
       <c r="K29" t="n">
-        <v>42.55</v>
+        <v>-49.23</v>
       </c>
       <c r="L29" t="n">
-        <v>111.68</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:22:25</t>
+          <t>05:20:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.25</v>
+        <v>3.44</v>
       </c>
       <c r="F30" t="n">
-        <v>14.03</v>
+        <v>8.08</v>
       </c>
       <c r="G30" t="n">
-        <v>188.5</v>
+        <v>191.1</v>
       </c>
       <c r="H30" t="n">
-        <v>85</v>
+        <v>66.7</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>2.35</v>
+        <v>-26.67</v>
       </c>
       <c r="K30" t="n">
-        <v>67.22</v>
+        <v>-40.95</v>
       </c>
       <c r="L30" t="n">
-        <v>67.26000000000001</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:24:47</t>
+          <t>05:22:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="F31" t="n">
-        <v>8.949999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="G31" t="n">
-        <v>203.1</v>
+        <v>187.2</v>
       </c>
       <c r="H31" t="n">
-        <v>87.59999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>20.76</v>
+        <v>-10.54</v>
       </c>
       <c r="K31" t="n">
-        <v>-80.73</v>
+        <v>-47.83</v>
       </c>
       <c r="L31" t="n">
-        <v>83.36</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:35</t>
+          <t>05:27:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.93</v>
+        <v>3.53</v>
       </c>
       <c r="F32" t="n">
-        <v>8.84</v>
+        <v>10.81</v>
       </c>
       <c r="G32" t="n">
-        <v>192.4</v>
+        <v>192.2</v>
       </c>
       <c r="H32" t="n">
-        <v>82.09999999999999</v>
+        <v>43.4</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>85.02</v>
+        <v>-15.58</v>
       </c>
       <c r="K32" t="n">
-        <v>101.71</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>132.57</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:58</t>
+          <t>05:28:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.6</v>
+        <v>4.23</v>
       </c>
       <c r="F33" t="n">
-        <v>10.88</v>
+        <v>12.02</v>
       </c>
       <c r="G33" t="n">
-        <v>193.5</v>
+        <v>196.9</v>
       </c>
       <c r="H33" t="n">
-        <v>81.3</v>
+        <v>61.7</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.11</v>
+        <v>11.38</v>
       </c>
       <c r="K33" t="n">
-        <v>-49.54</v>
+        <v>-97.89</v>
       </c>
       <c r="L33" t="n">
-        <v>95.05</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:33:21</t>
+          <t>05:30:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.52</v>
+        <v>3.93</v>
       </c>
       <c r="F34" t="n">
-        <v>11.08</v>
+        <v>14.03</v>
       </c>
       <c r="G34" t="n">
-        <v>195.9</v>
+        <v>187.6</v>
       </c>
       <c r="H34" t="n">
-        <v>81.90000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.26</v>
+        <v>13.68</v>
       </c>
       <c r="K34" t="n">
-        <v>103.25</v>
+        <v>43.47</v>
       </c>
       <c r="L34" t="n">
-        <v>111.56</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:39:30</t>
+          <t>05:35:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.66</v>
+        <v>4.2</v>
       </c>
       <c r="F35" t="n">
-        <v>10.63</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>197</v>
+        <v>187.8</v>
       </c>
       <c r="H35" t="n">
-        <v>84.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-75.18000000000001</v>
+        <v>-143.15</v>
       </c>
       <c r="K35" t="n">
-        <v>137</v>
+        <v>45.15</v>
       </c>
       <c r="L35" t="n">
-        <v>156.27</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:41:23</t>
+          <t>05:37:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.06</v>
+        <v>4.83</v>
       </c>
       <c r="F36" t="n">
-        <v>14.03</v>
+        <v>12.7</v>
       </c>
       <c r="G36" t="n">
-        <v>199.4</v>
+        <v>180.6</v>
       </c>
       <c r="H36" t="n">
-        <v>78.09999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-147.99</v>
+        <v>-137.66</v>
       </c>
       <c r="K36" t="n">
-        <v>50.99</v>
+        <v>8.5</v>
       </c>
       <c r="L36" t="n">
-        <v>156.53</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:42:10</t>
+          <t>05:39:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.03</v>
+        <v>4.27</v>
       </c>
       <c r="F37" t="n">
-        <v>10.7</v>
+        <v>13.74</v>
       </c>
       <c r="G37" t="n">
-        <v>178.2</v>
+        <v>186.9</v>
       </c>
       <c r="H37" t="n">
-        <v>80.3</v>
+        <v>45.1</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>1.06</v>
+        <v>-137.63</v>
       </c>
       <c r="K37" t="n">
-        <v>-135.33</v>
+        <v>28.68</v>
       </c>
       <c r="L37" t="n">
-        <v>135.33</v>
+        <v>140.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:48:10</t>
+          <t>05:43:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.87</v>
+        <v>4.34</v>
       </c>
       <c r="F38" t="n">
-        <v>12.09</v>
+        <v>14.03</v>
       </c>
       <c r="G38" t="n">
-        <v>186.9</v>
+        <v>187.1</v>
       </c>
       <c r="H38" t="n">
-        <v>78</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>36.97</v>
+        <v>-114.87</v>
       </c>
       <c r="K38" t="n">
-        <v>155.67</v>
+        <v>-116.07</v>
       </c>
       <c r="L38" t="n">
-        <v>160</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:49:12</t>
+          <t>05:44:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.86</v>
+        <v>3.61</v>
       </c>
       <c r="F39" t="n">
-        <v>10.58</v>
+        <v>11.12</v>
       </c>
       <c r="G39" t="n">
-        <v>198.5</v>
+        <v>204.2</v>
       </c>
       <c r="H39" t="n">
-        <v>84.7</v>
+        <v>81.2</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>1.42</v>
+        <v>-161.42</v>
       </c>
       <c r="K39" t="n">
-        <v>147.56</v>
+        <v>59.02</v>
       </c>
       <c r="L39" t="n">
-        <v>147.57</v>
+        <v>171.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:51:39</t>
+          <t>05:46:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.19</v>
+        <v>3.56</v>
       </c>
       <c r="F40" t="n">
-        <v>7.62</v>
+        <v>12.2</v>
       </c>
       <c r="G40" t="n">
-        <v>212.3</v>
+        <v>202.7</v>
       </c>
       <c r="H40" t="n">
-        <v>79.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-180.18</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>21.92</v>
+        <v>-114.96</v>
       </c>
       <c r="L40" t="n">
-        <v>181.51</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:56:25</t>
+          <t>05:52:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.57</v>
+        <v>2.76</v>
       </c>
       <c r="F41" t="n">
-        <v>14.03</v>
+        <v>11.31</v>
       </c>
       <c r="G41" t="n">
-        <v>185</v>
+        <v>191.3</v>
       </c>
       <c r="H41" t="n">
-        <v>81.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>284.18</v>
+        <v>182.5</v>
       </c>
       <c r="K41" t="n">
-        <v>-17.32</v>
+        <v>-26.09</v>
       </c>
       <c r="L41" t="n">
-        <v>284.71</v>
+        <v>184.35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:58:31</t>
+          <t>05:54:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.58</v>
+        <v>4.27</v>
       </c>
       <c r="F42" t="n">
-        <v>8.15</v>
+        <v>10.26</v>
       </c>
       <c r="G42" t="n">
-        <v>196.8</v>
+        <v>178.1</v>
       </c>
       <c r="H42" t="n">
-        <v>81.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>137.28</v>
+        <v>-199.95</v>
       </c>
       <c r="K42" t="n">
-        <v>-172.81</v>
+        <v>-218.58</v>
       </c>
       <c r="L42" t="n">
-        <v>220.71</v>
+        <v>296.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:00:18</t>
+          <t>05:56:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.31</v>
+        <v>4.02</v>
       </c>
       <c r="F43" t="n">
-        <v>12.7</v>
+        <v>11.43</v>
       </c>
       <c r="G43" t="n">
-        <v>197.9</v>
+        <v>192.2</v>
       </c>
       <c r="H43" t="n">
-        <v>77.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-153.59</v>
+        <v>-52.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-217</v>
+        <v>-220.47</v>
       </c>
       <c r="L43" t="n">
-        <v>265.85</v>
+        <v>226.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:10:18</t>
+          <t>06:06:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.8</v>
+        <v>5.69</v>
       </c>
       <c r="F44" t="n">
-        <v>10.58</v>
+        <v>14.03</v>
       </c>
       <c r="G44" t="n">
-        <v>189.9</v>
+        <v>194.2</v>
       </c>
       <c r="H44" t="n">
-        <v>81.09999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>92.97</v>
+        <v>-5.51</v>
       </c>
       <c r="K44" t="n">
-        <v>74.34999999999999</v>
+        <v>-132.41</v>
       </c>
       <c r="L44" t="n">
-        <v>119.04</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:11:32</t>
+          <t>06:08:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="F45" t="n">
-        <v>11.59</v>
+        <v>13.45</v>
       </c>
       <c r="G45" t="n">
-        <v>194.7</v>
+        <v>188.1</v>
       </c>
       <c r="H45" t="n">
-        <v>82.5</v>
+        <v>48.1</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.69</v>
+        <v>-61.7</v>
       </c>
       <c r="K45" t="n">
-        <v>69.15000000000001</v>
+        <v>5.16</v>
       </c>
       <c r="L45" t="n">
-        <v>70.3</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:12:33</t>
+          <t>06:10:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.32</v>
+        <v>4.79</v>
       </c>
       <c r="F46" t="n">
-        <v>13.12</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
-        <v>181.2</v>
+        <v>194.3</v>
       </c>
       <c r="H46" t="n">
-        <v>76.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>30.91</v>
+        <v>39.6</v>
       </c>
       <c r="K46" t="n">
-        <v>56.08</v>
+        <v>-61.79</v>
       </c>
       <c r="L46" t="n">
-        <v>64.03</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:17:01</t>
+          <t>06:15:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.29</v>
+        <v>4.05</v>
       </c>
       <c r="F47" t="n">
-        <v>10.52</v>
+        <v>11.08</v>
       </c>
       <c r="G47" t="n">
-        <v>185.6</v>
+        <v>192</v>
       </c>
       <c r="H47" t="n">
-        <v>81.90000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>10.02</v>
+        <v>61.68</v>
       </c>
       <c r="K47" t="n">
-        <v>68.81999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="L47" t="n">
-        <v>69.54000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:19:35</t>
+          <t>06:17:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="F48" t="n">
-        <v>11.65</v>
+        <v>11.24</v>
       </c>
       <c r="G48" t="n">
-        <v>174.8</v>
+        <v>188.2</v>
       </c>
       <c r="H48" t="n">
-        <v>77.2</v>
+        <v>36.8</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-31.26</v>
+        <v>46.85</v>
       </c>
       <c r="K48" t="n">
-        <v>-107.17</v>
+        <v>-91.26000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>111.63</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:22:05</t>
+          <t>06:18:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.72</v>
+        <v>4.36</v>
       </c>
       <c r="F49" t="n">
-        <v>8.84</v>
+        <v>13.39</v>
       </c>
       <c r="G49" t="n">
-        <v>191.4</v>
+        <v>185.1</v>
       </c>
       <c r="H49" t="n">
-        <v>88.7</v>
+        <v>63.7</v>
       </c>
       <c r="I49" t="n">
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-31.75</v>
+        <v>-101.9</v>
       </c>
       <c r="K49" t="n">
-        <v>61.28</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>69.01000000000001</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:27:01</t>
+          <t>06:24:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="F50" t="n">
-        <v>12.55</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>188.9</v>
+        <v>171.3</v>
       </c>
       <c r="H50" t="n">
-        <v>74.7</v>
+        <v>29.3</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-65.64</v>
+        <v>-100.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-153.39</v>
+        <v>5.24</v>
       </c>
       <c r="L50" t="n">
-        <v>166.85</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:29:35</t>
+          <t>06:25:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="F51" t="n">
-        <v>13.98</v>
+        <v>12.51</v>
       </c>
       <c r="G51" t="n">
-        <v>189.2</v>
+        <v>197.7</v>
       </c>
       <c r="H51" t="n">
-        <v>80.5</v>
+        <v>49.2</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>-47.88</v>
+        <v>83.7</v>
       </c>
       <c r="K51" t="n">
-        <v>199.53</v>
+        <v>-33.27</v>
       </c>
       <c r="L51" t="n">
-        <v>205.2</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:30:58</t>
+          <t>06:27:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="F52" t="n">
-        <v>14.03</v>
+        <v>12.28</v>
       </c>
       <c r="G52" t="n">
-        <v>197.4</v>
+        <v>176.2</v>
       </c>
       <c r="H52" t="n">
-        <v>76.5</v>
+        <v>46.4</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J52" t="n">
-        <v>-31.7</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-157.21</v>
+        <v>-82.55</v>
       </c>
       <c r="L52" t="n">
-        <v>160.37</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:36:32</t>
+          <t>06:31:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.01</v>
+        <v>4.45</v>
       </c>
       <c r="F53" t="n">
-        <v>11.82</v>
+        <v>13.1</v>
       </c>
       <c r="G53" t="n">
-        <v>190.7</v>
+        <v>192.8</v>
       </c>
       <c r="H53" t="n">
-        <v>77.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>-188.12</v>
+        <v>213.91</v>
       </c>
       <c r="K53" t="n">
-        <v>-137.87</v>
+        <v>36.08</v>
       </c>
       <c r="L53" t="n">
-        <v>233.23</v>
+        <v>216.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:37:29</t>
+          <t>06:33:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.93</v>
+        <v>3.67</v>
       </c>
       <c r="F54" t="n">
-        <v>14.03</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>185.6</v>
+        <v>190.6</v>
       </c>
       <c r="H54" t="n">
-        <v>79.3</v>
+        <v>69</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>62.35</v>
+        <v>-63.62</v>
       </c>
       <c r="K54" t="n">
-        <v>-148.98</v>
+        <v>-166.25</v>
       </c>
       <c r="L54" t="n">
-        <v>161.5</v>
+        <v>178.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:39:52</t>
+          <t>06:35:21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.81</v>
+        <v>4.11</v>
       </c>
       <c r="F55" t="n">
-        <v>12.83</v>
+        <v>11.75</v>
       </c>
       <c r="G55" t="n">
-        <v>191.6</v>
+        <v>183.7</v>
       </c>
       <c r="H55" t="n">
-        <v>77.09999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-90.61</v>
+        <v>-195.95</v>
       </c>
       <c r="K55" t="n">
-        <v>-204.18</v>
+        <v>24.21</v>
       </c>
       <c r="L55" t="n">
-        <v>223.38</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:44:28</t>
+          <t>06:40:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.4</v>
+        <v>3.66</v>
       </c>
       <c r="F56" t="n">
-        <v>12.61</v>
+        <v>12.06</v>
       </c>
       <c r="G56" t="n">
-        <v>183.3</v>
+        <v>186.8</v>
       </c>
       <c r="H56" t="n">
-        <v>80</v>
+        <v>7.5</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>24.81</v>
+        <v>27.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-275.05</v>
+        <v>219.17</v>
       </c>
       <c r="L56" t="n">
-        <v>276.17</v>
+        <v>220.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:45:59</t>
+          <t>06:42:19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.77</v>
+        <v>4.03</v>
       </c>
       <c r="F57" t="n">
-        <v>9.56</v>
+        <v>10.92</v>
       </c>
       <c r="G57" t="n">
-        <v>176.7</v>
+        <v>203.8</v>
       </c>
       <c r="H57" t="n">
-        <v>81.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>202.58</v>
+        <v>-263.25</v>
       </c>
       <c r="K57" t="n">
-        <v>148.09</v>
+        <v>83.62</v>
       </c>
       <c r="L57" t="n">
-        <v>250.93</v>
+        <v>276.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:47:44</t>
+          <t>06:44:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="F58" t="n">
-        <v>14.03</v>
+        <v>12.5</v>
       </c>
       <c r="G58" t="n">
-        <v>179.7</v>
+        <v>195.4</v>
       </c>
       <c r="H58" t="n">
-        <v>79</v>
+        <v>50.6</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>286.47</v>
+        <v>212.91</v>
       </c>
       <c r="K58" t="n">
-        <v>223.07</v>
+        <v>-331.73</v>
       </c>
       <c r="L58" t="n">
-        <v>363.08</v>
+        <v>394.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>06:56:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.62</v>
+        <v>4.53</v>
       </c>
       <c r="F59" t="n">
-        <v>10.72</v>
+        <v>12.35</v>
       </c>
       <c r="G59" t="n">
-        <v>172.4</v>
+        <v>188.4</v>
       </c>
       <c r="H59" t="n">
-        <v>75.09999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>45.41</v>
+        <v>12.24</v>
       </c>
       <c r="K59" t="n">
-        <v>58.2</v>
+        <v>-93.23999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>73.81999999999999</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:01:37</t>
+          <t>06:57:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="F60" t="n">
-        <v>9.390000000000001</v>
+        <v>11.49</v>
       </c>
       <c r="G60" t="n">
-        <v>188.9</v>
+        <v>194.6</v>
       </c>
       <c r="H60" t="n">
-        <v>76.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.45</v>
+        <v>57.82</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.94</v>
+        <v>-28.5</v>
       </c>
       <c r="L60" t="n">
-        <v>57.43</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:02:49</t>
+          <t>06:59:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.87</v>
+        <v>4.3</v>
       </c>
       <c r="F61" t="n">
-        <v>10.27</v>
+        <v>14.03</v>
       </c>
       <c r="G61" t="n">
-        <v>185.7</v>
+        <v>181.9</v>
       </c>
       <c r="H61" t="n">
-        <v>80.8</v>
+        <v>67.3</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>9.470000000000001</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-56.66</v>
+        <v>-14.06</v>
       </c>
       <c r="L61" t="n">
-        <v>57.44</v>
+        <v>66.51000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:08:23</t>
+          <t>07:04:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.82</v>
+        <v>3.47</v>
       </c>
       <c r="F62" t="n">
-        <v>13.27</v>
+        <v>10.54</v>
       </c>
       <c r="G62" t="n">
-        <v>188.6</v>
+        <v>179.4</v>
       </c>
       <c r="H62" t="n">
-        <v>75.3</v>
+        <v>61.2</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.07</v>
+        <v>55.61</v>
       </c>
       <c r="K62" t="n">
-        <v>92.06</v>
+        <v>-20.81</v>
       </c>
       <c r="L62" t="n">
-        <v>98.52</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:10:08</t>
+          <t>07:06:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="F63" t="n">
-        <v>13.85</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>185.6</v>
+        <v>199.2</v>
       </c>
       <c r="H63" t="n">
-        <v>73.09999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>94.75</v>
+        <v>-16.75</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.71</v>
+        <v>-84.38</v>
       </c>
       <c r="L63" t="n">
-        <v>106.08</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:12:03</t>
+          <t>07:08:24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.12</v>
+        <v>3.86</v>
       </c>
       <c r="F64" t="n">
-        <v>14.03</v>
+        <v>13.59</v>
       </c>
       <c r="G64" t="n">
-        <v>194.7</v>
+        <v>181.5</v>
       </c>
       <c r="H64" t="n">
-        <v>79.7</v>
+        <v>49.1</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-100.68</v>
+        <v>-80.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-146.27</v>
+        <v>-0.61</v>
       </c>
       <c r="L64" t="n">
-        <v>177.57</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:17:42</t>
+          <t>07:13:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.33</v>
+        <v>4.61</v>
       </c>
       <c r="F65" t="n">
-        <v>14.03</v>
+        <v>13.85</v>
       </c>
       <c r="G65" t="n">
-        <v>187.1</v>
+        <v>179.8</v>
       </c>
       <c r="H65" t="n">
-        <v>77.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>159.77</v>
+        <v>-113.08</v>
       </c>
       <c r="K65" t="n">
-        <v>50.93</v>
+        <v>20.7</v>
       </c>
       <c r="L65" t="n">
-        <v>167.69</v>
+        <v>114.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:18:50</t>
+          <t>07:15:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.16</v>
+        <v>3.58</v>
       </c>
       <c r="F66" t="n">
-        <v>12.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>187.1</v>
+        <v>184.4</v>
       </c>
       <c r="H66" t="n">
-        <v>78.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.67</v>
+        <v>62.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-150.44</v>
+        <v>-91.47</v>
       </c>
       <c r="L66" t="n">
-        <v>152.14</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:21:27</t>
+          <t>07:17:16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="F67" t="n">
-        <v>14.03</v>
+        <v>11.69</v>
       </c>
       <c r="G67" t="n">
-        <v>175.5</v>
+        <v>191.2</v>
       </c>
       <c r="H67" t="n">
-        <v>87.8</v>
+        <v>69.2</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.55</v>
+        <v>-59.99</v>
       </c>
       <c r="K67" t="n">
-        <v>147.77</v>
+        <v>-100.89</v>
       </c>
       <c r="L67" t="n">
-        <v>170.75</v>
+        <v>117.38</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:27:33</t>
+          <t>07:22:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.14</v>
+        <v>3.48</v>
       </c>
       <c r="F68" t="n">
-        <v>11.65</v>
+        <v>14.03</v>
       </c>
       <c r="G68" t="n">
-        <v>197.2</v>
+        <v>182</v>
       </c>
       <c r="H68" t="n">
-        <v>74.7</v>
+        <v>70.7</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J68" t="n">
-        <v>179.61</v>
+        <v>150.27</v>
       </c>
       <c r="K68" t="n">
-        <v>2.14</v>
+        <v>49.8</v>
       </c>
       <c r="L68" t="n">
-        <v>179.63</v>
+        <v>158.31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:29:09</t>
+          <t>07:23:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.03</v>
+        <v>4.02</v>
       </c>
       <c r="F69" t="n">
-        <v>10.48</v>
+        <v>10.34</v>
       </c>
       <c r="G69" t="n">
-        <v>179.3</v>
+        <v>189.2</v>
       </c>
       <c r="H69" t="n">
-        <v>78</v>
+        <v>81.7</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>139.26</v>
+        <v>-58.2</v>
       </c>
       <c r="K69" t="n">
-        <v>56.1</v>
+        <v>140.25</v>
       </c>
       <c r="L69" t="n">
-        <v>150.13</v>
+        <v>151.85</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:31:36</t>
+          <t>07:26:03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.82</v>
+        <v>4.81</v>
       </c>
       <c r="F70" t="n">
-        <v>9.640000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G70" t="n">
-        <v>167.9</v>
+        <v>180.2</v>
       </c>
       <c r="H70" t="n">
-        <v>79.7</v>
+        <v>22.1</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-26.19</v>
+        <v>133.53</v>
       </c>
       <c r="K70" t="n">
-        <v>217.76</v>
+        <v>-276.38</v>
       </c>
       <c r="L70" t="n">
-        <v>219.33</v>
+        <v>306.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:36:07</t>
+          <t>07:30:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="F71" t="n">
-        <v>11.16</v>
+        <v>12.9</v>
       </c>
       <c r="G71" t="n">
-        <v>193.7</v>
+        <v>198.7</v>
       </c>
       <c r="H71" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-214.21</v>
+        <v>10.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-108.43</v>
+        <v>-255.27</v>
       </c>
       <c r="L71" t="n">
-        <v>240.09</v>
+        <v>255.47</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:38:14</t>
+          <t>07:31:49</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.83</v>
+        <v>4.39</v>
       </c>
       <c r="F72" t="n">
-        <v>9.210000000000001</v>
+        <v>12.62</v>
       </c>
       <c r="G72" t="n">
-        <v>188.4</v>
+        <v>188.5</v>
       </c>
       <c r="H72" t="n">
-        <v>83.8</v>
+        <v>43.5</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-295.21</v>
+        <v>122.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-238.66</v>
+        <v>223.75</v>
       </c>
       <c r="L72" t="n">
-        <v>379.62</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:40:22</t>
+          <t>07:33:36</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="F73" t="n">
-        <v>14.03</v>
+        <v>12.56</v>
       </c>
       <c r="G73" t="n">
-        <v>177.1</v>
+        <v>189.7</v>
       </c>
       <c r="H73" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>241.56</v>
+        <v>247.97</v>
       </c>
       <c r="K73" t="n">
-        <v>-48.74</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>246.43</v>
+        <v>258.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:48:14</t>
+          <t>07:46:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.76</v>
+        <v>4.71</v>
       </c>
       <c r="F74" t="n">
-        <v>13.03</v>
+        <v>14.03</v>
       </c>
       <c r="G74" t="n">
-        <v>185.8</v>
+        <v>185.6</v>
       </c>
       <c r="H74" t="n">
-        <v>79.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-70.33</v>
+        <v>54.14</v>
       </c>
       <c r="K74" t="n">
-        <v>75.95</v>
+        <v>-89.18000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>103.52</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:50:33</t>
+          <t>07:49:13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="F75" t="n">
-        <v>13.08</v>
+        <v>12.59</v>
       </c>
       <c r="G75" t="n">
-        <v>172.3</v>
+        <v>205.5</v>
       </c>
       <c r="H75" t="n">
-        <v>75.3</v>
+        <v>72.7</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>40.87</v>
+        <v>-32.84</v>
       </c>
       <c r="K75" t="n">
-        <v>-86.29000000000001</v>
+        <v>-55.66</v>
       </c>
       <c r="L75" t="n">
-        <v>95.48</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:52:04</t>
+          <t>07:51:34</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="F76" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="G76" t="n">
-        <v>187.5</v>
+        <v>175.9</v>
       </c>
       <c r="H76" t="n">
-        <v>75.59999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-81.28</v>
+        <v>-51.67</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.33</v>
+        <v>-26.75</v>
       </c>
       <c r="L76" t="n">
-        <v>94.56</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:55:53</t>
+          <t>07:55:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.77</v>
+        <v>3.04</v>
       </c>
       <c r="F77" t="n">
-        <v>14.03</v>
+        <v>6.32</v>
       </c>
       <c r="G77" t="n">
-        <v>183.1</v>
+        <v>182.2</v>
       </c>
       <c r="H77" t="n">
-        <v>71.40000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>-62.35</v>
+        <v>-50.51</v>
       </c>
       <c r="K77" t="n">
-        <v>114.19</v>
+        <v>-48.83</v>
       </c>
       <c r="L77" t="n">
-        <v>130.1</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:35</t>
+          <t>07:56:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="F78" t="n">
-        <v>14.03</v>
+        <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>177.1</v>
+        <v>192.3</v>
       </c>
       <c r="H78" t="n">
-        <v>82</v>
+        <v>33.8</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>94.84999999999999</v>
+        <v>55.53</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.61</v>
+        <v>58.14</v>
       </c>
       <c r="L78" t="n">
-        <v>119.45</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:58:17</t>
+          <t>07:57:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="F79" t="n">
-        <v>14.03</v>
+        <v>12.88</v>
       </c>
       <c r="G79" t="n">
-        <v>181.1</v>
+        <v>186.9</v>
       </c>
       <c r="H79" t="n">
-        <v>77.8</v>
+        <v>54</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>20.6</v>
+        <v>103.78</v>
       </c>
       <c r="K79" t="n">
-        <v>79.15000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>81.78</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:02:05</t>
+          <t>08:03:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.96</v>
+        <v>4.62</v>
       </c>
       <c r="F80" t="n">
-        <v>13.09</v>
+        <v>14.03</v>
       </c>
       <c r="G80" t="n">
-        <v>196.7</v>
+        <v>197.1</v>
       </c>
       <c r="H80" t="n">
-        <v>76.09999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>20.32</v>
+        <v>40.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-108.67</v>
+        <v>-151.54</v>
       </c>
       <c r="L80" t="n">
-        <v>110.56</v>
+        <v>156.76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:04:28</t>
+          <t>08:04:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.84</v>
+        <v>4.23</v>
       </c>
       <c r="F81" t="n">
-        <v>13.62</v>
+        <v>11.85</v>
       </c>
       <c r="G81" t="n">
-        <v>174.6</v>
+        <v>171.1</v>
       </c>
       <c r="H81" t="n">
-        <v>80.5</v>
+        <v>43.9</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>-75.56999999999999</v>
+        <v>-78.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-166.58</v>
+        <v>-96.33</v>
       </c>
       <c r="L81" t="n">
-        <v>182.92</v>
+        <v>124.21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:05:58</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.71</v>
+        <v>4.71</v>
       </c>
       <c r="F82" t="n">
-        <v>8.300000000000001</v>
+        <v>14.03</v>
       </c>
       <c r="G82" t="n">
-        <v>189.1</v>
+        <v>196.8</v>
       </c>
       <c r="H82" t="n">
-        <v>76.8</v>
+        <v>56.5</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>51.85</v>
+        <v>-60.43</v>
       </c>
       <c r="K82" t="n">
-        <v>-107.3</v>
+        <v>-110.17</v>
       </c>
       <c r="L82" t="n">
-        <v>119.17</v>
+        <v>125.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:10:53</t>
+          <t>08:10:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.77</v>
+        <v>4.69</v>
       </c>
       <c r="F83" t="n">
-        <v>14.03</v>
+        <v>13.76</v>
       </c>
       <c r="G83" t="n">
-        <v>193.7</v>
+        <v>199.4</v>
       </c>
       <c r="H83" t="n">
-        <v>76.7</v>
+        <v>95.5</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>83.19</v>
+        <v>-175.15</v>
       </c>
       <c r="K83" t="n">
-        <v>-308.74</v>
+        <v>-107.91</v>
       </c>
       <c r="L83" t="n">
-        <v>319.75</v>
+        <v>205.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:12:19</t>
+          <t>08:12:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.31</v>
+        <v>3.91</v>
       </c>
       <c r="F84" t="n">
         <v>14.03</v>
       </c>
       <c r="G84" t="n">
-        <v>198.1</v>
+        <v>179.7</v>
       </c>
       <c r="H84" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-89.59</v>
+        <v>162.56</v>
       </c>
       <c r="K84" t="n">
-        <v>144.98</v>
+        <v>-73.3</v>
       </c>
       <c r="L84" t="n">
-        <v>170.43</v>
+        <v>178.32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:14</t>
+          <t>08:14:15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.49</v>
+        <v>3.77</v>
       </c>
       <c r="F85" t="n">
-        <v>10.25</v>
+        <v>11.57</v>
       </c>
       <c r="G85" t="n">
-        <v>178.1</v>
+        <v>203.7</v>
       </c>
       <c r="H85" t="n">
-        <v>85.7</v>
+        <v>61</v>
       </c>
       <c r="I85" t="n">
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>98.51000000000001</v>
+        <v>-179.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-154.05</v>
+        <v>-48.19</v>
       </c>
       <c r="L85" t="n">
-        <v>182.85</v>
+        <v>185.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:17:43</t>
+          <t>08:20:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.41</v>
+        <v>4.4</v>
       </c>
       <c r="F86" t="n">
-        <v>14.03</v>
+        <v>13.98</v>
       </c>
       <c r="G86" t="n">
-        <v>181.7</v>
+        <v>198.9</v>
       </c>
       <c r="H86" t="n">
-        <v>76.7</v>
+        <v>80.3</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>289.66</v>
+        <v>-264.11</v>
       </c>
       <c r="K86" t="n">
-        <v>-154.77</v>
+        <v>44.5</v>
       </c>
       <c r="L86" t="n">
-        <v>328.41</v>
+        <v>267.84</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:19:37</t>
+          <t>08:22:26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="F87" t="n">
-        <v>13.89</v>
+        <v>13.48</v>
       </c>
       <c r="G87" t="n">
-        <v>197.4</v>
+        <v>176.4</v>
       </c>
       <c r="H87" t="n">
-        <v>75.3</v>
+        <v>88.8</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-270.93</v>
+        <v>158.12</v>
       </c>
       <c r="K87" t="n">
-        <v>-351.48</v>
+        <v>68.37</v>
       </c>
       <c r="L87" t="n">
-        <v>443.77</v>
+        <v>172.26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:47</t>
+          <t>08:24:50</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="F88" t="n">
-        <v>8.390000000000001</v>
+        <v>14.03</v>
       </c>
       <c r="G88" t="n">
-        <v>180.7</v>
+        <v>178</v>
       </c>
       <c r="H88" t="n">
-        <v>75.8</v>
+        <v>39.1</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>276.75</v>
+        <v>129.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-109.32</v>
+        <v>-168.81</v>
       </c>
       <c r="L88" t="n">
-        <v>297.56</v>
+        <v>212.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="F14" t="n">
-        <v>10.84</v>
+        <v>13.78</v>
       </c>
       <c r="G14" t="n">
-        <v>172.7</v>
+        <v>180.4</v>
       </c>
       <c r="H14" t="n">
-        <v>49.9</v>
+        <v>75.8</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>60.42</v>
+        <v>-52.97</v>
       </c>
       <c r="K14" t="n">
-        <v>15.13</v>
+        <v>1.35</v>
       </c>
       <c r="L14" t="n">
-        <v>62.28</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:32:10</t>
+          <t>04:32:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.32</v>
+        <v>3.26</v>
       </c>
       <c r="F15" t="n">
-        <v>11.45</v>
+        <v>10.05</v>
       </c>
       <c r="G15" t="n">
-        <v>186.8</v>
+        <v>196.6</v>
       </c>
       <c r="H15" t="n">
-        <v>59.6</v>
+        <v>55.1</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>48.01</v>
+        <v>-47.71</v>
       </c>
       <c r="K15" t="n">
-        <v>20.93</v>
+        <v>-18.11</v>
       </c>
       <c r="L15" t="n">
-        <v>52.38</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:33:01</t>
+          <t>04:33:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.59</v>
+        <v>2.75</v>
       </c>
       <c r="F16" t="n">
-        <v>12.14</v>
+        <v>7.03</v>
       </c>
       <c r="G16" t="n">
-        <v>187.6</v>
+        <v>183.7</v>
       </c>
       <c r="H16" t="n">
-        <v>42.6</v>
+        <v>55.4</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.86</v>
+        <v>-33.6</v>
       </c>
       <c r="K16" t="n">
-        <v>22.35</v>
+        <v>-8.06</v>
       </c>
       <c r="L16" t="n">
-        <v>51.91</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:38:15</t>
+          <t>04:37:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="F17" t="n">
-        <v>8.27</v>
+        <v>7.63</v>
       </c>
       <c r="G17" t="n">
-        <v>198.7</v>
+        <v>183.4</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>58.5</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>-78.62</v>
+        <v>57.69</v>
       </c>
       <c r="K17" t="n">
-        <v>-53.84</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
-        <v>95.29000000000001</v>
+        <v>69.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:42</t>
+          <t>04:38:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>12.58</v>
       </c>
       <c r="G18" t="n">
-        <v>203.5</v>
+        <v>191.6</v>
       </c>
       <c r="H18" t="n">
-        <v>63.6</v>
+        <v>49.5</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>-71.87</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-44.98</v>
+        <v>-24.75</v>
       </c>
       <c r="L18" t="n">
-        <v>84.79000000000001</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:48</t>
+          <t>04:40:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="F19" t="n">
-        <v>11.95</v>
+        <v>11.79</v>
       </c>
       <c r="G19" t="n">
-        <v>179.9</v>
+        <v>189.7</v>
       </c>
       <c r="H19" t="n">
-        <v>57.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>73.16</v>
+        <v>-37.84</v>
       </c>
       <c r="K19" t="n">
-        <v>34.2</v>
+        <v>-44.59</v>
       </c>
       <c r="L19" t="n">
-        <v>80.76000000000001</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:49:18</t>
+          <t>04:44:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.71</v>
+        <v>4.21</v>
       </c>
       <c r="F20" t="n">
-        <v>8.01</v>
+        <v>14.03</v>
       </c>
       <c r="G20" t="n">
-        <v>178.1</v>
+        <v>191.7</v>
       </c>
       <c r="H20" t="n">
-        <v>61.7</v>
+        <v>45.4</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>105.05</v>
+        <v>155.04</v>
       </c>
       <c r="K20" t="n">
-        <v>-14.15</v>
+        <v>-5.66</v>
       </c>
       <c r="L20" t="n">
-        <v>106</v>
+        <v>155.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:36</t>
+          <t>04:46:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="F21" t="n">
-        <v>9.359999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>188</v>
+        <v>180.7</v>
       </c>
       <c r="H21" t="n">
-        <v>65.2</v>
+        <v>57.8</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>-108.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-101.3</v>
+        <v>52.23</v>
       </c>
       <c r="L21" t="n">
-        <v>101.34</v>
+        <v>120.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:31</t>
+          <t>04:48:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.04</v>
+        <v>3.28</v>
       </c>
       <c r="F22" t="n">
-        <v>6.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>193</v>
+        <v>185.2</v>
       </c>
       <c r="H22" t="n">
-        <v>56.9</v>
+        <v>47.8</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-29.15</v>
+        <v>-2.03</v>
       </c>
       <c r="K22" t="n">
-        <v>-61.35</v>
+        <v>118.97</v>
       </c>
       <c r="L22" t="n">
-        <v>67.92</v>
+        <v>118.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:06</t>
+          <t>04:51:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.77</v>
+        <v>3.49</v>
       </c>
       <c r="F23" t="n">
-        <v>12.9</v>
+        <v>11.87</v>
       </c>
       <c r="G23" t="n">
-        <v>189.5</v>
+        <v>179.8</v>
       </c>
       <c r="H23" t="n">
-        <v>77.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>124.82</v>
+        <v>-147.9</v>
       </c>
       <c r="K23" t="n">
-        <v>-95.56</v>
+        <v>87.95</v>
       </c>
       <c r="L23" t="n">
-        <v>157.2</v>
+        <v>172.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:52</t>
+          <t>04:54:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.3</v>
+        <v>4.29</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1</v>
+        <v>14.03</v>
       </c>
       <c r="G24" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H24" t="n">
-        <v>41.7</v>
+        <v>65.5</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-134.49</v>
+        <v>182.17</v>
       </c>
       <c r="K24" t="n">
-        <v>-25.8</v>
+        <v>68.94</v>
       </c>
       <c r="L24" t="n">
-        <v>136.95</v>
+        <v>194.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:57:52</t>
+          <t>04:56:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.19</v>
+        <v>3.69</v>
       </c>
       <c r="F25" t="n">
-        <v>9.890000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="G25" t="n">
-        <v>192.5</v>
+        <v>188.9</v>
       </c>
       <c r="H25" t="n">
-        <v>72.2</v>
+        <v>43.3</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-188.12</v>
+        <v>69.94</v>
       </c>
       <c r="K25" t="n">
-        <v>-49.35</v>
+        <v>204.19</v>
       </c>
       <c r="L25" t="n">
-        <v>194.48</v>
+        <v>215.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:03:45</t>
+          <t>05:00:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1132,31 +1132,31 @@
         <v>3.6</v>
       </c>
       <c r="F26" t="n">
-        <v>10.41</v>
+        <v>12.76</v>
       </c>
       <c r="G26" t="n">
-        <v>185.9</v>
+        <v>182.1</v>
       </c>
       <c r="H26" t="n">
-        <v>71.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-153.24</v>
+        <v>-227.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-130.11</v>
+        <v>0.98</v>
       </c>
       <c r="L26" t="n">
-        <v>201.02</v>
+        <v>227.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:43</t>
+          <t>05:01:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.83</v>
+        <v>4.31</v>
       </c>
       <c r="F27" t="n">
-        <v>13.32</v>
+        <v>12.57</v>
       </c>
       <c r="G27" t="n">
-        <v>190.5</v>
+        <v>180.4</v>
       </c>
       <c r="H27" t="n">
-        <v>34.8</v>
+        <v>63.3</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-258.71</v>
+        <v>-118.27</v>
       </c>
       <c r="K27" t="n">
-        <v>-80.84999999999999</v>
+        <v>326.02</v>
       </c>
       <c r="L27" t="n">
-        <v>271.04</v>
+        <v>346.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:28</t>
+          <t>05:03:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.03</v>
+        <v>3.31</v>
       </c>
       <c r="F28" t="n">
-        <v>13.65</v>
+        <v>11.68</v>
       </c>
       <c r="G28" t="n">
-        <v>187.6</v>
+        <v>177.4</v>
       </c>
       <c r="H28" t="n">
-        <v>38.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-185.22</v>
+        <v>51.61</v>
       </c>
       <c r="K28" t="n">
-        <v>-245.35</v>
+        <v>260.48</v>
       </c>
       <c r="L28" t="n">
-        <v>307.41</v>
+        <v>265.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:18:26</t>
+          <t>05:16:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.23</v>
+        <v>3.89</v>
       </c>
       <c r="F29" t="n">
-        <v>11.97</v>
+        <v>9.91</v>
       </c>
       <c r="G29" t="n">
-        <v>189.6</v>
+        <v>198.2</v>
       </c>
       <c r="H29" t="n">
-        <v>88.3</v>
+        <v>61.9</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>23.8</v>
+        <v>-2.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.23</v>
+        <v>-51.05</v>
       </c>
       <c r="L29" t="n">
-        <v>54.68</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:20:16</t>
+          <t>05:18:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.44</v>
+        <v>3.66</v>
       </c>
       <c r="F30" t="n">
-        <v>8.08</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>191.1</v>
+        <v>198.1</v>
       </c>
       <c r="H30" t="n">
-        <v>66.7</v>
+        <v>14.5</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.67</v>
+        <v>44.6</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.95</v>
+        <v>8.73</v>
       </c>
       <c r="L30" t="n">
-        <v>48.87</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:22:25</t>
+          <t>05:21:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.06</v>
+        <v>3.42</v>
       </c>
       <c r="F31" t="n">
-        <v>13.15</v>
+        <v>10.48</v>
       </c>
       <c r="G31" t="n">
-        <v>187.2</v>
+        <v>184.5</v>
       </c>
       <c r="H31" t="n">
-        <v>35.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.54</v>
+        <v>-37.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.83</v>
+        <v>-25.23</v>
       </c>
       <c r="L31" t="n">
-        <v>48.98</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:27:20</t>
+          <t>05:25:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.53</v>
+        <v>4.17</v>
       </c>
       <c r="F32" t="n">
-        <v>10.81</v>
+        <v>14.03</v>
       </c>
       <c r="G32" t="n">
-        <v>192.2</v>
+        <v>157</v>
       </c>
       <c r="H32" t="n">
-        <v>43.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.58</v>
+        <v>6.46</v>
       </c>
       <c r="K32" t="n">
-        <v>-82.68000000000001</v>
+        <v>36.88</v>
       </c>
       <c r="L32" t="n">
-        <v>84.13</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:28:52</t>
+          <t>05:27:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.23</v>
+        <v>3.78</v>
       </c>
       <c r="F33" t="n">
-        <v>12.02</v>
+        <v>10.74</v>
       </c>
       <c r="G33" t="n">
-        <v>196.9</v>
+        <v>192.4</v>
       </c>
       <c r="H33" t="n">
-        <v>61.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>11.38</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-97.89</v>
+        <v>41.91</v>
       </c>
       <c r="L33" t="n">
-        <v>98.55</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:30:16</t>
+          <t>05:29:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.93</v>
+        <v>4.43</v>
       </c>
       <c r="F34" t="n">
-        <v>14.03</v>
+        <v>12.02</v>
       </c>
       <c r="G34" t="n">
-        <v>187.6</v>
+        <v>171.3</v>
       </c>
       <c r="H34" t="n">
-        <v>32.2</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>13.68</v>
+        <v>163.11</v>
       </c>
       <c r="K34" t="n">
-        <v>43.47</v>
+        <v>-1.41</v>
       </c>
       <c r="L34" t="n">
-        <v>45.57</v>
+        <v>163.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:35:56</t>
+          <t>05:34:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="F35" t="n">
-        <v>9.390000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G35" t="n">
-        <v>187.8</v>
+        <v>182.1</v>
       </c>
       <c r="H35" t="n">
-        <v>60.9</v>
+        <v>51</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-143.15</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>45.15</v>
+        <v>2.64</v>
       </c>
       <c r="L35" t="n">
-        <v>150.1</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:37:53</t>
+          <t>05:36:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.83</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>12.7</v>
+        <v>14.03</v>
       </c>
       <c r="G36" t="n">
-        <v>180.6</v>
+        <v>209.5</v>
       </c>
       <c r="H36" t="n">
-        <v>45.4</v>
+        <v>77.5</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-137.66</v>
+        <v>-77.42</v>
       </c>
       <c r="K36" t="n">
-        <v>8.5</v>
+        <v>-34.7</v>
       </c>
       <c r="L36" t="n">
-        <v>137.93</v>
+        <v>84.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:28</t>
+          <t>05:38:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.27</v>
+        <v>3.99</v>
       </c>
       <c r="F37" t="n">
-        <v>13.74</v>
+        <v>10.65</v>
       </c>
       <c r="G37" t="n">
-        <v>186.9</v>
+        <v>194.8</v>
       </c>
       <c r="H37" t="n">
-        <v>45.1</v>
+        <v>53.5</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-137.63</v>
+        <v>-110.44</v>
       </c>
       <c r="K37" t="n">
-        <v>28.68</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>140.58</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:43:35</t>
+          <t>05:44:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.34</v>
+        <v>3.29</v>
       </c>
       <c r="F38" t="n">
-        <v>14.03</v>
+        <v>10.63</v>
       </c>
       <c r="G38" t="n">
-        <v>187.1</v>
+        <v>198.8</v>
       </c>
       <c r="H38" t="n">
-        <v>86.59999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-114.87</v>
+        <v>-171.71</v>
       </c>
       <c r="K38" t="n">
-        <v>-116.07</v>
+        <v>100.66</v>
       </c>
       <c r="L38" t="n">
-        <v>163.3</v>
+        <v>199.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:44:51</t>
+          <t>05:45:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.61</v>
+        <v>3.41</v>
       </c>
       <c r="F39" t="n">
-        <v>11.12</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>204.2</v>
+        <v>186.4</v>
       </c>
       <c r="H39" t="n">
-        <v>81.2</v>
+        <v>41.3</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-161.42</v>
+        <v>223.44</v>
       </c>
       <c r="K39" t="n">
-        <v>59.02</v>
+        <v>-30.45</v>
       </c>
       <c r="L39" t="n">
-        <v>171.87</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:46:50</t>
+          <t>05:47:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="F40" t="n">
-        <v>12.2</v>
+        <v>13.82</v>
       </c>
       <c r="G40" t="n">
-        <v>202.7</v>
+        <v>171.4</v>
       </c>
       <c r="H40" t="n">
-        <v>67.8</v>
+        <v>61.3</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>90.98999999999999</v>
+        <v>33.66</v>
       </c>
       <c r="K40" t="n">
-        <v>-114.96</v>
+        <v>211.9</v>
       </c>
       <c r="L40" t="n">
-        <v>146.61</v>
+        <v>214.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:52:02</t>
+          <t>05:52:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.76</v>
+        <v>4.04</v>
       </c>
       <c r="F41" t="n">
-        <v>11.31</v>
+        <v>10.7</v>
       </c>
       <c r="G41" t="n">
-        <v>191.3</v>
+        <v>191.1</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>182.5</v>
+        <v>-166.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-26.09</v>
+        <v>-209.94</v>
       </c>
       <c r="L41" t="n">
-        <v>184.35</v>
+        <v>267.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:54:36</t>
+          <t>05:54:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="F42" t="n">
-        <v>10.26</v>
+        <v>13.72</v>
       </c>
       <c r="G42" t="n">
-        <v>178.1</v>
+        <v>195.2</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>55.4</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-199.95</v>
+        <v>-226.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-218.58</v>
+        <v>-210.6</v>
       </c>
       <c r="L42" t="n">
-        <v>296.24</v>
+        <v>309.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:56:00</t>
+          <t>05:55:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="F43" t="n">
-        <v>11.43</v>
+        <v>9.56</v>
       </c>
       <c r="G43" t="n">
-        <v>192.2</v>
+        <v>183.2</v>
       </c>
       <c r="H43" t="n">
-        <v>67.09999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-52.48</v>
+        <v>112.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-220.47</v>
+        <v>217.23</v>
       </c>
       <c r="L43" t="n">
-        <v>226.63</v>
+        <v>244.57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:40</t>
+          <t>06:06:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.69</v>
+        <v>4.36</v>
       </c>
       <c r="F44" t="n">
-        <v>14.03</v>
+        <v>12.69</v>
       </c>
       <c r="G44" t="n">
-        <v>194.2</v>
+        <v>189.8</v>
       </c>
       <c r="H44" t="n">
-        <v>44.4</v>
+        <v>29</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.51</v>
+        <v>-5.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-132.41</v>
+        <v>36.49</v>
       </c>
       <c r="L44" t="n">
-        <v>132.52</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:08:35</t>
+          <t>06:07:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="F45" t="n">
-        <v>13.45</v>
+        <v>11.5</v>
       </c>
       <c r="G45" t="n">
-        <v>188.1</v>
+        <v>187.6</v>
       </c>
       <c r="H45" t="n">
-        <v>48.1</v>
+        <v>32.2</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.7</v>
+        <v>15.1</v>
       </c>
       <c r="K45" t="n">
-        <v>5.16</v>
+        <v>59.04</v>
       </c>
       <c r="L45" t="n">
-        <v>61.92</v>
+        <v>60.94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:10:18</t>
+          <t>06:09:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.79</v>
+        <v>4.31</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>194.3</v>
+        <v>189.4</v>
       </c>
       <c r="H46" t="n">
-        <v>61.3</v>
+        <v>30.8</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>39.6</v>
+        <v>-26.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.79</v>
+        <v>-130.46</v>
       </c>
       <c r="L46" t="n">
-        <v>73.39</v>
+        <v>133.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:15:26</t>
+          <t>06:13:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="F47" t="n">
-        <v>11.08</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>192</v>
+        <v>200.6</v>
       </c>
       <c r="H47" t="n">
-        <v>28.1</v>
+        <v>38.7</v>
       </c>
       <c r="I47" t="n">
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>61.68</v>
+        <v>-62.94</v>
       </c>
       <c r="K47" t="n">
-        <v>64.3</v>
+        <v>77.28</v>
       </c>
       <c r="L47" t="n">
-        <v>89.09999999999999</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:17:37</t>
+          <t>06:16:02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="F48" t="n">
-        <v>11.24</v>
+        <v>12.06</v>
       </c>
       <c r="G48" t="n">
-        <v>188.2</v>
+        <v>190.5</v>
       </c>
       <c r="H48" t="n">
-        <v>36.8</v>
+        <v>67.8</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>46.85</v>
+        <v>-66.77</v>
       </c>
       <c r="K48" t="n">
-        <v>-91.26000000000001</v>
+        <v>-23.3</v>
       </c>
       <c r="L48" t="n">
-        <v>102.58</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:18:49</t>
+          <t>06:17:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.36</v>
+        <v>4.11</v>
       </c>
       <c r="F49" t="n">
-        <v>13.39</v>
+        <v>14.03</v>
       </c>
       <c r="G49" t="n">
-        <v>185.1</v>
+        <v>199.7</v>
       </c>
       <c r="H49" t="n">
-        <v>63.7</v>
+        <v>85.3</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-101.9</v>
+        <v>89</v>
       </c>
       <c r="K49" t="n">
-        <v>-78.65000000000001</v>
+        <v>-38.41</v>
       </c>
       <c r="L49" t="n">
-        <v>128.72</v>
+        <v>96.93000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:24:41</t>
+          <t>06:22:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="F50" t="n">
-        <v>9</v>
+        <v>9.69</v>
       </c>
       <c r="G50" t="n">
-        <v>171.3</v>
+        <v>189.3</v>
       </c>
       <c r="H50" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="I50" t="n">
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-100.02</v>
+        <v>-133.83</v>
       </c>
       <c r="K50" t="n">
-        <v>5.24</v>
+        <v>20.72</v>
       </c>
       <c r="L50" t="n">
-        <v>100.16</v>
+        <v>135.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:25:57</t>
+          <t>06:25:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.25</v>
+        <v>3.87</v>
       </c>
       <c r="F51" t="n">
-        <v>12.51</v>
+        <v>10.28</v>
       </c>
       <c r="G51" t="n">
-        <v>197.7</v>
+        <v>194.5</v>
       </c>
       <c r="H51" t="n">
-        <v>49.2</v>
+        <v>54</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>83.7</v>
+        <v>26.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-33.27</v>
+        <v>-132.47</v>
       </c>
       <c r="L51" t="n">
-        <v>90.06</v>
+        <v>135.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:27:13</t>
+          <t>06:26:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="F52" t="n">
-        <v>12.28</v>
+        <v>6.46</v>
       </c>
       <c r="G52" t="n">
-        <v>176.2</v>
+        <v>200.9</v>
       </c>
       <c r="H52" t="n">
-        <v>46.4</v>
+        <v>37.4</v>
       </c>
       <c r="I52" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.109999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="K52" t="n">
-        <v>-82.55</v>
+        <v>75.87</v>
       </c>
       <c r="L52" t="n">
-        <v>82.94</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:31:49</t>
+          <t>06:32:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="F53" t="n">
-        <v>13.1</v>
+        <v>11.11</v>
       </c>
       <c r="G53" t="n">
-        <v>192.8</v>
+        <v>176.8</v>
       </c>
       <c r="H53" t="n">
-        <v>86.8</v>
+        <v>62.7</v>
       </c>
       <c r="I53" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
+        <v>-37.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-210.52</v>
+      </c>
+      <c r="L53" t="n">
         <v>213.91</v>
-      </c>
-      <c r="K53" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="L53" t="n">
-        <v>216.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:33:58</t>
+          <t>06:35:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="F54" t="n">
-        <v>8.869999999999999</v>
+        <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>190.6</v>
+        <v>185</v>
       </c>
       <c r="H54" t="n">
-        <v>69</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-63.62</v>
+        <v>158.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-166.25</v>
+        <v>-115.91</v>
       </c>
       <c r="L54" t="n">
-        <v>178.01</v>
+        <v>196.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:35:21</t>
+          <t>06:36:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="F55" t="n">
-        <v>11.75</v>
+        <v>14.03</v>
       </c>
       <c r="G55" t="n">
-        <v>183.7</v>
+        <v>188</v>
       </c>
       <c r="H55" t="n">
-        <v>53.9</v>
+        <v>61.1</v>
       </c>
       <c r="I55" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-195.95</v>
+        <v>-161.8</v>
       </c>
       <c r="K55" t="n">
-        <v>24.21</v>
+        <v>181.45</v>
       </c>
       <c r="L55" t="n">
-        <v>197.44</v>
+        <v>243.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:46</t>
+          <t>06:41:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.66</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="n">
-        <v>12.06</v>
+        <v>12.83</v>
       </c>
       <c r="G56" t="n">
-        <v>186.8</v>
+        <v>195.8</v>
       </c>
       <c r="H56" t="n">
-        <v>7.5</v>
+        <v>62.3</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>27.13</v>
+        <v>-51.15</v>
       </c>
       <c r="K56" t="n">
-        <v>219.17</v>
+        <v>233.72</v>
       </c>
       <c r="L56" t="n">
-        <v>220.84</v>
+        <v>239.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:42:19</t>
+          <t>06:43:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="F57" t="n">
-        <v>10.92</v>
+        <v>14.03</v>
       </c>
       <c r="G57" t="n">
-        <v>203.8</v>
+        <v>194.2</v>
       </c>
       <c r="H57" t="n">
-        <v>52.7</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-263.25</v>
+        <v>-38.26</v>
       </c>
       <c r="K57" t="n">
-        <v>83.62</v>
+        <v>296.24</v>
       </c>
       <c r="L57" t="n">
-        <v>276.21</v>
+        <v>298.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:06</t>
+          <t>06:45:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="F58" t="n">
-        <v>12.5</v>
+        <v>10.16</v>
       </c>
       <c r="G58" t="n">
-        <v>195.4</v>
+        <v>186.3</v>
       </c>
       <c r="H58" t="n">
-        <v>50.6</v>
+        <v>68.3</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>212.91</v>
+        <v>3.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-331.73</v>
+        <v>-213.01</v>
       </c>
       <c r="L58" t="n">
-        <v>394.18</v>
+        <v>213.04</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:56:54</t>
+          <t>06:54:26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="F59" t="n">
-        <v>12.35</v>
+        <v>11.48</v>
       </c>
       <c r="G59" t="n">
-        <v>188.4</v>
+        <v>188.7</v>
       </c>
       <c r="H59" t="n">
-        <v>44.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>12.24</v>
+        <v>-49.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-93.23999999999999</v>
+        <v>-42.36</v>
       </c>
       <c r="L59" t="n">
-        <v>94.04000000000001</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:57:48</t>
+          <t>06:56:21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.08</v>
+        <v>4.24</v>
       </c>
       <c r="F60" t="n">
-        <v>11.49</v>
+        <v>14.03</v>
       </c>
       <c r="G60" t="n">
-        <v>194.6</v>
+        <v>188.5</v>
       </c>
       <c r="H60" t="n">
-        <v>89.40000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>57.82</v>
+        <v>5.79</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.5</v>
+        <v>-70.44</v>
       </c>
       <c r="L60" t="n">
-        <v>64.45999999999999</v>
+        <v>70.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:23</t>
+          <t>06:58:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.3</v>
+        <v>3.31</v>
       </c>
       <c r="F61" t="n">
         <v>14.03</v>
       </c>
       <c r="G61" t="n">
-        <v>181.9</v>
+        <v>190.9</v>
       </c>
       <c r="H61" t="n">
-        <v>67.3</v>
+        <v>45.9</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>65.01000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.06</v>
+        <v>-39.37</v>
       </c>
       <c r="L61" t="n">
-        <v>66.51000000000001</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:04:14</t>
+          <t>07:03:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.47</v>
+        <v>4.38</v>
       </c>
       <c r="F62" t="n">
-        <v>10.54</v>
+        <v>14.03</v>
       </c>
       <c r="G62" t="n">
-        <v>179.4</v>
+        <v>188.2</v>
       </c>
       <c r="H62" t="n">
-        <v>61.2</v>
+        <v>76.7</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>55.61</v>
+        <v>-80.98999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-20.81</v>
+        <v>48.74</v>
       </c>
       <c r="L62" t="n">
-        <v>59.37</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:06:50</t>
+          <t>07:04:18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="F63" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>199.2</v>
+        <v>174.2</v>
       </c>
       <c r="H63" t="n">
-        <v>7.3</v>
+        <v>23</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.75</v>
+        <v>-46.97</v>
       </c>
       <c r="K63" t="n">
-        <v>-84.38</v>
+        <v>24.01</v>
       </c>
       <c r="L63" t="n">
-        <v>86.03</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:08:24</t>
+          <t>07:06:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="F64" t="n">
-        <v>13.59</v>
+        <v>9.59</v>
       </c>
       <c r="G64" t="n">
-        <v>181.5</v>
+        <v>191.3</v>
       </c>
       <c r="H64" t="n">
-        <v>49.1</v>
+        <v>86</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.08</v>
+        <v>-95.29000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.61</v>
+        <v>51.77</v>
       </c>
       <c r="L64" t="n">
-        <v>80.09</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:13:17</t>
+          <t>07:10:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.61</v>
+        <v>4.03</v>
       </c>
       <c r="F65" t="n">
-        <v>13.85</v>
+        <v>11.65</v>
       </c>
       <c r="G65" t="n">
-        <v>179.8</v>
+        <v>191.3</v>
       </c>
       <c r="H65" t="n">
-        <v>66.59999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-113.08</v>
+        <v>20.13</v>
       </c>
       <c r="K65" t="n">
-        <v>20.7</v>
+        <v>-128.48</v>
       </c>
       <c r="L65" t="n">
-        <v>114.96</v>
+        <v>130.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:15:30</t>
+          <t>07:12:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="F66" t="n">
-        <v>8.630000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="G66" t="n">
-        <v>184.4</v>
+        <v>183.4</v>
       </c>
       <c r="H66" t="n">
-        <v>84.8</v>
+        <v>47.4</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>62.3</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-91.47</v>
+        <v>-102.9</v>
       </c>
       <c r="L66" t="n">
-        <v>110.67</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:17:16</t>
+          <t>07:15:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="F67" t="n">
-        <v>11.69</v>
+        <v>12.37</v>
       </c>
       <c r="G67" t="n">
-        <v>191.2</v>
+        <v>168.1</v>
       </c>
       <c r="H67" t="n">
-        <v>69.2</v>
+        <v>65.3</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-59.99</v>
+        <v>-50.44</v>
       </c>
       <c r="K67" t="n">
-        <v>-100.89</v>
+        <v>-119.96</v>
       </c>
       <c r="L67" t="n">
-        <v>117.38</v>
+        <v>130.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:22:24</t>
+          <t>07:19:57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.48</v>
+        <v>2.78</v>
       </c>
       <c r="F68" t="n">
-        <v>14.03</v>
+        <v>5.2</v>
       </c>
       <c r="G68" t="n">
-        <v>182</v>
+        <v>203.8</v>
       </c>
       <c r="H68" t="n">
-        <v>70.7</v>
+        <v>52.7</v>
       </c>
       <c r="I68" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>150.27</v>
+        <v>-124.35</v>
       </c>
       <c r="K68" t="n">
-        <v>49.8</v>
+        <v>96.05</v>
       </c>
       <c r="L68" t="n">
-        <v>158.31</v>
+        <v>157.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:23:42</t>
+          <t>07:22:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
       <c r="F69" t="n">
-        <v>10.34</v>
+        <v>13.12</v>
       </c>
       <c r="G69" t="n">
-        <v>189.2</v>
+        <v>185.4</v>
       </c>
       <c r="H69" t="n">
-        <v>81.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-58.2</v>
+        <v>-202.9</v>
       </c>
       <c r="K69" t="n">
-        <v>140.25</v>
+        <v>-176.92</v>
       </c>
       <c r="L69" t="n">
-        <v>151.85</v>
+        <v>269.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:26:03</t>
+          <t>07:23:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.81</v>
+        <v>3.79</v>
       </c>
       <c r="F70" t="n">
-        <v>11.9</v>
+        <v>11.09</v>
       </c>
       <c r="G70" t="n">
-        <v>180.2</v>
+        <v>195.6</v>
       </c>
       <c r="H70" t="n">
-        <v>22.1</v>
+        <v>54.9</v>
       </c>
       <c r="I70" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>133.53</v>
+        <v>-156.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-276.38</v>
+        <v>50.12</v>
       </c>
       <c r="L70" t="n">
-        <v>306.94</v>
+        <v>164.25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:30:35</t>
+          <t>07:27:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.2</v>
+        <v>4.68</v>
       </c>
       <c r="F71" t="n">
-        <v>12.9</v>
+        <v>13.68</v>
       </c>
       <c r="G71" t="n">
-        <v>198.7</v>
+        <v>185.4</v>
       </c>
       <c r="H71" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>10.12</v>
+        <v>-74.27</v>
       </c>
       <c r="K71" t="n">
-        <v>-255.27</v>
+        <v>-291.7</v>
       </c>
       <c r="L71" t="n">
-        <v>255.47</v>
+        <v>301.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:49</t>
+          <t>07:29:52</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
       <c r="F72" t="n">
-        <v>12.62</v>
+        <v>14.03</v>
       </c>
       <c r="G72" t="n">
-        <v>188.5</v>
+        <v>182.7</v>
       </c>
       <c r="H72" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>122.38</v>
+        <v>-195.05</v>
       </c>
       <c r="K72" t="n">
-        <v>223.75</v>
+        <v>75.11</v>
       </c>
       <c r="L72" t="n">
-        <v>255.03</v>
+        <v>209.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:33:36</t>
+          <t>07:30:37</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="F73" t="n">
-        <v>12.56</v>
+        <v>12.94</v>
       </c>
       <c r="G73" t="n">
-        <v>189.7</v>
+        <v>192.3</v>
       </c>
       <c r="H73" t="n">
-        <v>79.90000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>247.97</v>
+        <v>-129.8</v>
       </c>
       <c r="K73" t="n">
-        <v>72.48999999999999</v>
+        <v>-200.07</v>
       </c>
       <c r="L73" t="n">
-        <v>258.34</v>
+        <v>238.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:46:51</t>
+          <t>07:41:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.71</v>
+        <v>3.47</v>
       </c>
       <c r="F74" t="n">
-        <v>14.03</v>
+        <v>6.4</v>
       </c>
       <c r="G74" t="n">
-        <v>185.6</v>
+        <v>171.8</v>
       </c>
       <c r="H74" t="n">
-        <v>72.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>54.14</v>
+        <v>-7.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-89.18000000000001</v>
+        <v>-61.42</v>
       </c>
       <c r="L74" t="n">
-        <v>104.33</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:49:13</t>
+          <t>07:44:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="F75" t="n">
-        <v>12.59</v>
+        <v>11.26</v>
       </c>
       <c r="G75" t="n">
-        <v>205.5</v>
+        <v>180.9</v>
       </c>
       <c r="H75" t="n">
-        <v>72.7</v>
+        <v>68.3</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-32.84</v>
+        <v>39.91</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.66</v>
+        <v>32.72</v>
       </c>
       <c r="L75" t="n">
-        <v>64.63</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:51:34</t>
+          <t>07:45:22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="F76" t="n">
-        <v>12.73</v>
+        <v>14.03</v>
       </c>
       <c r="G76" t="n">
-        <v>175.9</v>
+        <v>173.8</v>
       </c>
       <c r="H76" t="n">
-        <v>35.6</v>
+        <v>62.7</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.67</v>
+        <v>-24.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-26.75</v>
+        <v>56.75</v>
       </c>
       <c r="L76" t="n">
-        <v>58.18</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:55:37</t>
+          <t>07:49:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.04</v>
+        <v>4.65</v>
       </c>
       <c r="F77" t="n">
-        <v>6.32</v>
+        <v>14.03</v>
       </c>
       <c r="G77" t="n">
-        <v>182.2</v>
+        <v>198.2</v>
       </c>
       <c r="H77" t="n">
-        <v>34.9</v>
+        <v>55.3</v>
       </c>
       <c r="I77" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-50.51</v>
+        <v>-53.23</v>
       </c>
       <c r="K77" t="n">
-        <v>-48.83</v>
+        <v>-117.45</v>
       </c>
       <c r="L77" t="n">
-        <v>70.25</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:48</t>
+          <t>07:51:22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.08</v>
+        <v>4.35</v>
       </c>
       <c r="F78" t="n">
-        <v>12</v>
+        <v>14.03</v>
       </c>
       <c r="G78" t="n">
-        <v>192.3</v>
+        <v>176.7</v>
       </c>
       <c r="H78" t="n">
-        <v>33.8</v>
+        <v>52.1</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>55.53</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>58.14</v>
+        <v>57.19</v>
       </c>
       <c r="L78" t="n">
-        <v>80.39</v>
+        <v>105.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:57:57</t>
+          <t>07:53:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.71</v>
+        <v>3.82</v>
       </c>
       <c r="F79" t="n">
-        <v>12.88</v>
+        <v>13.48</v>
       </c>
       <c r="G79" t="n">
-        <v>186.9</v>
+        <v>184</v>
       </c>
       <c r="H79" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I79" t="n">
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>103.78</v>
+        <v>-59.68</v>
       </c>
       <c r="K79" t="n">
-        <v>-67.40000000000001</v>
+        <v>-48.54</v>
       </c>
       <c r="L79" t="n">
-        <v>123.75</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:03:19</t>
+          <t>07:58:05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.62</v>
+        <v>3.64</v>
       </c>
       <c r="F80" t="n">
-        <v>14.03</v>
+        <v>13.95</v>
       </c>
       <c r="G80" t="n">
-        <v>197.1</v>
+        <v>181.7</v>
       </c>
       <c r="H80" t="n">
-        <v>37.4</v>
+        <v>60.3</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>40.11</v>
+        <v>103.86</v>
       </c>
       <c r="K80" t="n">
-        <v>-151.54</v>
+        <v>25.83</v>
       </c>
       <c r="L80" t="n">
-        <v>156.76</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:04:43</t>
+          <t>07:59:08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.23</v>
+        <v>4.45</v>
       </c>
       <c r="F81" t="n">
-        <v>11.85</v>
+        <v>11.01</v>
       </c>
       <c r="G81" t="n">
-        <v>171.1</v>
+        <v>195.2</v>
       </c>
       <c r="H81" t="n">
-        <v>43.9</v>
+        <v>89</v>
       </c>
       <c r="I81" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-78.41</v>
+        <v>-140.87</v>
       </c>
       <c r="K81" t="n">
-        <v>-96.33</v>
+        <v>-10.5</v>
       </c>
       <c r="L81" t="n">
-        <v>124.21</v>
+        <v>141.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:00:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.71</v>
+        <v>4.05</v>
       </c>
       <c r="F82" t="n">
-        <v>14.03</v>
+        <v>12.8</v>
       </c>
       <c r="G82" t="n">
-        <v>196.8</v>
+        <v>175.4</v>
       </c>
       <c r="H82" t="n">
-        <v>56.5</v>
+        <v>84.2</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-60.43</v>
+        <v>-137.45</v>
       </c>
       <c r="K82" t="n">
-        <v>-110.17</v>
+        <v>-27.35</v>
       </c>
       <c r="L82" t="n">
-        <v>125.65</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:10:23</t>
+          <t>08:04:38</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.69</v>
+        <v>4.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.76</v>
+        <v>13.2</v>
       </c>
       <c r="G83" t="n">
-        <v>199.4</v>
+        <v>199.2</v>
       </c>
       <c r="H83" t="n">
-        <v>95.5</v>
+        <v>55.2</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-175.15</v>
+        <v>-195.76</v>
       </c>
       <c r="K83" t="n">
-        <v>-107.91</v>
+        <v>-159.22</v>
       </c>
       <c r="L83" t="n">
-        <v>205.73</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:12:00</t>
+          <t>08:06:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="F84" t="n">
         <v>14.03</v>
       </c>
       <c r="G84" t="n">
-        <v>179.7</v>
+        <v>184.2</v>
       </c>
       <c r="H84" t="n">
-        <v>55.6</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>162.56</v>
+        <v>-127.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-73.3</v>
+        <v>184.9</v>
       </c>
       <c r="L84" t="n">
-        <v>178.32</v>
+        <v>224.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:14:15</t>
+          <t>08:08:49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.77</v>
+        <v>4.45</v>
       </c>
       <c r="F85" t="n">
-        <v>11.57</v>
+        <v>13.36</v>
       </c>
       <c r="G85" t="n">
-        <v>203.7</v>
+        <v>184.1</v>
       </c>
       <c r="H85" t="n">
-        <v>61</v>
+        <v>73.8</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-179.24</v>
+        <v>-224.57</v>
       </c>
       <c r="K85" t="n">
-        <v>-48.19</v>
+        <v>104.75</v>
       </c>
       <c r="L85" t="n">
-        <v>185.61</v>
+        <v>247.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:20:55</t>
+          <t>08:13:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="F86" t="n">
-        <v>13.98</v>
+        <v>14.03</v>
       </c>
       <c r="G86" t="n">
-        <v>198.9</v>
+        <v>184.5</v>
       </c>
       <c r="H86" t="n">
-        <v>80.3</v>
+        <v>46.4</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>-264.11</v>
+        <v>124.35</v>
       </c>
       <c r="K86" t="n">
-        <v>44.5</v>
+        <v>-82.98</v>
       </c>
       <c r="L86" t="n">
-        <v>267.84</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:22:26</t>
+          <t>08:15:17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="F87" t="n">
-        <v>13.48</v>
+        <v>14.03</v>
       </c>
       <c r="G87" t="n">
-        <v>176.4</v>
+        <v>191.8</v>
       </c>
       <c r="H87" t="n">
-        <v>88.8</v>
+        <v>41.1</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>158.12</v>
+        <v>127</v>
       </c>
       <c r="K87" t="n">
-        <v>68.37</v>
+        <v>52.41</v>
       </c>
       <c r="L87" t="n">
-        <v>172.26</v>
+        <v>137.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:24:50</t>
+          <t>08:16:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.83</v>
+        <v>3.74</v>
       </c>
       <c r="F88" t="n">
-        <v>14.03</v>
+        <v>12.64</v>
       </c>
       <c r="G88" t="n">
-        <v>178</v>
+        <v>187.4</v>
       </c>
       <c r="H88" t="n">
-        <v>39.1</v>
+        <v>16.1</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>129.02</v>
+        <v>-183.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-168.81</v>
+        <v>-12.79</v>
       </c>
       <c r="L88" t="n">
-        <v>212.46</v>
+        <v>184.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>40.64</v>
+        <v>47.5</v>
       </c>
       <c r="K14" t="n">
-        <v>-49.09</v>
+        <v>-57.37</v>
       </c>
       <c r="L14" t="n">
-        <v>63.73</v>
+        <v>74.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.86</v>
+        <v>-17.37</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.67</v>
+        <v>-99.62</v>
       </c>
       <c r="L15" t="n">
-        <v>98.13</v>
+        <v>101.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.14</v>
+        <v>-53.88</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.15</v>
+        <v>-30.02</v>
       </c>
       <c r="L16" t="n">
-        <v>51.67</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>73.72</v>
+        <v>80.69</v>
       </c>
       <c r="K17" t="n">
-        <v>56.82</v>
+        <v>62.18</v>
       </c>
       <c r="L17" t="n">
-        <v>93.06999999999999</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>44.15</v>
+        <v>49.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.66</v>
+        <v>-90.97</v>
       </c>
       <c r="L18" t="n">
-        <v>91.95</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>31.26</v>
+        <v>32.08</v>
       </c>
       <c r="K19" t="n">
-        <v>-129.18</v>
+        <v>-132.53</v>
       </c>
       <c r="L19" t="n">
-        <v>132.91</v>
+        <v>136.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.16</v>
+        <v>-157.97</v>
       </c>
       <c r="K20" t="n">
-        <v>-34.23</v>
+        <v>-38.58</v>
       </c>
       <c r="L20" t="n">
-        <v>144.28</v>
+        <v>162.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-99.12</v>
+        <v>-118.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-37.4</v>
+        <v>-44.7</v>
       </c>
       <c r="L21" t="n">
-        <v>105.94</v>
+        <v>126.61</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.47</v>
+        <v>-24.61</v>
       </c>
       <c r="K22" t="n">
-        <v>10.15</v>
+        <v>12.84</v>
       </c>
       <c r="L22" t="n">
-        <v>21.96</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-41.54</v>
+        <v>-54.64</v>
       </c>
       <c r="K23" t="n">
-        <v>136.57</v>
+        <v>179.63</v>
       </c>
       <c r="L23" t="n">
-        <v>142.75</v>
+        <v>187.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-17.35</v>
+        <v>-20.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-219.38</v>
+        <v>-254.02</v>
       </c>
       <c r="L24" t="n">
-        <v>220.07</v>
+        <v>254.81</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>141.56</v>
+        <v>169.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.61</v>
+        <v>-144.55</v>
       </c>
       <c r="L25" t="n">
-        <v>185.98</v>
+        <v>222.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>190.34</v>
+        <v>260.46</v>
       </c>
       <c r="K26" t="n">
-        <v>45.49</v>
+        <v>62.25</v>
       </c>
       <c r="L26" t="n">
-        <v>195.7</v>
+        <v>267.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-244.26</v>
+        <v>-304.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.24</v>
+        <v>-16.53</v>
       </c>
       <c r="L27" t="n">
-        <v>244.62</v>
+        <v>305.38</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-135.4</v>
+        <v>-189.32</v>
       </c>
       <c r="K28" t="n">
-        <v>88.14</v>
+        <v>123.25</v>
       </c>
       <c r="L28" t="n">
-        <v>161.56</v>
+        <v>225.91</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-14.07</v>
+        <v>-15.72</v>
       </c>
       <c r="K29" t="n">
-        <v>69.42</v>
+        <v>77.56</v>
       </c>
       <c r="L29" t="n">
-        <v>70.83</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-110.21</v>
+        <v>-114.7</v>
       </c>
       <c r="L30" t="n">
-        <v>110.24</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.03</v>
+        <v>-30.86</v>
       </c>
       <c r="K31" t="n">
-        <v>83.77</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>88.66</v>
+        <v>94.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>82.62</v>
+        <v>94.03</v>
       </c>
       <c r="K32" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="L32" t="n">
-        <v>82.63</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>85.75</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>86.01000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="L33" t="n">
-        <v>121.46</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>44.61</v>
+        <v>52.92</v>
       </c>
       <c r="K34" t="n">
-        <v>48.69</v>
+        <v>57.76</v>
       </c>
       <c r="L34" t="n">
-        <v>66.03</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>42.14</v>
+        <v>53.52</v>
       </c>
       <c r="K35" t="n">
-        <v>98.09</v>
+        <v>124.58</v>
       </c>
       <c r="L35" t="n">
-        <v>106.76</v>
+        <v>135.59</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>47.8</v>
+        <v>58</v>
       </c>
       <c r="K36" t="n">
-        <v>103.19</v>
+        <v>125.19</v>
       </c>
       <c r="L36" t="n">
-        <v>113.72</v>
+        <v>137.97</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>91.09999999999999</v>
+        <v>104.05</v>
       </c>
       <c r="K37" t="n">
-        <v>80.98999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="L37" t="n">
-        <v>121.9</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-74.59</v>
+        <v>-91.38</v>
       </c>
       <c r="K38" t="n">
-        <v>166.82</v>
+        <v>204.38</v>
       </c>
       <c r="L38" t="n">
-        <v>182.74</v>
+        <v>223.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.71</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-178.01</v>
+        <v>-218.18</v>
       </c>
       <c r="L39" t="n">
-        <v>178.17</v>
+        <v>218.39</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-123.49</v>
+        <v>-160.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-61.51</v>
+        <v>-80.03</v>
       </c>
       <c r="L40" t="n">
-        <v>137.96</v>
+        <v>179.48</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>200.17</v>
+        <v>248.89</v>
       </c>
       <c r="K41" t="n">
-        <v>243.83</v>
+        <v>303.19</v>
       </c>
       <c r="L41" t="n">
-        <v>315.47</v>
+        <v>392.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>390.03</v>
+        <v>454.08</v>
       </c>
       <c r="K42" t="n">
-        <v>15.61</v>
+        <v>18.17</v>
       </c>
       <c r="L42" t="n">
-        <v>390.35</v>
+        <v>454.44</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-125.86</v>
+        <v>-167.92</v>
       </c>
       <c r="K43" t="n">
-        <v>-126.14</v>
+        <v>-168.3</v>
       </c>
       <c r="L43" t="n">
-        <v>178.2</v>
+        <v>237.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>36.33</v>
+        <v>43.11</v>
       </c>
       <c r="K44" t="n">
-        <v>56.23</v>
+        <v>66.73</v>
       </c>
       <c r="L44" t="n">
-        <v>66.94</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-37.94</v>
+        <v>-45.06</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.2</v>
+        <v>-42.98</v>
       </c>
       <c r="L45" t="n">
-        <v>52.44</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>47.41</v>
+        <v>49.64</v>
       </c>
       <c r="K46" t="n">
-        <v>74.31999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="L46" t="n">
-        <v>88.16</v>
+        <v>92.29000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>63.28</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-18</v>
+        <v>-21.69</v>
       </c>
       <c r="L47" t="n">
-        <v>65.79000000000001</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-61.91</v>
+        <v>-73.89</v>
       </c>
       <c r="K48" t="n">
-        <v>18.57</v>
+        <v>22.17</v>
       </c>
       <c r="L48" t="n">
-        <v>64.63</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-71.97</v>
+        <v>-86.48</v>
       </c>
       <c r="K49" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="L49" t="n">
-        <v>71.98</v>
+        <v>86.48</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-133.16</v>
+        <v>-154.61</v>
       </c>
       <c r="K50" t="n">
-        <v>-44.02</v>
+        <v>-51.12</v>
       </c>
       <c r="L50" t="n">
-        <v>140.24</v>
+        <v>162.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.34</v>
+        <v>-80.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-40.25</v>
+        <v>-50.84</v>
       </c>
       <c r="L51" t="n">
-        <v>75.05</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-118.76</v>
+        <v>-138.16</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.46</v>
+        <v>-55.22</v>
       </c>
       <c r="L52" t="n">
-        <v>127.89</v>
+        <v>148.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-41.03</v>
+        <v>-47.71</v>
       </c>
       <c r="K53" t="n">
-        <v>205.79</v>
+        <v>239.31</v>
       </c>
       <c r="L53" t="n">
-        <v>209.84</v>
+        <v>244.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.58</v>
+        <v>-36.36</v>
       </c>
       <c r="K54" t="n">
-        <v>-180.85</v>
+        <v>-222.3</v>
       </c>
       <c r="L54" t="n">
-        <v>183.25</v>
+        <v>225.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-168.67</v>
+        <v>-202.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-101.2</v>
+        <v>-121.51</v>
       </c>
       <c r="L55" t="n">
-        <v>196.7</v>
+        <v>236.18</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>103.1</v>
+        <v>143.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-163.6</v>
+        <v>-227.79</v>
       </c>
       <c r="L56" t="n">
-        <v>193.38</v>
+        <v>269.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-101.36</v>
+        <v>-127.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-222.49</v>
+        <v>-279.91</v>
       </c>
       <c r="L57" t="n">
-        <v>244.5</v>
+        <v>307.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>21.56</v>
+        <v>30.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.29</v>
+        <v>-283.62</v>
       </c>
       <c r="L58" t="n">
-        <v>202.44</v>
+        <v>285.25</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>44.18</v>
+        <v>49.68</v>
       </c>
       <c r="K59" t="n">
-        <v>55.15</v>
+        <v>62</v>
       </c>
       <c r="L59" t="n">
-        <v>70.66</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>67.89</v>
+        <v>71.12</v>
       </c>
       <c r="K60" t="n">
-        <v>67.34999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="L60" t="n">
-        <v>95.63</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>29.64</v>
+        <v>35.61</v>
       </c>
       <c r="K61" t="n">
-        <v>40.45</v>
+        <v>48.6</v>
       </c>
       <c r="L61" t="n">
-        <v>50.15</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-36.27</v>
+        <v>-44.07</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.24</v>
+        <v>-59.83</v>
       </c>
       <c r="L62" t="n">
-        <v>61.16</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>8.41</v>
+        <v>10.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.46</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>53.13</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.31</v>
+        <v>-30.09</v>
       </c>
       <c r="K64" t="n">
-        <v>75.09</v>
+        <v>85.88</v>
       </c>
       <c r="L64" t="n">
-        <v>79.56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>124.88</v>
+        <v>149.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-61.65</v>
+        <v>-73.66</v>
       </c>
       <c r="L65" t="n">
-        <v>139.27</v>
+        <v>166.41</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-111.18</v>
+        <v>-122.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-162.97</v>
+        <v>-179.65</v>
       </c>
       <c r="L66" t="n">
-        <v>197.29</v>
+        <v>217.47</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>138.09</v>
+        <v>158.7</v>
       </c>
       <c r="K67" t="n">
-        <v>56.26</v>
+        <v>64.66</v>
       </c>
       <c r="L67" t="n">
-        <v>149.11</v>
+        <v>171.36</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-23.43</v>
+        <v>-28.74</v>
       </c>
       <c r="K68" t="n">
-        <v>-158.01</v>
+        <v>-193.81</v>
       </c>
       <c r="L68" t="n">
-        <v>159.74</v>
+        <v>195.93</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-85.84</v>
+        <v>-107.35</v>
       </c>
       <c r="K69" t="n">
-        <v>144.87</v>
+        <v>181.17</v>
       </c>
       <c r="L69" t="n">
-        <v>168.4</v>
+        <v>210.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>174.22</v>
+        <v>213.03</v>
       </c>
       <c r="K70" t="n">
-        <v>31.32</v>
+        <v>38.3</v>
       </c>
       <c r="L70" t="n">
-        <v>177.01</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>124.78</v>
+        <v>167.43</v>
       </c>
       <c r="K71" t="n">
-        <v>98.39</v>
+        <v>132.02</v>
       </c>
       <c r="L71" t="n">
-        <v>158.91</v>
+        <v>213.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-44.33</v>
+        <v>-52.92</v>
       </c>
       <c r="K72" t="n">
-        <v>280.73</v>
+        <v>335.14</v>
       </c>
       <c r="L72" t="n">
-        <v>284.21</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.05</v>
+        <v>-206.76</v>
       </c>
       <c r="K73" t="n">
-        <v>-22.97</v>
+        <v>-31.23</v>
       </c>
       <c r="L73" t="n">
-        <v>153.77</v>
+        <v>209.1</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-72.97</v>
+        <v>-77.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.53</v>
+        <v>-47.29</v>
       </c>
       <c r="L74" t="n">
-        <v>85.48</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>43.38</v>
+        <v>52.96</v>
       </c>
       <c r="K75" t="n">
-        <v>34.04</v>
+        <v>41.56</v>
       </c>
       <c r="L75" t="n">
-        <v>55.14</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.76</v>
+        <v>-55.06</v>
       </c>
       <c r="K76" t="n">
-        <v>54.91</v>
+        <v>60.76</v>
       </c>
       <c r="L76" t="n">
-        <v>74.09999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>35.91</v>
+        <v>40.77</v>
       </c>
       <c r="K77" t="n">
-        <v>-76.44</v>
+        <v>-86.79000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>84.45999999999999</v>
+        <v>95.89</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.70999999999999</v>
+        <v>-80.34</v>
       </c>
       <c r="K78" t="n">
-        <v>-42.82</v>
+        <v>-47.97</v>
       </c>
       <c r="L78" t="n">
-        <v>83.52</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.02</v>
+        <v>-46.21</v>
       </c>
       <c r="K79" t="n">
-        <v>80.94</v>
+        <v>89.02</v>
       </c>
       <c r="L79" t="n">
-        <v>91.2</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>106.3</v>
+        <v>125.54</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.81</v>
+        <v>-97.8</v>
       </c>
       <c r="L80" t="n">
-        <v>134.75</v>
+        <v>159.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>21.56</v>
+        <v>28.39</v>
       </c>
       <c r="K81" t="n">
-        <v>87.09</v>
+        <v>114.67</v>
       </c>
       <c r="L81" t="n">
-        <v>89.72</v>
+        <v>118.14</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>35.26</v>
+        <v>45.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-85.48</v>
+        <v>-111.16</v>
       </c>
       <c r="L82" t="n">
-        <v>92.45999999999999</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-91.09999999999999</v>
+        <v>-120.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-163.28</v>
+        <v>-216.45</v>
       </c>
       <c r="L83" t="n">
-        <v>186.97</v>
+        <v>247.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>74.81999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-133.69</v>
+        <v>-164.58</v>
       </c>
       <c r="L84" t="n">
-        <v>153.2</v>
+        <v>188.6</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>74.92</v>
+        <v>92.78</v>
       </c>
       <c r="K85" t="n">
-        <v>-218.31</v>
+        <v>-270.35</v>
       </c>
       <c r="L85" t="n">
-        <v>230.8</v>
+        <v>285.82</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-54.22</v>
+        <v>-77.56</v>
       </c>
       <c r="K86" t="n">
-        <v>200.49</v>
+        <v>286.83</v>
       </c>
       <c r="L86" t="n">
-        <v>207.69</v>
+        <v>297.13</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>152.6</v>
+        <v>206.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-225.18</v>
+        <v>-304.74</v>
       </c>
       <c r="L87" t="n">
-        <v>272.01</v>
+        <v>368.12</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>198.47</v>
+        <v>252.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-67.38</v>
+        <v>-85.56999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>209.59</v>
+        <v>266.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-10.xlsx
+++ b/output/2024-06-10.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>47.5</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>-57.37</v>
+        <v>-67.64</v>
       </c>
       <c r="L14" t="n">
-        <v>74.48</v>
+        <v>87.81</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.37</v>
+        <v>-20.52</v>
       </c>
       <c r="K15" t="n">
-        <v>-99.62</v>
+        <v>-117.69</v>
       </c>
       <c r="L15" t="n">
-        <v>101.13</v>
+        <v>119.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.88</v>
+        <v>-57.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.02</v>
+        <v>-32.08</v>
       </c>
       <c r="L16" t="n">
-        <v>61.68</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>80.69</v>
+        <v>93.84</v>
       </c>
       <c r="K17" t="n">
-        <v>62.18</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>101.87</v>
+        <v>118.48</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>49.79</v>
+        <v>61.23</v>
       </c>
       <c r="K18" t="n">
-        <v>-90.97</v>
+        <v>-111.86</v>
       </c>
       <c r="L18" t="n">
-        <v>103.71</v>
+        <v>127.52</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>32.08</v>
+        <v>34.89</v>
       </c>
       <c r="K19" t="n">
-        <v>-132.53</v>
+        <v>-144.15</v>
       </c>
       <c r="L19" t="n">
-        <v>136.36</v>
+        <v>148.31</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.72</v>
+        <v>-15.87</v>
       </c>
       <c r="K29" t="n">
-        <v>77.56</v>
+        <v>78.33</v>
       </c>
       <c r="L29" t="n">
-        <v>79.14</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>3.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-114.7</v>
+        <v>-140.59</v>
       </c>
       <c r="L30" t="n">
-        <v>114.73</v>
+        <v>140.63</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.86</v>
+        <v>-34.09</v>
       </c>
       <c r="K31" t="n">
-        <v>89.04000000000001</v>
+        <v>98.38</v>
       </c>
       <c r="L31" t="n">
-        <v>94.23999999999999</v>
+        <v>104.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>94.03</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="L32" t="n">
-        <v>94.03</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>52.92</v>
+        <v>57.73</v>
       </c>
       <c r="K34" t="n">
-        <v>57.76</v>
+        <v>63.01</v>
       </c>
       <c r="L34" t="n">
-        <v>78.34</v>
+        <v>85.45999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>43.11</v>
+        <v>62.76</v>
       </c>
       <c r="K44" t="n">
-        <v>66.73</v>
+        <v>97.14</v>
       </c>
       <c r="L44" t="n">
-        <v>79.44</v>
+        <v>115.65</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.06</v>
+        <v>-50.59</v>
       </c>
       <c r="K45" t="n">
-        <v>-42.98</v>
+        <v>-48.26</v>
       </c>
       <c r="L45" t="n">
-        <v>62.27</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>49.64</v>
+        <v>55.95</v>
       </c>
       <c r="K46" t="n">
-        <v>77.8</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>92.29000000000001</v>
+        <v>104.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>76.26000000000001</v>
+        <v>93.34</v>
       </c>
       <c r="K47" t="n">
-        <v>-21.69</v>
+        <v>-26.55</v>
       </c>
       <c r="L47" t="n">
-        <v>79.29000000000001</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.89</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>22.17</v>
+        <v>26.02</v>
       </c>
       <c r="L48" t="n">
-        <v>77.14</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-86.48</v>
+        <v>-99.95999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="L49" t="n">
-        <v>86.48</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>49.68</v>
+        <v>57.38</v>
       </c>
       <c r="K59" t="n">
-        <v>62</v>
+        <v>71.62</v>
       </c>
       <c r="L59" t="n">
-        <v>79.45</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>71.12</v>
+        <v>87.17</v>
       </c>
       <c r="K60" t="n">
-        <v>70.55</v>
+        <v>86.48</v>
       </c>
       <c r="L60" t="n">
-        <v>100.18</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>35.61</v>
+        <v>39.66</v>
       </c>
       <c r="K61" t="n">
-        <v>48.6</v>
+        <v>54.13</v>
       </c>
       <c r="L61" t="n">
-        <v>60.25</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.07</v>
+        <v>-49.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-59.83</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>74.31</v>
+        <v>84.06</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>10.38</v>
+        <v>11.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.73999999999999</v>
+        <v>-72.79000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>65.56999999999999</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.09</v>
+        <v>-33.57</v>
       </c>
       <c r="K64" t="n">
-        <v>85.88</v>
+        <v>95.83</v>
       </c>
       <c r="L64" t="n">
-        <v>91</v>
+        <v>101.54</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-77.5</v>
+        <v>-90.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.29</v>
+        <v>-55.19</v>
       </c>
       <c r="L74" t="n">
-        <v>90.79000000000001</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>52.96</v>
+        <v>71.69</v>
       </c>
       <c r="K75" t="n">
-        <v>41.56</v>
+        <v>56.25</v>
       </c>
       <c r="L75" t="n">
-        <v>67.31999999999999</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.06</v>
+        <v>-63.21</v>
       </c>
       <c r="K76" t="n">
-        <v>60.76</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>82</v>
+        <v>94.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>40.77</v>
+        <v>44.48</v>
       </c>
       <c r="K77" t="n">
-        <v>-86.79000000000001</v>
+        <v>-94.68000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>95.89</v>
+        <v>104.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-80.34</v>
+        <v>-94.59999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-47.97</v>
+        <v>-56.49</v>
       </c>
       <c r="L78" t="n">
-        <v>93.58</v>
+        <v>110.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-46.21</v>
+        <v>-51.17</v>
       </c>
       <c r="K79" t="n">
-        <v>89.02</v>
+        <v>98.58</v>
       </c>
       <c r="L79" t="n">
-        <v>100.3</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="80">
